--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B7B5E0-3B70-42EC-BC95-4969B1A439B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15718B7-2B67-4D7C-98BE-68B73CF5375A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="559">
   <si>
     <t>地圖編號</t>
   </si>
@@ -894,9 +894,6 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1-LQRlGfzne0_J4nhxIvUTFjCue4MyWAs/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>district-04</t>
   </si>
   <si>
     <t>陳政維</t>
@@ -13532,12 +13529,24 @@
     <t>Félix-Antoine Morin</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>district-04</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Home</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13630,6 +13639,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -13652,7 +13668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -13707,6 +13723,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13921,26 +13940,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="13" width="21.28515625" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="26.85546875" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" customWidth="1"/>
-    <col min="17" max="21" width="11.5703125" customWidth="1"/>
-    <col min="22" max="23" width="16.140625" customWidth="1"/>
-    <col min="24" max="24" width="11.5703125" customWidth="1"/>
-    <col min="25" max="25" width="18.85546875" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="6" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="9" max="14" width="21.28515625" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" customWidth="1"/>
+    <col min="16" max="16" width="26.85546875" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" customWidth="1"/>
+    <col min="18" max="22" width="11.5703125" customWidth="1"/>
+    <col min="23" max="24" width="16.140625" customWidth="1"/>
+    <col min="25" max="25" width="11.5703125" customWidth="1"/>
+    <col min="26" max="26" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="25.5">
+    <row r="1" spans="1:27" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -13950,74 +13969,77 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="23" t="s">
+        <v>557</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Z1" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
@@ -14028,70 +14050,73 @@
         <v>27</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>502</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="P2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="13">
         <v>2024</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="S2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="T2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="U2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="V2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="16" t="s">
+      <c r="W2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="X2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3" s="12" t="s">
         <v>42</v>
       </c>
@@ -14102,74 +14127,77 @@
         <v>43</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="14" t="s">
-        <v>504</v>
-      </c>
       <c r="K3" s="14" t="s">
-        <v>470</v>
-      </c>
-      <c r="L3" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="N3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="O3" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="Q3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>2024</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="W3" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="17" t="s">
+      <c r="Y3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Z3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4" s="12" t="s">
         <v>60</v>
       </c>
@@ -14180,70 +14208,73 @@
         <v>61</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="I4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="J4" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="K4" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" s="13" t="s">
+      <c r="Q4" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="13">
+        <v>2022</v>
+      </c>
+      <c r="S4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="P4" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>2022</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="V4" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="W4" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="13" t="s">
+      <c r="X4" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5" s="12" t="s">
         <v>73</v>
       </c>
@@ -14253,73 +14284,76 @@
       <c r="C5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>508</v>
-      </c>
       <c r="K5" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="L5" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="N5" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="O5" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="P5" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="Q5" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="R5" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="16" t="s">
+      <c r="S5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="16" t="s">
+      <c r="T5" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="U5" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="U5" s="16" t="s">
+      <c r="V5" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="W5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="W5" s="16" t="s">
+      <c r="X5" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6" s="12" t="s">
         <v>91</v>
       </c>
@@ -14329,69 +14363,72 @@
       <c r="C6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="I6" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>509</v>
-      </c>
       <c r="K6" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="L6" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="N6" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="Q6" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>2023</v>
       </c>
-      <c r="R6" s="16"/>
       <c r="S6" s="16"/>
-      <c r="T6" s="16" t="s">
+      <c r="T6" s="16"/>
+      <c r="U6" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="V6" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="W6" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="X6" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="13" t="s">
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7" s="12" t="s">
         <v>107</v>
       </c>
@@ -14402,62 +14439,65 @@
         <v>108</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>550</v>
+        <v>108</v>
       </c>
       <c r="E7" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="J7" s="19"/>
       <c r="K7" s="19"/>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="19"/>
+      <c r="M7" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="N7" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="O7" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="P7" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="16"/>
+      <c r="Q7" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="13"/>
       <c r="S7" s="16"/>
-      <c r="T7" s="16" t="s">
+      <c r="T7" s="16"/>
+      <c r="U7" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="U7" s="16" t="s">
+      <c r="V7" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="W7" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="W7" s="16" t="s">
+      <c r="X7" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="13" t="s">
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8" s="12" t="s">
         <v>120</v>
       </c>
@@ -14467,69 +14507,72 @@
       <c r="C8" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="D8" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="I8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="L8" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="L8" s="15" t="s">
+      <c r="M8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="O8" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>130</v>
       </c>
       <c r="P8" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="S8" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="T8" s="16"/>
       <c r="U8" s="16"/>
-      <c r="V8" s="16" t="s">
+      <c r="V8" s="16"/>
+      <c r="W8" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="W8" s="16" t="s">
+      <c r="X8" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="13" t="s">
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9" s="12" t="s">
         <v>136</v>
       </c>
@@ -14540,74 +14583,77 @@
         <v>137</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="M9" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="O9" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="P9" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="Q9" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>2026</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="S9" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="S9" s="16" t="s">
+      <c r="T9" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="U9" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="V9" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="W9" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="X9" s="17" t="s">
+      <c r="Y9" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="Y9" s="13" t="s">
+      <c r="Z9" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10" s="12" t="s">
         <v>156</v>
       </c>
@@ -14617,75 +14663,78 @@
       <c r="C10" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="D10" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="I10" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>512</v>
-      </c>
       <c r="K10" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="L10" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="O10" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>166</v>
       </c>
       <c r="P10" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" s="13">
         <v>2026</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="S10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S10" s="16" t="s">
+      <c r="T10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="T10" s="16" t="s">
+      <c r="U10" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="U10" s="16" t="s">
+      <c r="V10" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="V10" s="16" t="s">
+      <c r="W10" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="X10" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="X10" s="17" t="s">
+      <c r="Y10" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="Y10" s="13" t="s">
+      <c r="Z10" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11" s="12" t="s">
         <v>25</v>
       </c>
@@ -14696,72 +14745,75 @@
         <v>173</v>
       </c>
       <c r="D11" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="I11" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="J11" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="13"/>
+      <c r="N11" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="O11" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="Q11" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>2025</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="S11" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="T11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="U11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="V11" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="W11" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="X11" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="X11" s="17" t="s">
+      <c r="Y11" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="Y11" s="13" t="s">
+      <c r="Z11" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12" s="12" t="s">
         <v>42</v>
       </c>
@@ -14771,73 +14823,76 @@
       <c r="C12" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="I12" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="J12" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="K12" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="M12" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="P12" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>2013</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="S12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="T12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="T12" s="16" t="s">
+      <c r="U12" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="U12" s="16" t="s">
+      <c r="V12" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="W12" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="X12" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="X12" s="17" t="s">
+      <c r="Y12" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="Y12" s="13" t="s">
+      <c r="Z12" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13" s="12" t="s">
         <v>25</v>
       </c>
@@ -14848,74 +14903,77 @@
         <v>209</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="I13" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="J13" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="J13" s="14" t="s">
-        <v>513</v>
-      </c>
       <c r="K13" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="L13" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="N13" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="O13" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="P13" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="Q13" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="Q13" s="18" t="s">
+      <c r="R13" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="R13" s="16" t="s">
+      <c r="S13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="S13" s="16" t="s">
+      <c r="T13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="T13" s="16" t="s">
+      <c r="U13" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="U13" s="16" t="s">
+      <c r="V13" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="W13" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="W13" s="16" t="s">
+      <c r="X13" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="X13" s="17" t="s">
+      <c r="Y13" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="Y13" s="13" t="s">
+      <c r="Z13" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14" s="12" t="s">
         <v>42</v>
       </c>
@@ -14926,74 +14984,77 @@
         <v>225</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="H14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="I14" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="J14" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="L14" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="M14" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="N14" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="O14" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="P14" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="Q14" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>2024</v>
       </c>
-      <c r="R14" s="16" t="s">
+      <c r="S14" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="S14" s="16" t="s">
+      <c r="T14" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="T14" s="16" t="s">
+      <c r="U14" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="U14" s="16" t="s">
+      <c r="V14" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="V14" s="16" t="s">
+      <c r="W14" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="W14" s="16" t="s">
+      <c r="X14" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="X14" s="17" t="s">
+      <c r="Y14" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="Y14" s="13" t="s">
+      <c r="Z14" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15" s="12" t="s">
         <v>60</v>
       </c>
@@ -15004,72 +15065,75 @@
         <v>244</v>
       </c>
       <c r="D15" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="G15" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="I15" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="K15" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="L15" s="14" t="s">
         <v>514</v>
       </c>
-      <c r="K15" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="13"/>
+      <c r="N15" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="O15" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="O15" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="Q15" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>2025</v>
       </c>
-      <c r="R15" s="16" t="s">
+      <c r="S15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="S15" s="16" t="s">
+      <c r="T15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="T15" s="16" t="s">
+      <c r="U15" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="U15" s="16" t="s">
+      <c r="V15" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="W15" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="W15" s="16" t="s">
+      <c r="X15" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="X15" s="17" t="s">
+      <c r="Y15" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="Y15" s="13" t="s">
+      <c r="Z15" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16" s="12" t="s">
         <v>73</v>
       </c>
@@ -15077,75 +15141,78 @@
         <v>208</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="G16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="14" t="s">
+      <c r="J16" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="K16" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="O16" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="R16" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S16" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>473</v>
-      </c>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="P16" s="13" t="s">
+      <c r="T16" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="U16" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="V16" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="W16" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="Q16" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R16" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="S16" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="T16" s="16" t="s">
-        <v>518</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="V16" s="16" t="s">
+      <c r="X16" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y16" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="Z16" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="W16" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="X16" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="Y16" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:27">
       <c r="A17" s="12" t="s">
         <v>73</v>
       </c>
@@ -15153,77 +15220,80 @@
         <v>208</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="F17" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="G17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="14" t="s">
+      <c r="J17" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="K17" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="M17" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="J17" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="L17" s="15" t="s">
+      <c r="N17" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="M17" s="15" t="s">
+      <c r="O17" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="P17" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="O17" s="13" t="s">
+      <c r="Q17" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="P17" s="13" t="s">
+      <c r="R17" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S17" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="U17" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="Q17" s="13">
-        <v>2025</v>
-      </c>
-      <c r="R17" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="S17" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="T17" s="16" t="s">
+      <c r="V17" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="U17" s="16" t="s">
+      <c r="W17" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="X17" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="W17" s="16" t="s">
+      <c r="Y17" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="X17" s="17" t="s">
+      <c r="Z17" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="Y17" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:27">
       <c r="A18" s="12" t="s">
         <v>73</v>
       </c>
@@ -15231,75 +15301,78 @@
         <v>208</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="G18" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="14" t="s">
+      <c r="J18" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="K18" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="L18" s="13"/>
-      <c r="M18" s="15" t="s">
+      <c r="O18" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="P18" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="Q18" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="R18" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="P18" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="S18" s="16" t="s">
+      <c r="U18" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="T18" s="16" t="s">
+      <c r="V18" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="U18" s="16" t="s">
+      <c r="W18" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="X18" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="W18" s="16" t="s">
+      <c r="Y18" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="X18" s="17" t="s">
+      <c r="Z18" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="Y18" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
     </row>
-    <row r="19" spans="1:26" s="5" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="1:27" s="5" customFormat="1" ht="16.5" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>73</v>
       </c>
@@ -15307,75 +15380,78 @@
         <v>208</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="F19" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="G19" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="I19" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="J19" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="K19" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="L19" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="M19" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="N19" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="M19" s="15" t="s">
+      <c r="O19" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="N19" s="13" t="s">
+      <c r="P19" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="Q19" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="R19" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S19" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="Q19" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R19" s="16" t="s">
+      <c r="T19" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="S19" s="16" t="s">
+      <c r="U19" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="T19" s="16" t="s">
+      <c r="V19" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="U19" s="16" t="s">
+      <c r="W19" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="V19" s="20" t="s">
+      <c r="X19" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="W19" s="20" t="s">
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:27">
       <c r="A20" s="12" t="s">
         <v>73</v>
       </c>
@@ -15383,75 +15459,78 @@
         <v>208</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="F20" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="14" t="s">
+      <c r="J20" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="K20" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="J20" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="L20" s="15" t="s">
+      <c r="N20" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="M20" s="15" t="s">
+      <c r="O20" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="N20" s="13" t="s">
+      <c r="P20" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="Q20" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="R20" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S20" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="P20" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>2025</v>
-      </c>
-      <c r="R20" s="16" t="s">
+      <c r="T20" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="S20" s="16" t="s">
+      <c r="U20" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="V20" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="W20" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="X20" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="W20" s="16" t="s">
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:27">
       <c r="A21" s="12" t="s">
         <v>91</v>
       </c>
@@ -15459,77 +15538,80 @@
         <v>208</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="G21" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="14" t="s">
+      <c r="J21" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="K21" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="L21" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="K21" s="14" t="s">
-        <v>467</v>
-      </c>
-      <c r="L21" s="15" t="s">
+      <c r="N21" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="M21" s="15" t="s">
+      <c r="O21" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="N21" s="13" t="s">
+      <c r="P21" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="Q21" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="R21" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S21" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="Q21" s="13">
-        <v>2025</v>
-      </c>
-      <c r="R21" s="16" t="s">
+      <c r="T21" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="S21" s="16" t="s">
+      <c r="U21" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="T21" s="16" t="s">
+      <c r="V21" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="U21" s="16" t="s">
+      <c r="W21" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="X21" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="W21" s="16" t="s">
+      <c r="Y21" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="X21" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="Y21" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA21" s="6"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:27">
       <c r="A22" s="12" t="s">
         <v>107</v>
       </c>
@@ -15537,71 +15619,74 @@
         <v>208</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="F22" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="G22" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="14" t="s">
+      <c r="J22" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="K22" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="L22" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13" t="s">
+      <c r="P22" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="O22" s="13" t="s">
+      <c r="Q22" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="R22" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S22" s="16" t="s">
         <v>365</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>2025</v>
-      </c>
-      <c r="R22" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="S22" s="16" t="s">
-        <v>367</v>
       </c>
       <c r="T22" s="16" t="s">
         <v>366</v>
       </c>
       <c r="U22" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="W22" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="X22" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="W22" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z22" s="6"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA22" s="6"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:27">
       <c r="A23" s="12" t="s">
         <v>120</v>
       </c>
@@ -15609,75 +15694,78 @@
         <v>208</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="G23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="14" t="s">
+      <c r="J23" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="K23" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="15" t="s">
+      <c r="O23" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="N23" s="13" t="s">
+      <c r="P23" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="O23" s="13" t="s">
+      <c r="Q23" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="R23" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="T23" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="U23" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="Q23" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R23" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="S23" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="T23" s="16" t="s">
+      <c r="V23" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="U23" s="16" t="s">
+      <c r="W23" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="X23" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="W23" s="16" t="s">
+      <c r="Y23" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="X23" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y23" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z23" s="6"/>
+      <c r="Z23" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA23" s="6"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:27">
       <c r="A24" s="12" t="s">
         <v>136</v>
       </c>
@@ -15685,77 +15773,80 @@
         <v>208</v>
       </c>
       <c r="C24" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="F24" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="G24" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="14" t="s">
+      <c r="J24" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="K24" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="M24" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="J24" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="L24" s="15" t="s">
+      <c r="N24" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="M24" s="15" t="s">
+      <c r="O24" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="P24" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="R24" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S24" s="16" t="s">
         <v>393</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="S24" s="16" t="s">
-        <v>395</v>
       </c>
       <c r="T24" s="16" t="s">
         <v>394</v>
       </c>
       <c r="U24" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="W24" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="V24" s="16" t="s">
+      <c r="X24" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="W24" s="16" t="s">
+      <c r="Y24" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="X24" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="Y24" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z24" s="6"/>
+      <c r="Z24" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA24" s="6"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:27">
       <c r="A25" s="12" t="s">
         <v>156</v>
       </c>
@@ -15763,198 +15854,206 @@
         <v>208</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="F25" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="G25" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="14" t="s">
+      <c r="J25" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="K25" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="M25" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="J25" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="L25" s="15" t="s">
+      <c r="N25" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="O25" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="N25" s="13" t="s">
+      <c r="P25" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="P25" s="13" t="s">
+      <c r="R25" s="13">
+        <v>2024</v>
+      </c>
+      <c r="S25" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="Q25" s="13">
-        <v>2024</v>
-      </c>
-      <c r="R25" s="16" t="s">
+      <c r="T25" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="S25" s="16" t="s">
+      <c r="U25" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="V25" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="W25" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="V25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="W25" s="16" t="s">
+      <c r="Y25" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="X25" s="17" t="s">
+      <c r="Z25" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA25" s="6"/>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="12" t="s">
         <v>415</v>
-      </c>
-      <c r="Y25" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z25" s="6"/>
-    </row>
-    <row r="26" spans="1:26">
-      <c r="A26" s="12" t="s">
-        <v>416</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="F26" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="G26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="14" t="s">
+      <c r="J26" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="K26" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="M26" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="J26" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="L26" s="15" t="s">
+      <c r="N26" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="M26" s="15" t="s">
+      <c r="O26" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="P26" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="Q26" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="R26" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S26" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="U26" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="Q26" s="13">
-        <v>2025</v>
-      </c>
-      <c r="R26" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="S26" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="T26" s="16" t="s">
+      <c r="V26" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="W26" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="X26" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="W26" s="16" t="s">
+      <c r="Y26" s="17" t="s">
         <v>430</v>
       </c>
-      <c r="X26" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="Y26" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="Z26" s="6"/>
+      <c r="Z26" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="AA26" s="6"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:27">
       <c r="A27" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>527</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="M27" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>527</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="L27" s="15" t="s">
+      <c r="N27" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="M27" s="15" t="s">
+      <c r="O27" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="N27" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="O27" s="13"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
@@ -15964,466 +16063,487 @@
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="Z27" s="6"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="AA27" s="6"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:27">
       <c r="A28" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>433</v>
-      </c>
       <c r="D28" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F28" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="G28" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="R28" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S28" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="T28" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="X28" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="S28" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="W28" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:27">
       <c r="A29" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>433</v>
-      </c>
       <c r="D29" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="G29" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="H29" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="I29" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="K29" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="J29" s="14" t="s">
+      <c r="L29" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="P29" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="K29" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>498</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="O29" s="13" t="s">
+      <c r="Q29" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="T29" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13" t="s">
         <v>536</v>
       </c>
-      <c r="P29" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="S29" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="W29" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="Z29" s="6"/>
+      <c r="X29" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="AA29" s="6"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:27">
       <c r="A30" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B30" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>433</v>
-      </c>
       <c r="D30" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="F30" s="13" t="s">
+      <c r="G30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="I30" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="K30" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="I30" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="J30" s="14" t="s">
+      <c r="L30" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="M30" s="21"/>
+      <c r="N30" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="P30" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="K30" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="L30" s="21"/>
-      <c r="M30" s="22" t="s">
-        <v>501</v>
-      </c>
-      <c r="N30" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="P30" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="R30" s="13">
         <v>2026</v>
       </c>
-      <c r="R30" s="13" t="s">
+      <c r="S30" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="T30" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="S30" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="T30" s="13"/>
       <c r="U30" s="13"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="Z30" s="6"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="AA30" s="6"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:27">
       <c r="A31" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>433</v>
-      </c>
       <c r="D31" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="14" t="s">
         <v>541</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="J31" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="14" t="s">
+      <c r="K31" s="14" t="s">
         <v>542</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="L31" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="M31" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="P31" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="M31" s="15" t="s">
+      <c r="Q31" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="N31" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="O31" s="13" t="s">
+      <c r="R31" s="13"/>
+      <c r="S31" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="T31" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="P31" s="13" t="s">
+      <c r="X31" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="S31" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13" t="s">
-        <v>545</v>
-      </c>
-      <c r="W31" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="Z31" s="6"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="AA31" s="6"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:27">
       <c r="A32" s="12" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C32" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>556</v>
-      </c>
-      <c r="E32" s="13" t="s">
+      <c r="G32" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="H32" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="I32" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="J32" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="K32" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="J32" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="L32" s="15" t="s">
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13" t="s">
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S32" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13">
-        <v>2026</v>
-      </c>
-      <c r="R32" s="13" t="s">
+      <c r="T32" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="T32" s="13"/>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13" t="s">
+      <c r="X32" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="W32" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="Z32" s="6"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="AA32" s="6"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:26">
       <c r="A33" s="3"/>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="Y33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:26">
       <c r="A34" s="3"/>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="Y34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:26">
       <c r="A35" s="3"/>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:26">
       <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:26">
       <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="L4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="L5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="L6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="M6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="L7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="M7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="L8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="M8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="L9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="M9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="X9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="L10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="M10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="X10" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="M11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="X11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="X12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="L13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="M13" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="X13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="L14" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="M14" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="X14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="M15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="X15" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="L17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="M17" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="X17" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="M18" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="X18" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="L19" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="M19" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="L20" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="M20" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L21" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="M21" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="X21" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="M23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="X23" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="L24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="M24" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="X24" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="L25" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="M25" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="X25" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="L26" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="M26" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="X26" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="L27" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="M27" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L32" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="X16" r:id="rId58" xr:uid="{EC25DFAD-6C70-46EA-BB56-5E3B1102F497}"/>
-    <hyperlink ref="L31" r:id="rId59" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
-    <hyperlink ref="M31" r:id="rId60" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
-    <hyperlink ref="M29" r:id="rId61" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
-    <hyperlink ref="L28" r:id="rId62" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
-    <hyperlink ref="M28" r:id="rId63" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
-    <hyperlink ref="M30" r:id="rId64" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="Y3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="Y9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="Y10" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="Y11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="Y12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N13" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="Y13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M14" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N14" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="Y14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="Y15" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="M17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N17" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="Y17" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N18" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="Y18" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="M19" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N19" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M20" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N20" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M21" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N21" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="Y21" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="Y23" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N24" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="Y24" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="M25" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N25" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="Y25" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="M26" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N26" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="Y26" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="M27" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N27" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M32" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="Y16" r:id="rId58" xr:uid="{EC25DFAD-6C70-46EA-BB56-5E3B1102F497}"/>
+    <hyperlink ref="M31" r:id="rId59" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
+    <hyperlink ref="N31" r:id="rId60" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
+    <hyperlink ref="N29" r:id="rId61" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
+    <hyperlink ref="M28" r:id="rId62" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
+    <hyperlink ref="N28" r:id="rId63" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
+    <hyperlink ref="N30" r:id="rId64" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805B5AB8-610E-4875-BE5B-65AEF473439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A63E4A1-7C56-4C11-9DE1-19B06AF71B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="清冊一覽" sheetId="7" r:id="rId1"/>
+    <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
+    <sheet name="活動節目" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="601">
   <si>
     <t>地圖編號</t>
   </si>
@@ -96,9 +97,6 @@
     <t>作品英文簡介</t>
   </si>
   <si>
-    <t>影像連結</t>
-  </si>
-  <si>
     <t>圖片資料夾</t>
   </si>
   <si>
@@ -112,9 +110,6 @@
   </si>
   <si>
     <t>吳宜曄</t>
-  </si>
-  <si>
-    <t>WU I-YEH</t>
   </si>
   <si>
     <t>台灣</t>
@@ -164,9 +159,6 @@
     <t>無邊製造-林俊遑 / 黃紀虹 / 鄭子芸</t>
   </si>
   <si>
-    <t>No Side Here - LIN Chun-Huang / HUANG Chi-Hung / JHENG Zih-Yun</t>
-  </si>
-  <si>
     <t>無邊製造由林俊遑、黃紀虹與鄭子芸組成，創作專注於聲光裝置與體感互動，從日常中不易被察覺的訊息出發，探索環境、科技與人文之間的連結，並透過藝術實踐建立觀眾與空間的對話。作品曾獲全國美展新媒體藝術類首獎、新北市美展科技藝術類首獎等肯定，並參與 Ars Electronica、ISEA、RECTO VRso、FUTURE VISION LAB 等國際展演與研究平台。</t>
   </si>
   <si>
@@ -206,9 +198,6 @@
     <t>Statement Languages convey meanings through diverse words and phrases. In the digital age, however keywords have altered linguistic structures. Large databases have been reduced to words through layers of algorithms, rendering some words irrelevant and unnecessary to exist in the “keyword era.” Words that make sentences meaningful are disappearing. Repeated computing simplifies information and changes languages, and we are becoming human flotsam with our utter indifference.</t>
   </si>
   <si>
-    <t>https://youtu.be/XrW1aR4HQR0?si=hLnbwYJbFz7L_PlH</t>
-  </si>
-  <si>
     <t>03</t>
   </si>
   <si>
@@ -216,9 +205,6 @@
   </si>
   <si>
     <t>鄭先喻</t>
-  </si>
-  <si>
-    <t>HsienYu Cheng</t>
   </si>
   <si>
     <t>鄭先喻1984年生於高雄，現居臺北，身兼藝術家與軟體開發者。創作涵蓋軟體、電子設備與實驗性生物電子裝置，關注人類行為、情感、軟體及人機關係，並以幽默方式回應科技社會與環境議題。曾獲台北數位藝術獎首獎、高雄獎新媒體藝術首獎、台新藝術獎視覺藝術獎及 S+T+ARTS 榮譽提名，作品於臺灣、亞洲與歐洲多地展出。</t>
@@ -349,9 +335,6 @@
     <t>main-06</t>
   </si>
   <si>
-    <t>C-LAB’s Future Vision Lab</t>
-  </si>
-  <si>
     <t>https://clab.org.tw/unit/future-vision-lab/</t>
   </si>
   <si>
@@ -428,9 +411,6 @@
   </si>
   <si>
     <t>何芯源</t>
-  </si>
-  <si>
-    <t>Hsin-Yuan Ho</t>
   </si>
   <si>
     <t>何芯源的創作以新媒體、互動裝置與跨域實踐為主，關注科技媒介如何改變人的感知、身體經驗與環境關係。她常從日常觀察與個人感受出發，結合數位技術、空間裝置與參與式互動，將抽象的感知狀態轉化為可被觀看與體驗的形式。作品與研究曾參與科技藝術、跨域創作及相關展演計畫，持續在藝術與技術交會的脈絡中發展。</t>
@@ -494,9 +474,6 @@
     <t>The reverberations of rocks and silicon wafers scraping and colliding echo through the space, serving as murmured whispers within their mutual dreams. The work seeks to construct a recursive dialogue between materials, entangling matter between ancient nature and contemporary technology. Does processed silicon ever dream of its chaotic origins? Or did rocks, tens of millions of years ago, already foresee becoming computational substrates? The noise and resonance generated through the mutual interpretation and misreading between materials accumulate and take shape in space, generating a dream belonging purely to matter itself.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/19ydHg35yHbzjiYRbXFdiCg8YsLtRCEIM/view?usp=drive_link 、 https://drive.google.com/file/d/118It20SgZ5u1doug79jlyLPdWwQnHtBe/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>09</t>
   </si>
   <si>
@@ -543,9 +520,6 @@
     <t>Belugas’ Sphere revisits Beluga Pod (2008) as a new ecology of autonomous robotic entities. Each Beluga seeks light and moves in response to its environment. As light intensity changes, their activity and collective behavior evolve, producing shifting formations, flocking, and song rather than fixed choreography. Visitors may influence these behaviors by introducing light, but participation is not required: the Belugas continue to act on their own. First imagined nearly two decades ago, they now resemble early inhabitants of an emerging machine economy, organizing around energy, proximity, and environmental conditions. The installation looks backward and forward at once, returning to an earlier vision of autonomous machines in a present increasingly shaped by agentic systems.</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=XTPzJ-lzobo</t>
-  </si>
-  <si>
     <t>主展場戶外</t>
   </si>
   <si>
@@ -553,9 +527,6 @@
   </si>
   <si>
     <t>林書瑜</t>
-  </si>
-  <si>
-    <t>ShuYu-Lin</t>
   </si>
   <si>
     <t>林書瑜1988年生於宜蘭，現任國立臺北藝術大學新媒體藝術學系講師，居住、工作於臺北。創作從自然與科學現象的觀察出發，運用互動、機械動力、光影與空間裝置轉譯個人經驗與感知，詩意呈現人在當代社會中的狀態與處境。作品曾獲台北數位藝術獎首獎、台南新藝獎等肯定，並參與關渡光藝術節、月津港燈節等展演與策展計畫。</t>
@@ -632,9 +603,6 @@
 As viewers enter the work, their bodies intertwine with the arcs of light; shadows stretch and contract with the rhythm, and contours rise and fall in response. These transient yet vivid moments evoke the sensation of gazing at moonlight, while also reflecting the human condition within the flux of environment and time. Through the emergence and fading of light, the work invites reflection on memory and existence—reminding us that even in a time of constant change, one may still grasp fragments of truth and continuity.</t>
   </si>
   <si>
-    <t>https://youtu.be/ygRaaQP0NXk?si=10N-19-A1487ZL7d</t>
-  </si>
-  <si>
     <t>outdoor-02</t>
   </si>
   <si>
@@ -687,9 +655,6 @@
     <t>Solar Pink Pong is a hybrid of a street and video game. Players of this game can interact with an animated pink sunlight reflection on the street using their bodies and shadows. The device that makes this game possible works autonomously and completely off the grid. Solar Pink Pong aims at pushing the boundaries of video game culture and technology outside of the living room changing the way humans interact with outdoor environments and see daylight through the lens of technology.</t>
   </si>
   <si>
-    <t>https://vimeo.com/138126896</t>
-  </si>
-  <si>
     <t>街區</t>
   </si>
   <si>
@@ -699,9 +664,6 @@
     <t>謝佩庭</t>
   </si>
   <si>
-    <t>HSIEH PEI TING</t>
-  </si>
-  <si>
     <t>謝佩庭的創作探討科技觀看系統與人類存在、記憶及身分交會所形成的痕跡與張力，關注影像技術、機器視覺與數位基礎設施如何重塑主體性、精神性與崇高感。她透過錄像、裝置與數位媒介，思考科技時代中的觀看權力與存在命題。曾入選2023年高雄獎，作品於奧地利林茲電子藝術節、高雄市立美術館、金馬賓館當代美術館等場域展出。</t>
   </si>
   <si>
@@ -738,16 +700,10 @@
     <t>The work draws on global streetscapes captured by Google Street View. By reconfiguring the focus and rhythm of viewing, it brings human figures that happen to enter the frame—otherwise nearly indistinguishable from visual noise—to the center of attention. The camera has no intention of looking at anyone, yet the AI system mechanically detects faces only to obscure them, rendering individuals anonymous even as their presence remains precisely geolocated and publicly exposed online, entirely beyond their control. Given Street View’s global reach, the authority conferred by geolocation, and the platform’s searchability, these ostensibly neutral records may be reread through personal memory, becoming sites of emotional projection and remembrance. The work asks: How do these spectral images reflect the conditions of existence in the technological age and become intimately entwined with contemporary experiences of memory, identity, and emotion?</t>
   </si>
   <si>
-    <t>https://youtu.be/OvTRXUJFpq0%20</t>
-  </si>
-  <si>
     <t>district-02</t>
   </si>
   <si>
     <t>陳芷渝</t>
-  </si>
-  <si>
-    <t>Chih-Yu Chen</t>
   </si>
   <si>
     <t>陳芷渝是臺灣科技藝術與生成藝術家，運用演算法及其持續變化的特性捕捉日常經驗，並透過跨媒介實驗探索新的藝術形式。創作涵蓋生成藝術、互動設計與機器學習，近期以程式碼描摹現實與意象之間的游移邊界。除個人創作外，她亦投入生成藝術的國際交流與教育推廣，曾於臺灣、日本、韓國、歐洲及北美展出，並發起 Creative Code Commons 等交流計畫。</t>
@@ -820,16 +776,10 @@
 This process demonstrates the collaboration between the artist and generative systems, the surrender of aesthetic and authorial rights. Each brushstroke is a dialogue between artistic intent and digital intelligence, challenging the essence of creation and exploring the role and potential of artificial intelligence in art.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Dhok3VN7KAiCEjjIdWa8hEC6QE7sIfd3/view?usp=sharing</t>
-  </si>
-  <si>
     <t>district-03</t>
   </si>
   <si>
     <t>樊卓鏗</t>
-  </si>
-  <si>
-    <t>Fan Cheuk Hang</t>
   </si>
   <si>
     <t>香港</t>
@@ -872,15 +822,9 @@
     <t>Over four years in Taiwan, my dialogues evoke “waat6 ngaa4”—like a stripped screw idling between languages. Though Hong Kong and Taiwan share Traditional Chinese, a profound referential slippage occurs. In NLP, “zi6 goeng6” collapses into one vector, yet misaligns culturally: Taiwan's memory of the term eludes Hong Kongers. Conversely, guava reveals divergent signifiers for an identical signified. My video deconstructs these symbols, merging landforms to probe this semantic void.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1-LQRlGfzne0_J4nhxIvUTFjCue4MyWAs/view?usp=sharing</t>
-  </si>
-  <si>
     <t>陳政維</t>
   </si>
   <si>
-    <t>Cheng-Wei Chen</t>
-  </si>
-  <si>
     <t>陳政維為臺灣新媒體藝術創作者，畢業於國立臺北藝術大學新媒體藝術學系，亦為藝術團隊 2ENTER 貳進成員。創作以影像裝置、動畫、網路資訊與遊戲引擎為主要媒介，關注即時網路資料、虛擬生態與數位世界的生成關係。他透過程式與視覺系統將持續流動的資料轉化為作品，探索網路環境如何形成新的觀看經驗與虛擬空間。團隊作品曾獲臺南新藝獎、北藝當代創作獎等肯定。</t>
   </si>
   <si>
@@ -911,9 +855,6 @@
     <t>郭子耘</t>
   </si>
   <si>
-    <t>KUO TZU YUNG</t>
-  </si>
-  <si>
     <t>郭子耘1998年生於臺北，現就讀國立臺北藝術大學新媒體藝術學系研究所。創作以動力裝置與影像為主要媒材，同時參與跨域表演與科技劇場，從生命經驗、情感、記憶與日常觀察出發，探索觀看過程中產生的矛盾與感受。作品曾參與 Ars Electronica、關渡光藝術節、月津港燈節與白晝之夜等展演，並曾入圍桃源美展、桃園科技表演藝術獎及宜蘭獎。</t>
   </si>
   <si>
@@ -947,9 +888,6 @@
     <t>Can we trust what we see? How confident are we in discerning reality? Should we continuously seek the truth? How much of the flashing scenes remain in our memory? It's difficult for us to distinguish between reality and memory. Images are constantly cropped, cut, compressed, and distorted, giving rise to unique and peculiar landscapes. Memories operate similarly, incomplete yet imbued with deeper meanings. Through the lens, we create intricately layered, enigmatic, and beautiful images.</t>
   </si>
   <si>
-    <t>https://youtu.be/JM4bneQTeUM</t>
-  </si>
-  <si>
     <t>district-04_2</t>
   </si>
   <si>
@@ -959,9 +897,6 @@
     <t>沈宇軒</t>
   </si>
   <si>
-    <t>Yu-Hsuan Shen</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/crazy.curly17</t>
   </si>
   <si>
@@ -987,9 +922,6 @@
   </si>
   <si>
     <t>超級浪-洪譽豪 / 林思瑩 / 邱杰森 / 莫珊嵐 / 賴佩君</t>
-  </si>
-  <si>
-    <t>Hyper Wave</t>
   </si>
   <si>
     <t>台灣 / 法國</t>
@@ -1129,9 +1061,6 @@
     <t>陳品蓁</t>
   </si>
   <si>
-    <t>CHEN PIN JHEN</t>
-  </si>
-  <si>
     <t>陳品蓁現就讀國立臺北藝術大學新媒體藝術學系，創作媒介涵蓋動畫、網頁互動、遊戲引擎與延展實境。她關注科技依賴、社群疲勞等當代心理狀態，以情境建構與遊戲化機制將日常觀察轉化為可參與的互動經驗。透過敘事導向的體驗設計，引導觀眾在摸索、選擇與參與過程中重新審視人與科技環境的關係。曾入選 NTT+ LAB X 青年創作工作室延展實境組，持續發展跨媒介創作。</t>
   </si>
   <si>
@@ -1175,16 +1104,10 @@
     <t>This work explores the mutual influence between artificial intelligence and humans through a fictional world and gamified interaction. Inspired by “Soma,” the pleasure-inducing drug in *Brave New World*, it draws a parallel to generative AI increasingly embedded in everyday life. Amid information overload and “brain rot,” our capacity to judge, understand, and act may gradually become unbalanced. The audience is invited to reverse roles and play as an AI, conversing with a user to influence or manipulate their thoughts and actions toward different outcomes. Through this role reversal, the work examines power, dependence, and the boundaries of understanding between humans and technology.</t>
   </si>
   <si>
-    <t>https://youtu.be/nRK3TdYaKGM</t>
-  </si>
-  <si>
     <t>district-10</t>
   </si>
   <si>
     <t>簡嘉誼</t>
-  </si>
-  <si>
-    <t>CHIEN CHIA YI</t>
   </si>
   <si>
     <t>簡嘉誼為視覺設計與藝術創作者，現就讀視覺藝術研究所。創作關注個體感知、身體經驗與外在環境之間的關係，嘗試將難以直接觀看的情緒、意識與感知狀態轉化為具體視覺形式。她以視覺設計、動態影像、裝置與複合媒材進行跨媒介實驗，在設計語言與藝術表達之間建立連結。作品曾獲德國紅點品牌暨傳達設計大獎、美國 Communication Arts 及 Applied Arts 等設計獎項肯定。</t>
@@ -1230,9 +1153,6 @@
     <t>楊子毅</t>
   </si>
   <si>
-    <t>Tzu-I Yang</t>
-  </si>
-  <si>
     <t>楊子毅1989年生於臺北，為科技藝術創作者，現就讀國立臺北藝術大學新媒體藝術研究所，亦為數位跨域藝術組合「互跪合作社」主創成員。具電機資訊與機器學習工程背景，並受女性主義與 STS 影響，創作關注科技環境中的權力、壓迫與社會關係。他跨足程式、互動媒體、舞蹈、編舞與文字創作，透過技術實作回應當代生活受到數位科技深刻影響的處境。</t>
   </si>
   <si>
@@ -1265,18 +1185,12 @@
 Humans often imagine gods in their own image, while AI is also trained using humans as its reference. In turn, both gods and AI become objects of human faith, forming a recurring, recursive loop. As a result, the definitions and boundaries between the three gradually blur. What we worship seems at once to be something beyond humanity—and, at the same time, a reflection of ourselves.</t>
   </si>
   <si>
-    <t>https://youtube.com/shorts/xUBnyI_IK8M</t>
-  </si>
-  <si>
     <t>district-12</t>
   </si>
   <si>
     <t>鄭芳宜</t>
   </si>
   <si>
-    <t>Fang-Yi Cheng</t>
-  </si>
-  <si>
     <t>https://www.chengfangyi.com/</t>
   </si>
   <si>
@@ -1304,9 +1218,6 @@
     <t>黃姿婷</t>
   </si>
   <si>
-    <t>Huang Tzu Ting</t>
-  </si>
-  <si>
     <t>黃姿婷以錄像與裝置為主要創作媒介，關注語言、影像與技術如何形塑感知、記憶與認知。作品常從語境轉譯與錯置出發，結合多頻道影像、聲音、身體與人工智慧，探索人與科技、真實與虛擬、歷史與當代之間的邊界。她將語言視為文化、權力與情感的載體，透過人機對話、機械翻譯與歷史影像重組，呈現意義在不同觀看位置中的生成與偏移。</t>
   </si>
   <si>
@@ -1346,10 +1257,6 @@
     <t>Language serves as the starting point of the work, exploring how AI intervenes in human thought, emotion, and perception. AI speaks through human language, while humans communicate through code. Keyboard sounds, the dancer’s body, and multi-channel video together form an intimate dialogue between human and machine. Through sound, body, and language, the work presents a body rewritten by code under the gaze of AI, alongside a virtual world generated from data through human imagination, reconsidering the shifting boundaries between humans and AI, technology and humanity, and the real and the virtual.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/150U2efvgK8mYunYcL4LKPXYRh2HY7Y4d/view?u
-sp=sharing</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -1357,9 +1264,6 @@
   </si>
   <si>
     <t>余柏霆</t>
-  </si>
-  <si>
-    <t>YU PO-TING</t>
   </si>
   <si>
     <t>余柏霆現就讀國立臺北藝術大學新媒體藝術學系，創作與研究關注影像、檔案、力與自然物之間的關係，試圖在理性建構的系統與脈絡中尋找詩性介入的可能。他以感知觀察為出發點，結合動態影像、數位模擬、自然現成物與空間裝置，建立介於技術系統與物質經驗之間的美學地景。作品曾獲新媒體卓越獎、大墩美展等肯定，並參與 C-LAB FUTURE VISION LAB 等展演。</t>
@@ -1397,9 +1301,6 @@
     <t>When I encountered nineteenth-century British records of explorations in northern Taiwan, I became interested in how foreign language and measurement transformed the land into an object of observation and possession. Retracing these historical routes, I collected natural found objects corresponding to locations described in the archives.
 By projecting the archival texts back onto the surfaces of stones, the work creates a dislocation between language and landscape. The projection resembles an act of occupation, yet the stones’ coarse textures distort and fragment the descriptions, producing friction between text and land.
 The video adopts the perspective of a contemporary geologist, examining the stones through precise instruments and seemingly objective methods. By juxtaposing colonial records with contemporary scientific measurement, the work reflects on the intimate relationship between technologies of observation, territorial knowledge, and colonial logic.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1n8bIwTVwjCnG63VbpJw7fkNXDTuxtC6/view?usp= drive_link</t>
   </si>
   <si>
     <t>開幕表演</t>
@@ -1692,15 +1593,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1sqmmYXyaynXnnQO-ncI7cicJtZHI21bf/view?usp=sharing</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>CRT television, 3D-printed sculpture</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yen-Chi Chen x Huan Chou</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -12570,10 +12463,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Fluid Noise</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>performance-01_2</t>
   </si>
   <si>
@@ -13296,14 +13185,6 @@
   </si>
   <si>
     <t>In contemporary society, many situations involve the surrender of biometric data. This work draws inspiration from the moment when individuals relinquish control over such information. As a camera equipped with recognition technology automatically moves up and down to align with a person’s face, it is no longer merely a tool for documentation, but becomes a technological interface that actively identifies, locates, and observes the individual. In this process, the individual loses their subjectivity and is reduced to an object waiting to be scanned, measured, and archived. The discomfort of having one’s digital identity forcibly stripped away, or even consumed by a digital profiling system, lies at the core of this work.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=5x4J4qsCXds</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1XsQngYskmGOHsx2mkjLtDVo3p2hc3zHY?usp=sharing</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -14116,10 +13997,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Cheng-Ru Wu ( P B )</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -14241,6 +14118,1026 @@
       </rPr>
       <t>再現，並透過音像演出詮釋藝術家在臺灣生活的觀察與狀態。</t>
     </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-Yeh Wu</t>
+  </si>
+  <si>
+    <t>No Side Here — Chun-Huang Lin / Chi-Hung Huang / Zih-Yun Jheng</t>
+  </si>
+  <si>
+    <t>Fluid Noise</t>
+  </si>
+  <si>
+    <t>Cheng-Ru Wu (P B)</t>
+  </si>
+  <si>
+    <t>Yen-Chi Chen × Huan Chou</t>
+  </si>
+  <si>
+    <t>Shu-Yu Lin</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>C-LAB’s Future Vision Lab</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yu-Hsuan Shen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin-Jhen Chen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fang-Yi Cheng</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tzu-Yung Kuo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pei-Ting Hsieh</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tzu-I Yang</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chia-Yi Chien</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Po-Ting Yu</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cheuk Hang Fan</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chih-Yu Chen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hsien-Yu Cheng</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hsin-Yuan Ho</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hyper Wave</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cheng-Wei Chen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tzu-Ting Huang</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天使生活館一樓大廳</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15:30-16:40</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Po-Chi Su
+Artist: Cheng-Wei Chen, Tzu-Ting Huang, Bety Krňanská
+Artist Group: Hyper Wave</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與談人：蘇珀琪
+藝術家：陳政維、黃姿婷、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bety Krňanská
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術團體：超級浪</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家講座</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14:00-15:10</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Chih-Yung Chiu
+Artist: Hsien-Yu Cheng, Hsin-Yuan Ho
+Artist Group: No Side Here, Assocreation</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與談人：邱誌勇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：鄭先喻、何芯源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體：無邊製造、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Assocreation</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15:30-16:40</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Shih-Yu Hsu
+Artist: Tzu-I Yang, Chia-Yi Chien, Po-Ting Yu, Cheuk Hang Fan, Chih-Yu Chen</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與談人：徐詩雨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：楊子毅、簡嘉誼、余柏霆、樊卓鏗、陳芷渝</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14:00-15:10</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Duo Chao
+Artist: Yu-Hsuan Shen, Pin-Jhen Chen, Fang-Yi Cheng, Tzu-Yung Kuo, Pei-Ting Hsieh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與談人：趙鐸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：沈宇軒、陳品蓁、鄭芳宜、郭子耘、謝佩庭</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15:30-16:40</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Dar-Kuen Wu
+Artist: Stefan Tiefengraber, Jed Berk, Shu-Yu Lin
+Artist Group: C-LAB’s Future Vision Lab</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與談人：吳達坤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stefan Tiefengraber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jed Berk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、林書瑜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術團體：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">C-LAB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未來視覺實驗室</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14:00-15:10</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panelist: Jau-Lan Guo
+Artist: Dries Depoorter, Verena Friedrich, I-Yeh Wu</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>與談人：郭紹蘭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dries Depoorter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Verena Friedrich</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、吳宜曄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Riso </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>印刷需將彩色圖分色、製版，再逐色疊印完成。工作坊將用程式拍攝人像、去背並拆成三色網點，模擬半調顆粒與隨機錯位，探索機器如何辨識人物與影像。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10:00-12:00</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist: Chih-Yu Chen</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：陳芷渝</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>How Machines See You: Body Silhouette Printing Workshop</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>機器怎麼看你：身體剪影印刷工作坊</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>工作坊</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hydra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是一套在瀏覽器中執行的視覺即時編碼工具，受到早期的類比影像合成器啟發，能透過簡單的語法組合，產生豐富的視覺效果。本工作坊將從基本圖形、動態、疊合到調變，帶領學員認識</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Hydra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的撰寫邏輯，運用有限的元素，創造多變的視覺。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artist: Tung-Yu Liu</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藝術家：劉東昱</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>From Scratch: Hydra Live Coding Workshop</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>From Scratch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hydra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>影像編碼工作坊</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖片來源</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡介英文</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡介中文</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>地點</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動英文名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動中文名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>workshop-01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>workshop-02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>talking-01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>talking-02</t>
+  </si>
+  <si>
+    <t>talking-03</t>
+  </si>
+  <si>
+    <t>talking-04</t>
+  </si>
+  <si>
+    <t>talking-05</t>
+  </si>
+  <si>
+    <t>talking-06</t>
+  </si>
+  <si>
+    <t>表演者/講者英文名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>表演者/講者中文名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（日）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10:00-12:00</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10/31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（六）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19:00-22:00</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>performance</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>音像之夜</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audiovisual Performance</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北典藏植物園－主展場</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -14248,7 +15145,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14265,16 +15165,19 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -14288,6 +15191,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -14353,12 +15257,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="136"/>
     </font>
     <font>
@@ -14367,6 +15265,43 @@
       <name val="細明體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -14386,11 +15321,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -14430,9 +15366,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -14461,21 +15394,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="2" xr:uid="{B05CBEFA-BE0D-4672-A9D9-4BA313F68CEC}"/>
     <cellStyle name="超連結" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -14686,7 +15642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
@@ -14701,11 +15657,10 @@
     <col min="17" max="17" width="16.42578125" customWidth="1"/>
     <col min="18" max="22" width="11.5703125" customWidth="1"/>
     <col min="23" max="24" width="16.140625" customWidth="1"/>
-    <col min="25" max="25" width="11.5703125" customWidth="1"/>
-    <col min="26" max="26" width="18.85546875" customWidth="1"/>
+    <col min="25" max="25" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="25.5">
+    <row r="1" spans="1:26" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -14715,8 +15670,8 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>532</v>
+      <c r="D1" s="22" t="s">
+        <v>496</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -14781,375 +15736,366 @@
       <c r="Y1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:27">
-      <c r="A2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="K2" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>31</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R2" s="13">
         <v>2024</v>
       </c>
       <c r="S2" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="V2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="W2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="16" t="s">
+      <c r="X2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="Y2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="6"/>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="16" t="s">
+      <c r="B3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA2" s="6"/>
-    </row>
-    <row r="3" spans="1:27">
-      <c r="A3" s="12" t="s">
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="K3" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="O3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="M3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="Q3" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>52</v>
       </c>
       <c r="R3" s="13">
         <v>2024</v>
       </c>
       <c r="S3" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="W3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="Y3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="B4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="D4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="Y3" s="17" t="s">
+      <c r="F4" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="Z3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA3" s="6"/>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="12" t="s">
+      <c r="J4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="K4" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="M4" s="15" t="s">
         <v>61</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>484</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>66</v>
       </c>
       <c r="N4" s="13"/>
       <c r="O4" s="13" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="R4" s="13">
         <v>2022</v>
       </c>
       <c r="S4" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="X4" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z4" s="6"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="D5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="U4" s="16" t="s">
+      <c r="G5" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="W4" s="16" t="s">
-        <v>486</v>
-      </c>
-      <c r="X4" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="6"/>
+      <c r="I5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="U5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="V5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="W5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="X5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z5" s="6"/>
     </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P5" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="T5" s="16" t="s">
+    <row r="6" spans="1:26">
+      <c r="A6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="U5" s="16" t="s">
+      <c r="B6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="D6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="W5" s="16" t="s">
+      <c r="G6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="X5" s="16" t="s">
+      <c r="H6" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA5" s="6"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="12" t="s">
+      <c r="I6" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="N6" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="Q6" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>440</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
@@ -15157,1648 +16103,1597 @@
       <c r="S6" s="16"/>
       <c r="T6" s="16"/>
       <c r="U6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="W6" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="6"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="N7" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="W6" s="25" t="s">
-        <v>538</v>
-      </c>
-      <c r="X6" s="16" t="s">
+      <c r="O7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA6" s="6"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="12" t="s">
+      <c r="P7" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="Q7" s="13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
-      <c r="U7" s="26" t="s">
-        <v>536</v>
+      <c r="U7" s="25" t="s">
+        <v>500</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="6"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="W7" s="25" t="s">
-        <v>535</v>
-      </c>
-      <c r="X7" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA7" s="6"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="12" t="s">
+      <c r="J8" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="K8" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="N8" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="O8" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="P8" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="R8" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="S8" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="M8" s="15" t="s">
+      <c r="T8" s="16" t="s">
         <v>120</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="R8" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="S8" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="T8" s="16" t="s">
-        <v>126</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="X8" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z8" s="6"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="X8" s="16" t="s">
+      <c r="K9" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA8" s="6"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="12" t="s">
+      <c r="L9" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="M9" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="N9" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="O9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="14" t="s">
+      <c r="P9" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="Q9" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>141</v>
       </c>
       <c r="R9" s="13">
         <v>2026</v>
       </c>
       <c r="S9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="U9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="V9" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="W9" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y9" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z9" s="6"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="D10" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="G10" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="H10" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="J10" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="Y9" s="17" t="s">
+      <c r="K10" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="Z9" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA9" s="6"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="12" t="s">
+      <c r="N10" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="O10" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="P10" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>159</v>
-      </c>
       <c r="Q10" s="13" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R10" s="13">
         <v>2026</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="U10" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="V10" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="W10" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="X10" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z10" s="6"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="V10" s="16" t="s">
+      <c r="K11" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="L11" s="14" t="s">
         <v>162</v>
-      </c>
-      <c r="X10" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y10" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z10" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA10" s="6"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>172</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="15" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="R11" s="13">
         <v>2025</v>
       </c>
       <c r="S11" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="T11" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="U11" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="V11" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="W11" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="X11" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y11" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z11" s="6"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="J12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="K12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="L12" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="M12" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="X11" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y11" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z11" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA11" s="6"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>525</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>192</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="R12" s="13">
         <v>2013</v>
       </c>
       <c r="S12" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="V12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="W12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="X12" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y12" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z12" s="6"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="O13" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="P13" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="Q13" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="X12" s="16" t="s">
+      <c r="R13" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="Y12" s="17" t="s">
+      <c r="S13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T13" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="U13" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="Z12" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA12" s="6"/>
+      <c r="V13" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="W13" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="X13" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z13" s="6"/>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F13" s="13" t="s">
+    <row r="14" spans="1:26">
+      <c r="A14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="14" t="s">
+      <c r="D14" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="F14" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="M13" s="15" t="s">
+      <c r="J14" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="K14" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="L14" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="M14" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="N14" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="R13" s="18" t="s">
+      <c r="O14" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="S13" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="T13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="U13" s="16" t="s">
+      <c r="P14" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="Q14" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="W13" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="X13" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y13" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z13" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA13" s="6"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>229</v>
       </c>
       <c r="R14" s="13">
         <v>2024</v>
       </c>
       <c r="S14" s="16" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="T14" s="16" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="W14" s="16" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="X14" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y14" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z14" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA14" s="6"/>
+        <v>220</v>
+      </c>
+      <c r="Y14" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z14" s="6"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:26">
       <c r="A15" s="12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>239</v>
+        <v>537</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="15" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="R15" s="13">
         <v>2025</v>
       </c>
       <c r="S15" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="W15" s="16" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="X15" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y15" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z15" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y15" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z15" s="6"/>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="AA15" s="6"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>256</v>
-      </c>
       <c r="K16" s="14" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="R16" s="13">
         <v>2026</v>
       </c>
       <c r="S16" s="16" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
       <c r="W16" s="16" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="X16" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="Y16" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="Z16" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA16" s="6"/>
+        <v>421</v>
+      </c>
+      <c r="Y16" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z16" s="6"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:26">
       <c r="A17" s="12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>265</v>
+        <v>532</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="R17" s="13">
         <v>2025</v>
       </c>
       <c r="S17" s="16" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="V17" s="16" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="W17" s="16" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="X17" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="Y17" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="Z17" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA17" s="6"/>
+        <v>256</v>
+      </c>
+      <c r="Y17" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z17" s="6"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:26">
       <c r="A18" s="12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>281</v>
+        <v>529</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>541</v>
+        <v>29</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>505</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>543</v>
+        <v>506</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="15" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="R18" s="13">
         <v>2026</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="U18" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="V18" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="W18" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="X18" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="Y18" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z18" s="6"/>
+    </row>
+    <row r="19" spans="1:26" s="5" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="V18" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="W18" s="26" t="s">
-        <v>545</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="Y18" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z18" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="AA18" s="6"/>
-    </row>
-    <row r="19" spans="1:27" s="5" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>309</v>
-      </c>
       <c r="E19" s="13" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>291</v>
+        <v>541</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>297</v>
+        <v>270</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>274</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="R19" s="13">
         <v>2026</v>
       </c>
       <c r="S19" s="16" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="W19" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="X19" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="AA19" s="7"/>
+        <v>283</v>
+      </c>
+      <c r="W19" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="X19" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z19" s="7"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:26">
       <c r="A20" s="12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="R20" s="13">
         <v>2025</v>
       </c>
       <c r="S20" s="16" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="W20" s="16" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="X20" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA20" s="6"/>
+        <v>300</v>
+      </c>
+      <c r="Y20" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z20" s="6"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:26">
       <c r="A21" s="12" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>327</v>
+        <v>530</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="R21" s="13">
         <v>2025</v>
       </c>
       <c r="S21" s="16" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="W21" s="16" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="X21" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="Y21" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z21" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA21" s="6"/>
+        <v>317</v>
+      </c>
+      <c r="Y21" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z21" s="6"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:26">
       <c r="A22" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>345</v>
+        <v>535</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="W22" s="16" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="X22" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA22" s="6"/>
+        <v>330</v>
+      </c>
+      <c r="Y22" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z22" s="6"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:26">
       <c r="A23" s="12" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>359</v>
+        <v>534</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="15" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="R23" s="13">
         <v>2026</v>
       </c>
       <c r="S23" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="W23" s="16" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
       <c r="X23" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="Y23" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="Z23" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="AA23" s="6"/>
+        <v>342</v>
+      </c>
+      <c r="Y23" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z23" s="6"/>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:26">
       <c r="A24" s="12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>373</v>
+        <v>531</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>553</v>
+        <v>29</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>515</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="K24" s="24" t="s">
-        <v>551</v>
+        <v>516</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>513</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="R24" s="13">
         <v>2026</v>
       </c>
       <c r="S24" s="16" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="W24" s="29" t="s">
-        <v>550</v>
+        <v>351</v>
+      </c>
+      <c r="W24" s="27" t="s">
+        <v>512</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>549</v>
-      </c>
-      <c r="Y24" s="28" t="s">
-        <v>548</v>
-      </c>
-      <c r="Z24" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AA24" s="6"/>
+        <v>511</v>
+      </c>
+      <c r="Y24" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z24" s="6"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:26">
       <c r="A25" s="12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>383</v>
+        <v>543</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="W25" s="16" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="X25" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="Y25" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z25" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="AA25" s="6"/>
+        <v>366</v>
+      </c>
+      <c r="Y25" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z25" s="6"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:26">
       <c r="A26" s="12" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>401</v>
+        <v>536</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
       </c>
       <c r="S26" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="W26" s="16" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="X26" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="Y26" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="Z26" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="AA26" s="6"/>
+        <v>380</v>
+      </c>
+      <c r="Y26" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z26" s="6"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:26">
       <c r="A27" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -16809,349 +17704,344 @@
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="AA27" s="6"/>
+      <c r="Y27" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="Z27" s="6"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:26">
       <c r="A28" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>555</v>
+        <v>497</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>517</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>557</v>
+        <v>29</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>518</v>
       </c>
       <c r="J28" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="P28" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="N28" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>507</v>
-      </c>
       <c r="Q28" s="13" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="R28" s="13">
         <v>2026</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="T28" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="V28" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="W28" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="X28" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="U28" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="V28" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="W28" s="30" t="s">
-        <v>560</v>
-      </c>
-      <c r="X28" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="AA28" s="6"/>
+      <c r="Y28" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z28" s="6"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:26">
       <c r="A29" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>418</v>
+        <v>497</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="T29" s="13" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13"/>
       <c r="W29" s="13" t="s">
-        <v>511</v>
+        <v>476</v>
       </c>
       <c r="X29" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="AA29" s="6"/>
+        <v>434</v>
+      </c>
+      <c r="Y29" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="Z29" s="6"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:26">
       <c r="A30" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>512</v>
+        <v>477</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="22" t="s">
-        <v>480</v>
+        <v>440</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="21" t="s">
+        <v>445</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>418</v>
+        <v>497</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="U30" s="13"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="13"/>
-      <c r="Z30" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA30" s="6"/>
+      <c r="Y30" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z30" s="6"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:26">
       <c r="A31" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>517</v>
+        <v>482</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>461</v>
+        <v>426</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>418</v>
+        <v>497</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="Q31" s="13" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="13" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="AA31" s="6"/>
+        <v>428</v>
+      </c>
+      <c r="Y31" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="Z31" s="6"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:26">
       <c r="A32" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>428</v>
+        <v>395</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -17159,26 +18049,25 @@
         <v>2026</v>
       </c>
       <c r="S32" s="13" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="T32" s="13" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="X32" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="AA32" s="6"/>
+        <v>404</v>
+      </c>
+      <c r="Y32" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z32" s="6"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:25">
       <c r="A33" s="3"/>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
@@ -17187,9 +18076,9 @@
       <c r="F33" s="4"/>
       <c r="H33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="Z33" s="4"/>
+      <c r="Y33" s="4"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:25">
       <c r="A34" s="3"/>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
@@ -17198,9 +18087,9 @@
       <c r="F34" s="4"/>
       <c r="H34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="Z34" s="4"/>
+      <c r="Y34" s="4"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:25">
       <c r="A35" s="3"/>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
@@ -17209,7 +18098,7 @@
       <c r="F35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:25">
       <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
@@ -17218,7 +18107,7 @@
       <c r="F36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:25">
       <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
@@ -17233,69 +18122,401 @@
     <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="N3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="Y3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="M6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="M8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Y9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="M10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="Y10" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="Y11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="M12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="Y12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="M13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N13" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="Y13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="M14" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N14" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="Y14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="N15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="Y15" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="M17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N17" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="Y17" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="N18" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="M19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N19" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="M20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N20" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="M21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N21" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="Y21" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="N23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="Y23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="M24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="M25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="N25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="Y25" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="M26" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="N26" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="Y26" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="M27" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N27" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="M32" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="Y16" r:id="rId56" xr:uid="{EC25DFAD-6C70-46EA-BB56-5E3B1102F497}"/>
-    <hyperlink ref="M31" r:id="rId57" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
-    <hyperlink ref="N31" r:id="rId58" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
-    <hyperlink ref="N29" r:id="rId59" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
-    <hyperlink ref="M28" r:id="rId60" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
-    <hyperlink ref="N28" r:id="rId61" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
-    <hyperlink ref="N30" r:id="rId62" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
-    <hyperlink ref="Y18" r:id="rId63" xr:uid="{0544507E-4606-4E6B-883A-497D16B2D146}"/>
-    <hyperlink ref="Y24" r:id="rId64" xr:uid="{D1CE81CE-EFDD-4285-9DAB-C96845705C7F}"/>
+    <hyperlink ref="M4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M7" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M8" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M10" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N10" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N11" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M12" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N13" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M14" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N14" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N15" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M17" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N17" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N18" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M19" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N19" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M20" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N20" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N23" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M24" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N24" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N25" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M26" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N26" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M27" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N27" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M32" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M31" r:id="rId43" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
+    <hyperlink ref="N31" r:id="rId44" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
+    <hyperlink ref="N29" r:id="rId45" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
+    <hyperlink ref="M28" r:id="rId46" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
+    <hyperlink ref="N28" r:id="rId47" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
+    <hyperlink ref="N30" r:id="rId48" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE38AF5-0CED-4EE5-85AA-B535BA8B1989}">
+  <dimension ref="A1:U17"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="31" customWidth="1"/>
+    <col min="9" max="10" width="21.28515625" style="31" customWidth="1"/>
+    <col min="11" max="12" width="45.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="13.5">
+      <c r="A1" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>581</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>593</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>580</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1" s="35" t="s">
+        <v>578</v>
+      </c>
+      <c r="J1" s="35" t="s">
+        <v>577</v>
+      </c>
+      <c r="K1" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="L1" s="35"/>
+    </row>
+    <row r="2" spans="1:21" ht="13.5">
+      <c r="A2" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>585</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>575</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>573</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>572</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>595</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>569</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>587</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>561</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>588</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>558</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>589</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>555</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>590</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="13.5">
+      <c r="A8" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>591</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>550</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>549</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="31" t="s">
+        <v>548</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>592</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>547</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>546</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>545</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+    </row>
+    <row r="10" spans="1:21" ht="13.5">
+      <c r="A10" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>598</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>596</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>600</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="1:21" ht="13.5">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="32"/>
+      <c r="E13" s="32"/>
+    </row>
+    <row r="14" spans="1:21" ht="13.5">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="I14" s="34"/>
+    </row>
+    <row r="15" spans="1:21" ht="13.5">
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:21" ht="13.5">
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="1:9" ht="13.5">
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="I17" s="32"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A63E4A1-7C56-4C11-9DE1-19B06AF71B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7A20C3-FFD2-4871-8C29-5C6820C57685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
-    <sheet name="活動節目" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="544">
   <si>
     <t>地圖編號</t>
   </si>
@@ -14203,952 +14202,12 @@
     <t>Tzu-Ting Huang</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>天使生活館一樓大廳</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15:30-16:40</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Po-Chi Su
-Artist: Cheng-Wei Chen, Tzu-Ting Huang, Bety Krňanská
-Artist Group: Hyper Wave</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：蘇珀琪
-藝術家：陳政維、黃姿婷、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bety Krňanská
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術團體：超級浪</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家講座</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14:00-15:10</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Chih-Yung Chiu
-Artist: Hsien-Yu Cheng, Hsin-Yuan Ho
-Artist Group: No Side Here, Assocreation</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>與談人：邱誌勇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>藝術家：鄭先喻、何芯源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>藝術團體：無邊製造、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Assocreation</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15:30-16:40</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Shih-Yu Hsu
-Artist: Tzu-I Yang, Chia-Yi Chien, Po-Ting Yu, Cheuk Hang Fan, Chih-Yu Chen</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：徐詩雨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：楊子毅、簡嘉誼、余柏霆、樊卓鏗、陳芷渝</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14:00-15:10</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Duo Chao
-Artist: Yu-Hsuan Shen, Pin-Jhen Chen, Fang-Yi Cheng, Tzu-Yung Kuo, Pei-Ting Hsieh</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：趙鐸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：沈宇軒、陳品蓁、鄭芳宜、郭子耘、謝佩庭</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15:30-16:40</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Dar-Kuen Wu
-Artist: Stefan Tiefengraber, Jed Berk, Shu-Yu Lin
-Artist Group: C-LAB’s Future Vision Lab</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：吳達坤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Stefan Tiefengraber</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jed Berk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、林書瑜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術團體：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">C-LAB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>未來視覺實驗室</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14:00-15:10</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panelist: Jau-Lan Guo
-Artist: Dries Depoorter, Verena Friedrich, I-Yeh Wu</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>與談人：郭紹蘭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dries Depoorter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Verena Friedrich</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、吳宜曄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Riso </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>印刷需將彩色圖分色、製版，再逐色疊印完成。工作坊將用程式拍攝人像、去背並拆成三色網點，模擬半調顆粒與隨機錯位，探索機器如何辨識人物與影像。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10:00-12:00</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Artist: Chih-Yu Chen</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：陳芷渝</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>How Machines See You: Body Silhouette Printing Workshop</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>機器怎麼看你：身體剪影印刷工作坊</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>工作坊</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hydra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是一套在瀏覽器中執行的視覺即時編碼工具，受到早期的類比影像合成器啟發，能透過簡單的語法組合，產生豐富的視覺效果。本工作坊將從基本圖形、動態、疊合到調變，帶領學員認識</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Hydra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的撰寫邏輯，運用有限的元素，創造多變的視覺。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Artist: Tung-Yu Liu</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>藝術家：劉東昱</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>From Scratch: Hydra Live Coding Workshop</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>From Scratch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Hydra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>影像編碼工作坊</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>圖片來源</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>簡介英文</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>簡介中文</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>地點</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>時間</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動英文名</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動中文名</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>分類</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>workshop-01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>workshop-02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>talking-01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>talking-02</t>
-  </si>
-  <si>
-    <t>talking-03</t>
-  </si>
-  <si>
-    <t>talking-04</t>
-  </si>
-  <si>
-    <t>talking-05</t>
-  </si>
-  <si>
-    <t>talking-06</t>
-  </si>
-  <si>
-    <t>表演者/講者英文名</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>表演者/講者中文名</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>（日）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10:00-12:00</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>10/31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>（六）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>19:00-22:00</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>performance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>音像之夜</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Audiovisual Performance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>臺北典藏植物園－主展場</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
-  </numFmts>
-  <fonts count="22">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15272,37 +14331,6 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -15326,7 +14354,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -15402,31 +14430,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -18171,352 +17174,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE38AF5-0CED-4EE5-85AA-B535BA8B1989}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="31" customWidth="1"/>
-    <col min="9" max="10" width="21.28515625" style="31" customWidth="1"/>
-    <col min="11" max="12" width="45.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="30"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" ht="13.5">
-      <c r="A1" s="35" t="s">
-        <v>583</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>584</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>582</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>581</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>594</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>593</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>580</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>579</v>
-      </c>
-      <c r="I1" s="35" t="s">
-        <v>578</v>
-      </c>
-      <c r="J1" s="35" t="s">
-        <v>577</v>
-      </c>
-      <c r="K1" s="35" t="s">
-        <v>576</v>
-      </c>
-      <c r="L1" s="35"/>
-    </row>
-    <row r="2" spans="1:21" ht="13.5">
-      <c r="A2" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>585</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>575</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>574</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>573</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>572</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>595</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>586</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>565</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>587</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>562</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>561</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>588</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>559</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>558</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>589</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>555</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>590</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="13.5">
-      <c r="A8" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>591</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>551</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>550</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>549</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>592</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>547</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>546</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>545</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-    </row>
-    <row r="10" spans="1:21" ht="13.5">
-      <c r="A10" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>598</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>599</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>596</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>600</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-    </row>
-    <row r="13" spans="1:21" ht="13.5">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="32"/>
-      <c r="E13" s="32"/>
-    </row>
-    <row r="14" spans="1:21" ht="13.5">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="I14" s="34"/>
-    </row>
-    <row r="15" spans="1:21" ht="13.5">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="I15" s="32"/>
-    </row>
-    <row r="16" spans="1:21" ht="13.5">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="I16" s="32"/>
-    </row>
-    <row r="17" spans="1:9" ht="13.5">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="I17" s="32"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7A20C3-FFD2-4871-8C29-5C6820C57685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E455F8D6-0EC9-437A-B127-9A4C4EAD6C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="545">
   <si>
     <t>地圖編號</t>
   </si>
@@ -12734,22 +12734,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Verena Friedrich </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>的創作主要以時間性裝置為核心，結合有機媒材、電子媒介與雕塑性元素，發展出兼具感知經驗與觀念性的作品。她的計畫曾於國際間多個展覽、媒體藝術節與學術研討會中發表。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
@@ -12844,11 +12828,6 @@
   <si>
     <t>FUTURE VISION LAB is a technology and media experimentation platform initiated by the Taiwan Contemporary Culture Lab (C-LAB), with a particular focus on immersive moving-image practices. At its core is DOME, a dome theater that uses spherical projection technology to explore new possibilities in future visual culture and technological art.
 With strong R&amp;D capabilities, the platform integrates technologies including image processing, projection stitching, hardware and software systems, surround sound, and architectural design. In addition to presenting exhibitions and performances and supporting creators in developing new works, FUTURE VISION LAB facilitates a wide range of interdisciplinary experiments, continually expanding new horizons for future visual practices and innovative technologies.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Verena Friedrich’s artistic practice centers on time-based installations that combine organic materials, electronic media, and sculptural elements. Her works bring together perceptual experience and conceptual inquiry, exploring the intersections between material processes, technology, and temporality.
-Her projects have been presented internationally at exhibitions, media art festivals, and academic conferences.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -14200,6 +14179,264 @@
   </si>
   <si>
     <t>Tzu-Ting Huang</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Verena Friedrich (she/they) develops installations and poetic-functional machines that condense complex relationships into material and sensorial experiences. Her work explores the possibilities and limits of techno-scientific systems and their embedded narratives of efficiency, controllability, and progress. Her works have been presented internationally at ZKM Karlsruhe, Ars Electronica, ISEA, and various venues in Asia, including the Nam June Paik Art Center in Seoul, the Hong Kong Arts Centre, and the Matsudo International Science Art Festival. She has held professorships and teaching positions at the Academy of Media Arts Cologne, Bauhaus University Weimar, and the Offenbach University of Art and Design (all in Germany).</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Verena Friedrich</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的創作以裝置與兼具詩意及功能性的機械為核心，將複雜的關係凝聚並轉化為具體且可感知的經驗。她的作品探索科技與科學系統的可能性及其限制，並關注其中所承載關於效率、可控性與進步的敘事。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>其作品曾於世界各地展出，包括德國卡爾斯魯厄藝術與媒體中心（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ZKM Karlsruhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）、林茲電子藝術節（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ars Electronica</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）、國際電子藝術研討會（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISEA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>），以及亞洲多個藝術機構與展覽，包括首爾白南準藝術中心（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nam June Paik Art Center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）、香港藝術中心（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hong Kong Arts Centre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）及松戶國際科學藝術節（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Matsudo International Science Art Festival</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>她亦曾於德國科隆媒體藝術學院（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Academy of Media Arts Cologne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）、威瑪包浩斯大學（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bauhaus University Weimar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）及奧芬巴赫藝術與設計大學（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Offenbach University of Art and Design</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）擔任教授及教學職務。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Installation</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -14329,6 +14566,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -14757,7 +14995,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -14833,7 +15071,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -14911,7 +15149,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -15074,10 +15312,10 @@
         <v>90</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>501</v>
+        <v>543</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>453</v>
@@ -15103,8 +15341,12 @@
       <c r="R6" s="13">
         <v>2023</v>
       </c>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
+      <c r="S6" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>544</v>
+      </c>
       <c r="U6" s="16" t="s">
         <v>96</v>
       </c>
@@ -15112,7 +15354,7 @@
         <v>97</v>
       </c>
       <c r="W6" s="24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="X6" s="16" t="s">
         <v>98</v>
@@ -15139,7 +15381,7 @@
         <v>488</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -15151,7 +15393,7 @@
         <v>498</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
@@ -15281,7 +15523,7 @@
         <v>125</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>28</v>
@@ -15437,7 +15679,7 @@
         <v>158</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>28</v>
@@ -15589,7 +15831,7 @@
         <v>191</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>28</v>
@@ -15667,7 +15909,7 @@
         <v>205</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>28</v>
@@ -15745,7 +15987,7 @@
         <v>222</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>223</v>
@@ -15821,7 +16063,7 @@
         <v>235</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -15897,7 +16139,7 @@
         <v>245</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -15975,7 +16217,7 @@
         <v>259</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -15984,16 +16226,16 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="K18" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="L18" s="14" t="s">
         <v>506</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>507</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>508</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="15" t="s">
@@ -16024,10 +16266,10 @@
         <v>265</v>
       </c>
       <c r="W18" s="25" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Y18" s="13" t="s">
         <v>266</v>
@@ -16051,7 +16293,7 @@
         <v>268</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>269</v>
@@ -16207,7 +16449,7 @@
         <v>303</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>28</v>
@@ -16285,7 +16527,7 @@
         <v>319</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -16359,7 +16601,7 @@
         <v>332</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>28</v>
@@ -16435,7 +16677,7 @@
         <v>344</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -16444,16 +16686,16 @@
         <v>29</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M24" s="15" t="s">
         <v>345</v>
@@ -16486,10 +16728,10 @@
         <v>351</v>
       </c>
       <c r="W24" s="27" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y24" s="13" t="s">
         <v>287</v>
@@ -16513,7 +16755,7 @@
         <v>353</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -16591,7 +16833,7 @@
         <v>369</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>28</v>
@@ -16669,7 +16911,7 @@
         <v>486</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -16726,10 +16968,10 @@
         <v>497</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -16738,7 +16980,7 @@
         <v>29</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>437</v>
@@ -16774,13 +17016,13 @@
         <v>402</v>
       </c>
       <c r="U28" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="V28" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="W28" s="28" t="s">
         <v>519</v>
-      </c>
-      <c r="V28" s="13" t="s">
-        <v>520</v>
-      </c>
-      <c r="W28" s="28" t="s">
-        <v>521</v>
       </c>
       <c r="X28" s="13" t="s">
         <v>435</v>
@@ -16947,7 +17189,7 @@
         <v>480</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>28</v>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E455F8D6-0EC9-437A-B127-9A4C4EAD6C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0513AA1B-4E58-4905-BD71-DD2DD263267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="546">
   <si>
     <t>地圖編號</t>
   </si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>main-05</t>
-  </si>
-  <si>
-    <t>Verena Friedrich</t>
   </si>
   <si>
     <t>德國</t>
@@ -869,12 +866,6 @@
     <t>artist-16</t>
   </si>
   <si>
-    <t>景伸</t>
-  </si>
-  <si>
-    <t>Spectacle Extension</t>
-  </si>
-  <si>
     <t>六頻道影像</t>
   </si>
   <si>
@@ -975,9 +966,6 @@
   </si>
   <si>
     <t>《游離的引線》— 延伸版本</t>
-  </si>
-  <si>
-    <t>Dissociated Fuses</t>
   </si>
   <si>
     <t>裝置</t>
@@ -14437,6 +14425,26 @@
   </si>
   <si>
     <t>Installation</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Verena Friedrich</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>貝蒂．克爾尼安斯卡</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>景伸：未曾之景</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spectacle Extension: A Landscape That Never Was</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dissociated Fuses</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -14912,7 +14920,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -14995,7 +15003,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -15004,16 +15012,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -15071,7 +15079,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -15086,10 +15094,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -15149,7 +15157,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -15164,10 +15172,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -15177,7 +15185,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -15198,10 +15206,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -15222,7 +15230,7 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>70</v>
@@ -15240,10 +15248,10 @@
         <v>74</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>75</v>
@@ -15300,64 +15308,64 @@
         <v>87</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F6" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="M6" s="15" t="s">
+      <c r="N6" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="O6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="Q6" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="U6" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="V6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="W6" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="X6" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="W6" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="X6" s="16" t="s">
-        <v>98</v>
       </c>
       <c r="Y6" s="13" t="s">
         <v>87</v>
@@ -15366,22 +15374,22 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -15390,140 +15398,140 @@
         <v>29</v>
       </c>
       <c r="I7" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>498</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>502</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="N7" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="O7" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="P7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="P7" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="Q7" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="25" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="X7" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="W7" s="24" t="s">
-        <v>499</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>106</v>
-      </c>
       <c r="Y7" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z7" s="6"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="O8" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="P8" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="R8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="Q8" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="R8" s="17" t="s">
+      <c r="S8" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>119</v>
-      </c>
-      <c r="T8" s="16" t="s">
-        <v>120</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="X8" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="16" t="s">
-        <v>122</v>
-      </c>
       <c r="Y8" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>28</v>
@@ -15532,109 +15540,109 @@
         <v>29</v>
       </c>
       <c r="I9" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="O9" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="P9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="Q9" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="R9" s="13">
         <v>2026</v>
       </c>
       <c r="S9" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="T9" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="U9" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="V9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="W9" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="X9" s="16" t="s">
-        <v>140</v>
-      </c>
       <c r="Y9" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="K10" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="P10" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="P10" s="13" t="s">
-        <v>151</v>
-      </c>
       <c r="Q10" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R10" s="13">
         <v>2026</v>
@@ -15646,19 +15654,19 @@
         <v>81</v>
       </c>
       <c r="U10" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="V10" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="V10" s="16" t="s">
+      <c r="W10" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="X10" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="X10" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="Y10" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
@@ -15667,19 +15675,19 @@
         <v>24</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>158</v>
-      </c>
       <c r="F11" s="13" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>28</v>
@@ -15688,53 +15696,53 @@
         <v>29</v>
       </c>
       <c r="I11" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="Q11" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>166</v>
       </c>
       <c r="R11" s="13">
         <v>2025</v>
       </c>
       <c r="S11" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="T11" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="U11" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="V11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="W11" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="X11" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="X11" s="16" t="s">
-        <v>172</v>
-      </c>
       <c r="Y11" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
@@ -15743,50 +15751,50 @@
         <v>40</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="J12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="K12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="M12" s="15" t="s">
         <v>180</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>181</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>183</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>184</v>
       </c>
       <c r="R12" s="13">
         <v>2013</v>
@@ -15798,19 +15806,19 @@
         <v>51</v>
       </c>
       <c r="U12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="V12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="W12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="X12" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="X12" s="16" t="s">
-        <v>188</v>
-      </c>
       <c r="Y12" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
@@ -15819,19 +15827,19 @@
         <v>24</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>191</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>28</v>
@@ -15840,34 +15848,34 @@
         <v>29</v>
       </c>
       <c r="I13" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="K13" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="M13" s="15" t="s">
+      <c r="N13" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="O13" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="P13" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="Q13" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="S13" s="16" t="s">
         <v>34</v>
@@ -15876,19 +15884,19 @@
         <v>35</v>
       </c>
       <c r="U13" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="V13" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="W13" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="W13" s="16" t="s">
+      <c r="X13" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="X13" s="16" t="s">
-        <v>203</v>
-      </c>
       <c r="Y13" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
@@ -15897,19 +15905,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>28</v>
@@ -15918,55 +15926,55 @@
         <v>29</v>
       </c>
       <c r="I14" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="L14" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="M14" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="N14" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="O14" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="P14" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="Q14" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="R14" s="13">
         <v>2024</v>
       </c>
       <c r="S14" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="T14" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="T14" s="16" t="s">
+      <c r="U14" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="U14" s="16" t="s">
+      <c r="V14" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="V14" s="16" t="s">
+      <c r="W14" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="W14" s="16" t="s">
+      <c r="X14" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="X14" s="16" t="s">
-        <v>220</v>
-      </c>
       <c r="Y14" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
@@ -15975,50 +15983,50 @@
         <v>56</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="I15" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="J15" s="14" t="s">
-        <v>226</v>
-      </c>
       <c r="K15" s="14" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="O15" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="Q15" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>230</v>
       </c>
       <c r="R15" s="13">
         <v>2025</v>
@@ -16030,19 +16038,19 @@
         <v>35</v>
       </c>
       <c r="U15" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="V15" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="W15" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="W15" s="16" t="s">
+      <c r="X15" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="X15" s="16" t="s">
-        <v>234</v>
-      </c>
       <c r="Y15" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
@@ -16051,19 +16059,19 @@
         <v>68</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>243</v>
+        <v>491</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -16072,53 +16080,53 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="J16" s="14" t="s">
-        <v>237</v>
-      </c>
       <c r="K16" s="14" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="O16" s="13" t="s">
+      <c r="P16" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="Q16" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="Q16" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="R16" s="13">
         <v>2026</v>
       </c>
       <c r="S16" s="16" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="W16" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="X16" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y16" s="13" t="s">
         <v>242</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>421</v>
-      </c>
-      <c r="Y16" s="13" t="s">
-        <v>243</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
@@ -16127,19 +16135,19 @@
         <v>68</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>245</v>
-      </c>
       <c r="F17" s="13" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -16148,55 +16156,55 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="K17" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="M17" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="K17" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="M17" s="15" t="s">
+      <c r="N17" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="N17" s="15" t="s">
+      <c r="O17" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="O17" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>251</v>
+      <c r="P17" s="11" t="s">
+        <v>543</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>252</v>
+        <v>544</v>
       </c>
       <c r="R17" s="13">
         <v>2025</v>
       </c>
       <c r="S17" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="T17" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="T17" s="16" t="s">
-        <v>216</v>
-      </c>
       <c r="U17" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="V17" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="W17" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="X17" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="Y17" s="13" t="s">
         <v>254</v>
-      </c>
-      <c r="W17" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="X17" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y17" s="13" t="s">
-        <v>257</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
@@ -16205,19 +16213,19 @@
         <v>68</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -16226,29 +16234,29 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="R18" s="13">
         <v>2026</v>
@@ -16257,22 +16265,22 @@
         <v>50</v>
       </c>
       <c r="T18" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="V18" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="W18" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="X18" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y18" s="13" t="s">
         <v>263</v>
-      </c>
-      <c r="U18" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="V18" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="W18" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="Y18" s="13" t="s">
-        <v>266</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
@@ -16281,76 +16289,76 @@
         <v>68</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="I19" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>539</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="J19" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="K19" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="L19" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="M19" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="N19" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="O19" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="M19" s="15" t="s">
+      <c r="P19" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="N19" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>278</v>
-      </c>
       <c r="Q19" s="13" t="s">
-        <v>279</v>
+        <v>545</v>
       </c>
       <c r="R19" s="13">
         <v>2026</v>
       </c>
       <c r="S19" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="T19" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="U19" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="W19" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="T19" s="16" t="s">
+      <c r="X19" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="U19" s="16" t="s">
+      <c r="Y19" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="V19" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="W19" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="X19" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>286</v>
       </c>
       <c r="Z19" s="7"/>
     </row>
@@ -16359,76 +16367,76 @@
         <v>68</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="E20" s="13" t="s">
+      <c r="N20" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="14" t="s">
+      <c r="O20" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="P20" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>294</v>
-      </c>
       <c r="Q20" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="R20" s="13">
         <v>2025</v>
       </c>
       <c r="S20" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="W20" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="X20" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="Y20" s="13" t="s">
         <v>297</v>
-      </c>
-      <c r="V20" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="W20" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="X20" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y20" s="13" t="s">
-        <v>301</v>
       </c>
       <c r="Z20" s="6"/>
     </row>
@@ -16437,19 +16445,19 @@
         <v>86</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>28</v>
@@ -16458,76 +16466,76 @@
         <v>29</v>
       </c>
       <c r="I21" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N21" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="O21" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="P21" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="L21" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="M21" s="15" t="s">
+      <c r="Q21" s="13" t="s">
         <v>307</v>
-      </c>
-      <c r="N21" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>311</v>
       </c>
       <c r="R21" s="13">
         <v>2025</v>
       </c>
       <c r="S21" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="W21" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="T21" s="16" t="s">
+      <c r="X21" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="U21" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="V21" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="W21" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>317</v>
-      </c>
       <c r="Y21" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z21" s="6"/>
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -16536,72 +16544,72 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="W22" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="X22" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>28</v>
@@ -16610,29 +16618,29 @@
         <v>29</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R23" s="13">
         <v>2026</v>
@@ -16641,43 +16649,43 @@
         <v>50</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="W23" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="X23" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Y23" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -16686,76 +16694,76 @@
         <v>29</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="M24" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q24" s="13" t="s">
         <v>345</v>
-      </c>
-      <c r="N24" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="O24" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>349</v>
       </c>
       <c r="R24" s="13">
         <v>2026</v>
       </c>
       <c r="S24" s="16" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="W24" s="27" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -16764,76 +16772,76 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="O25" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="P25" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="K25" s="14" t="s">
-        <v>466</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="M25" s="15" t="s">
+      <c r="Q25" s="13" t="s">
         <v>356</v>
-      </c>
-      <c r="N25" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>360</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="U25" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="V25" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="W25" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="U25" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="V25" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="W25" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="X25" s="16" t="s">
-        <v>366</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="12" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>28</v>
@@ -16842,31 +16850,31 @@
         <v>29</v>
       </c>
       <c r="I26" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="O26" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="P26" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>467</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="M26" s="15" t="s">
+      <c r="Q26" s="13" t="s">
         <v>372</v>
-      </c>
-      <c r="N26" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="O26" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>376</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -16878,19 +16886,19 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="W26" s="16" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="X26" s="16" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y26" s="13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
@@ -16899,19 +16907,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -16920,25 +16928,25 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -16950,7 +16958,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
@@ -16959,19 +16967,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -16980,55 +16988,55 @@
         <v>29</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="R28" s="13">
         <v>2026</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="T28" s="13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="V28" s="13" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="W28" s="28" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="X28" s="13" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
@@ -17037,19 +17045,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -17058,49 +17066,49 @@
         <v>29</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="T29" s="13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13"/>
       <c r="W29" s="13" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="X29" s="13" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
@@ -17109,19 +17117,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>28</v>
@@ -17130,45 +17138,45 @@
         <v>29</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="21" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="U30" s="13"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="Z30" s="6"/>
     </row>
@@ -17177,19 +17185,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>28</v>
@@ -17198,49 +17206,49 @@
         <v>29</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="J31" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q31" s="13" t="s">
         <v>423</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="N31" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="O31" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q31" s="13" t="s">
-        <v>427</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
@@ -17249,44 +17257,44 @@
         <v>40</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C32" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="I32" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="J32" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="K32" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>395</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>399</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -17294,21 +17302,21 @@
         <v>2026</v>
       </c>
       <c r="S32" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="T32" s="13" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="X32" s="13" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="Y32" s="13" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Z32" s="6"/>
     </row>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0513AA1B-4E58-4905-BD71-DD2DD263267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3891DFCF-FEA3-4BFF-BB9F-147006C3BFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>EZ品質分解機V2</t>
-  </si>
-  <si>
-    <t>EZ Quality Soryer V2</t>
   </si>
   <si>
     <t>機械裝置、電腦</t>
@@ -14445,6 +14442,10 @@
   </si>
   <si>
     <t>Dissociated Fuses</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>EZ Quality Sorter V2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -14920,7 +14921,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15003,7 +15004,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -15012,16 +15013,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -15079,7 +15080,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -15094,10 +15095,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -15157,7 +15158,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -15172,10 +15173,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -15185,7 +15186,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -15206,10 +15207,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -15230,7 +15231,7 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>70</v>
@@ -15248,10 +15249,10 @@
         <v>74</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>75</v>
@@ -15308,10 +15309,10 @@
         <v>87</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>88</v>
@@ -15320,16 +15321,16 @@
         <v>89</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>90</v>
@@ -15344,28 +15345,28 @@
         <v>93</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>94</v>
+        <v>545</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="U6" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="W6" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="X6" s="16" t="s">
         <v>96</v>
-      </c>
-      <c r="W6" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="X6" s="16" t="s">
-        <v>97</v>
       </c>
       <c r="Y6" s="13" t="s">
         <v>87</v>
@@ -15374,22 +15375,22 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -15398,140 +15399,140 @@
         <v>29</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="N7" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="O7" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="P7" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="P7" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="Q7" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="25" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="X7" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="W7" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="Y7" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z7" s="6"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="O8" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="P8" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="R8" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="Q8" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="R8" s="17" t="s">
+      <c r="S8" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>118</v>
-      </c>
-      <c r="T8" s="16" t="s">
-        <v>119</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="X8" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="X8" s="16" t="s">
-        <v>121</v>
-      </c>
       <c r="Y8" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>124</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>28</v>
@@ -15540,109 +15541,109 @@
         <v>29</v>
       </c>
       <c r="I9" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="O9" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="P9" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="Q9" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="R9" s="13">
         <v>2026</v>
       </c>
       <c r="S9" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="T9" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="U9" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="V9" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="W9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="X9" s="16" t="s">
-        <v>139</v>
-      </c>
       <c r="Y9" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="K10" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="P10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="P10" s="13" t="s">
-        <v>150</v>
-      </c>
       <c r="Q10" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R10" s="13">
         <v>2026</v>
@@ -15654,19 +15655,19 @@
         <v>81</v>
       </c>
       <c r="U10" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="V10" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="V10" s="16" t="s">
+      <c r="W10" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="X10" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="X10" s="16" t="s">
-        <v>154</v>
-      </c>
       <c r="Y10" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
@@ -15675,19 +15676,19 @@
         <v>24</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>157</v>
-      </c>
       <c r="F11" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>28</v>
@@ -15696,53 +15697,53 @@
         <v>29</v>
       </c>
       <c r="I11" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>161</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="Q11" s="13" t="s">
         <v>164</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>165</v>
       </c>
       <c r="R11" s="13">
         <v>2025</v>
       </c>
       <c r="S11" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="T11" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="U11" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="V11" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="W11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="X11" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="X11" s="16" t="s">
-        <v>171</v>
-      </c>
       <c r="Y11" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
@@ -15751,50 +15752,50 @@
         <v>40</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="J12" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="K12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="M12" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>180</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="P12" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>182</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>183</v>
       </c>
       <c r="R12" s="13">
         <v>2013</v>
@@ -15806,19 +15807,19 @@
         <v>51</v>
       </c>
       <c r="U12" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="V12" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="W12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="X12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="X12" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="Y12" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
@@ -15827,19 +15828,19 @@
         <v>24</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>190</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>28</v>
@@ -15848,34 +15849,34 @@
         <v>29</v>
       </c>
       <c r="I13" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="K13" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="M13" s="15" t="s">
+      <c r="N13" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="O13" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="P13" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="Q13" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="17" t="s">
         <v>197</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>198</v>
       </c>
       <c r="S13" s="16" t="s">
         <v>34</v>
@@ -15884,19 +15885,19 @@
         <v>35</v>
       </c>
       <c r="U13" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="V13" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="W13" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="W13" s="16" t="s">
+      <c r="X13" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="X13" s="16" t="s">
-        <v>202</v>
-      </c>
       <c r="Y13" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
@@ -15905,19 +15906,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>204</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>28</v>
@@ -15926,55 +15927,55 @@
         <v>29</v>
       </c>
       <c r="I14" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="L14" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="M14" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="N14" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="O14" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="P14" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="Q14" s="13" t="s">
         <v>212</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>213</v>
       </c>
       <c r="R14" s="13">
         <v>2024</v>
       </c>
       <c r="S14" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="T14" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="T14" s="16" t="s">
+      <c r="U14" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="U14" s="16" t="s">
+      <c r="V14" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="V14" s="16" t="s">
+      <c r="W14" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="W14" s="16" t="s">
+      <c r="X14" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="X14" s="16" t="s">
-        <v>219</v>
-      </c>
       <c r="Y14" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
@@ -15983,50 +15984,50 @@
         <v>56</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="I15" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J15" s="14" t="s">
-        <v>225</v>
-      </c>
       <c r="K15" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="L15" s="14" t="s">
         <v>454</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>455</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="O15" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="Q15" s="13" t="s">
         <v>228</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>229</v>
       </c>
       <c r="R15" s="13">
         <v>2025</v>
@@ -16038,19 +16039,19 @@
         <v>35</v>
       </c>
       <c r="U15" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="V15" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="W15" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="W15" s="16" t="s">
+      <c r="X15" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="X15" s="16" t="s">
-        <v>233</v>
-      </c>
       <c r="Y15" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
@@ -16059,19 +16060,19 @@
         <v>68</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -16080,53 +16081,53 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="J16" s="14" t="s">
-        <v>236</v>
-      </c>
       <c r="K16" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="O16" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="O16" s="13" t="s">
+      <c r="P16" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="Q16" s="13" t="s">
         <v>239</v>
-      </c>
-      <c r="Q16" s="13" t="s">
-        <v>240</v>
       </c>
       <c r="R16" s="13">
         <v>2026</v>
       </c>
       <c r="S16" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="U16" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="T16" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>458</v>
-      </c>
       <c r="V16" s="16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="W16" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="X16" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y16" s="13" t="s">
         <v>241</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="Y16" s="13" t="s">
-        <v>242</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
@@ -16135,19 +16136,19 @@
         <v>68</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>244</v>
-      </c>
       <c r="F17" s="13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -16156,55 +16157,55 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="K17" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="M17" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="K17" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="M17" s="15" t="s">
+      <c r="N17" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="N17" s="15" t="s">
+      <c r="O17" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="O17" s="13" t="s">
-        <v>249</v>
-      </c>
       <c r="P17" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="Q17" s="13" t="s">
         <v>543</v>
-      </c>
-      <c r="Q17" s="13" t="s">
-        <v>544</v>
       </c>
       <c r="R17" s="13">
         <v>2025</v>
       </c>
       <c r="S17" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="T17" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="T17" s="16" t="s">
-        <v>215</v>
-      </c>
       <c r="U17" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="V17" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="W17" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="W17" s="16" t="s">
+      <c r="X17" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="X17" s="16" t="s">
+      <c r="Y17" s="13" t="s">
         <v>253</v>
-      </c>
-      <c r="Y17" s="13" t="s">
-        <v>254</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
@@ -16213,19 +16214,19 @@
         <v>68</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>256</v>
-      </c>
       <c r="F18" s="13" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -16234,29 +16235,29 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="K18" s="23" t="s">
         <v>500</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="L18" s="14" t="s">
         <v>501</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>502</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="O18" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="P18" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="P18" s="13" t="s">
-        <v>259</v>
-      </c>
       <c r="Q18" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R18" s="13">
         <v>2026</v>
@@ -16265,22 +16266,22 @@
         <v>50</v>
       </c>
       <c r="T18" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="U18" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="U18" s="16" t="s">
+      <c r="V18" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="W18" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="X18" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="Y18" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="W18" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>504</v>
-      </c>
-      <c r="Y18" s="13" t="s">
-        <v>263</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
@@ -16289,76 +16290,76 @@
         <v>68</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="F19" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="I19" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="J19" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="K19" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="L19" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="M19" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="M19" s="15" t="s">
+      <c r="N19" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="N19" s="15" t="s">
+      <c r="O19" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="P19" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="P19" s="13" t="s">
-        <v>275</v>
-      </c>
       <c r="Q19" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R19" s="13">
         <v>2026</v>
       </c>
       <c r="S19" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="T19" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="T19" s="16" t="s">
+      <c r="U19" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="U19" s="16" t="s">
+      <c r="V19" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="V19" s="16" t="s">
+      <c r="W19" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="W19" s="19" t="s">
+      <c r="X19" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="X19" s="19" t="s">
+      <c r="Y19" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>282</v>
       </c>
       <c r="Z19" s="7"/>
     </row>
@@ -16367,19 +16368,19 @@
         <v>68</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>284</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>88</v>
@@ -16388,55 +16389,55 @@
         <v>89</v>
       </c>
       <c r="I20" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="K20" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="M20" s="15" t="s">
+      <c r="N20" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="N20" s="15" t="s">
+      <c r="O20" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="P20" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="P20" s="13" t="s">
-        <v>290</v>
-      </c>
       <c r="Q20" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R20" s="13">
         <v>2025</v>
       </c>
       <c r="S20" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="T20" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="U20" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="V20" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="W20" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="W20" s="16" t="s">
+      <c r="X20" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="X20" s="16" t="s">
+      <c r="Y20" s="13" t="s">
         <v>296</v>
-      </c>
-      <c r="Y20" s="13" t="s">
-        <v>297</v>
       </c>
       <c r="Z20" s="6"/>
     </row>
@@ -16445,19 +16446,19 @@
         <v>86</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>299</v>
-      </c>
       <c r="F21" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>28</v>
@@ -16466,76 +16467,76 @@
         <v>29</v>
       </c>
       <c r="I21" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J21" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="K21" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="L21" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="L21" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="M21" s="15" t="s">
+      <c r="N21" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="N21" s="15" t="s">
+      <c r="O21" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="P21" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="Q21" s="13" t="s">
         <v>306</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>307</v>
       </c>
       <c r="R21" s="13">
         <v>2025</v>
       </c>
       <c r="S21" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="T21" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="T21" s="16" t="s">
+      <c r="U21" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="U21" s="16" t="s">
+      <c r="V21" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="W21" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="W21" s="16" t="s">
+      <c r="X21" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="X21" s="16" t="s">
-        <v>313</v>
-      </c>
       <c r="Y21" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Z21" s="6"/>
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>315</v>
-      </c>
       <c r="F22" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -16544,72 +16545,72 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="K22" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="L22" s="14" t="s">
         <v>318</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>319</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="P22" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="Q22" s="13" t="s">
         <v>321</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>322</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="T22" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="T22" s="16" t="s">
+      <c r="U22" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="W22" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="U22" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="V22" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="W22" s="16" t="s">
+      <c r="X22" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="X22" s="16" t="s">
-        <v>326</v>
-      </c>
       <c r="Y22" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>328</v>
-      </c>
       <c r="F23" s="13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>28</v>
@@ -16618,29 +16619,29 @@
         <v>29</v>
       </c>
       <c r="I23" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>330</v>
-      </c>
       <c r="K23" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="O23" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="O23" s="13" t="s">
+      <c r="P23" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="Q23" s="13" t="s">
         <v>333</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>334</v>
       </c>
       <c r="R23" s="13">
         <v>2026</v>
@@ -16649,43 +16650,43 @@
         <v>50</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U23" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="V23" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="W23" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="W23" s="16" t="s">
+      <c r="X23" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="X23" s="16" t="s">
-        <v>338</v>
-      </c>
       <c r="Y23" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C24" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>340</v>
-      </c>
       <c r="F24" s="13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -16694,76 +16695,76 @@
         <v>29</v>
       </c>
       <c r="I24" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="J24" s="14" t="s">
-        <v>510</v>
-      </c>
       <c r="K24" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="L24" s="14" t="s">
         <v>507</v>
       </c>
-      <c r="L24" s="14" t="s">
-        <v>508</v>
-      </c>
       <c r="M24" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="N24" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="N24" s="15" t="s">
+      <c r="O24" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="P24" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>344</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>345</v>
       </c>
       <c r="R24" s="13">
         <v>2026</v>
       </c>
       <c r="S24" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="T24" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="T24" s="16" t="s">
-        <v>347</v>
-      </c>
       <c r="U24" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="V24" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="V24" s="16" t="s">
-        <v>347</v>
-      </c>
       <c r="W24" s="27" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>349</v>
-      </c>
       <c r="F25" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -16772,76 +16773,76 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="K25" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="M25" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="K25" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="M25" s="15" t="s">
+      <c r="N25" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="N25" s="15" t="s">
+      <c r="O25" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="P25" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="P25" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>356</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="T25" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="U25" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="V25" s="16" t="s">
+      <c r="W25" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="W25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="X25" s="16" t="s">
-        <v>362</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>365</v>
-      </c>
       <c r="F26" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>28</v>
@@ -16850,31 +16851,31 @@
         <v>29</v>
       </c>
       <c r="I26" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="K26" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="M26" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="M26" s="15" t="s">
+      <c r="N26" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="N26" s="15" t="s">
+      <c r="O26" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="P26" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="Q26" s="13" t="s">
         <v>371</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>372</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -16886,19 +16887,19 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="V26" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="W26" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="W26" s="16" t="s">
+      <c r="X26" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="X26" s="16" t="s">
-        <v>376</v>
-      </c>
       <c r="Y26" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
@@ -16907,19 +16908,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="D27" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -16928,25 +16929,25 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="K27" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="L27" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>426</v>
-      </c>
       <c r="M27" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="N27" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="N27" s="15" t="s">
+      <c r="O27" s="13" t="s">
         <v>380</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>381</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -16958,7 +16959,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
@@ -16967,19 +16968,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="D28" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -16988,55 +16989,55 @@
         <v>29</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K28" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="L28" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="M28" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="P28" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="M28" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="N28" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>468</v>
-      </c>
       <c r="Q28" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R28" s="13">
         <v>2026</v>
       </c>
       <c r="S28" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="T28" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="T28" s="13" t="s">
-        <v>398</v>
-      </c>
       <c r="U28" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="V28" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="V28" s="13" t="s">
+      <c r="W28" s="28" t="s">
         <v>514</v>
       </c>
-      <c r="W28" s="28" t="s">
-        <v>515</v>
-      </c>
       <c r="X28" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
@@ -17045,19 +17046,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="D29" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E29" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>383</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>384</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -17066,49 +17067,49 @@
         <v>29</v>
       </c>
       <c r="I29" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="K29" s="14" t="s">
         <v>469</v>
       </c>
-      <c r="J29" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="K29" s="14" t="s">
+      <c r="L29" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="P29" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="O29" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>471</v>
-      </c>
       <c r="Q29" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="T29" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="T29" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13"/>
       <c r="W29" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="X29" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
@@ -17117,19 +17118,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="D30" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E30" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>386</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>387</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>28</v>
@@ -17138,45 +17139,45 @@
         <v>29</v>
       </c>
       <c r="I30" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="K30" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="J30" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>474</v>
-      </c>
       <c r="L30" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="T30" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="T30" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="U30" s="13"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Z30" s="6"/>
     </row>
@@ -17185,19 +17186,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="D31" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>28</v>
@@ -17206,49 +17207,49 @@
         <v>29</v>
       </c>
       <c r="I31" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="L31" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="M31" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="P31" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="L31" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="N31" s="15" t="s">
+      <c r="Q31" s="13" t="s">
         <v>422</v>
-      </c>
-      <c r="O31" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="Q31" s="13" t="s">
-        <v>423</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="T31" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="T31" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
@@ -17257,44 +17258,44 @@
         <v>40</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C32" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="G32" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="H32" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="I32" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="J32" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="K32" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>394</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>395</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -17302,21 +17303,21 @@
         <v>2026</v>
       </c>
       <c r="S32" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="T32" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="T32" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="X32" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="X32" s="13" t="s">
-        <v>400</v>
-      </c>
       <c r="Y32" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Z32" s="6"/>
     </row>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3891DFCF-FEA3-4BFF-BB9F-147006C3BFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE15F40B-52C2-4E6A-9728-98DD371FECCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE15F40B-52C2-4E6A-9728-98DD371FECCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72D64B3-2CC6-4743-BCAB-F661C8E2E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>Mechanical installation, computer</t>
-  </si>
-  <si>
-    <t>EZ Quality Sorter V2 is an interactive installation by German artist Verena Friedrich and forms part of her ERBSENZÄHLER project. Centered on an industrial-looking automated sorting mechanism, the work uses a feeding device, conveyor belt, and image-recognition process to classify pea seeds into two categories: “good quality” and “poor quality.” Through this seemingly simple act of sorting, the work reveals the human labor, subjective judgment, and violence of classification embedded in contemporary “smart” systems. When complex forms of life are compressed into a binary of good and bad, the supposed objectivity of the machine itself becomes questionable.</t>
   </si>
   <si>
     <t>06</t>
@@ -12718,99 +12715,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>《</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EZ Quality Sorter V2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>》</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>是德國藝術家</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Verena Friedrich </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>的互動裝置，屬於其</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ERBSENZÄHLER </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>計畫的一部分。作品以一座帶有工業感的自動分選機構為核心，透過送料裝置、輸送帶與影像辨識流程，將豌豆種子區分為「品質良好」與「品質不佳」兩類。作品藉由看似簡單的分選行為，揭示當代「智慧」系統背後的人工勞動、主觀判斷與分類暴力。當複雜生命被壓縮為好壞二分，機器的客觀性也變得可疑。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>FUTURE VISION LAB is a technology and media experimentation platform initiated by the Taiwan Contemporary Culture Lab (C-LAB), with a particular focus on immersive moving-image practices. At its core is DOME, a dome theater that uses spherical projection technology to explore new possibilities in future visual culture and technological art.
 With strong R&amp;D capabilities, the platform integrates technologies including image processing, projection stitching, hardware and software systems, surround sound, and architectural design. In addition to presenting exhibitions and performances and supporting creators in developing new works, FUTURE VISION LAB facilitates a wide range of interdisciplinary experiments, continually expanding new horizons for future visual practices and innovative technologies.</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -14171,256 +14075,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Verena Friedrich</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的創作以裝置與兼具詩意及功能性的機械為核心，將複雜的關係凝聚並轉化為具體且可感知的經驗。她的作品探索科技與科學系統的可能性及其限制，並關注其中所承載關於效率、可控性與進步的敘事。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>其作品曾於世界各地展出，包括德國卡爾斯魯厄藝術與媒體中心（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ZKM Karlsruhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）、林茲電子藝術節（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ars Electronica</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）、國際電子藝術研討會（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ISEA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>），以及亞洲多個藝術機構與展覽，包括首爾白南準藝術中心（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Nam June Paik Art Center</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）、香港藝術中心（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hong Kong Arts Centre</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）及松戶國際科學藝術節（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Matsudo International Science Art Festival</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>她亦曾於德國科隆媒體藝術學院（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Academy of Media Arts Cologne</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）、威瑪包浩斯大學（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bauhaus University Weimar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）及奧芬巴赫藝術與設計大學（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Offenbach University of Art and Design</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）擔任教授及教學職務。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Installation</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -14446,6 +14100,281 @@
   </si>
   <si>
     <t>EZ Quality Sorter V2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>“The good ones go into the pot, the bad ones go into your crop.” – so the story goes in Cinderella. But who decides what is good or bad?
+The “EZ Quality Sorter V2” is an industrial-looking machine that automatically separates and classifies pea seeds according to quality. Visitors are invited to inspect individual peas through an optical device and classify them by pressing a green or red button. Their decisions are recorded as image data, which the machine subsequently uses for automated sorting.
+The work explores how subjective human judgments become formalized and embedded in seemingly objective, “intelligent” systems, and what happens when complex situations are reduced to binary categories.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Verena Friedrich</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（她／她們）擅長創作裝置藝術與兼具詩意與功能性的機械作品，將複雜的共生關係凝練為具體的物質與感官體驗。她的創作深入探索科技系統的潛力與局限，並審視其中所隱含關於效率、可控性與進步的敘事。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其作品曾受邀於國際盛會與藝術機構展出，包括卡爾斯魯厄藝術與媒體中心（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ZKM Karlsruhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）、奧地利林茲電子藝術節（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ars Electronica</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）、國際電子藝術研討會（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISEA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>），以及亞洲各地的展演場域，如首爾白南準藝術中心（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nam June Paik Art Center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）、香港藝術中心與松戶國際科學藝術節（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Matsudo International Science Art Festival</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）。她亦曾於德國多所知名學府任教並擔任教授，包含科隆媒體藝術學院（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Academy of Media Arts Cologne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）、魏瑪包浩斯大學（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bauhaus University Weimar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）及奧芬巴赫藝術與設計學院（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Offenbach University of Art and Design</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「灰姑娘的故事裡這麼說道：『好豆進鍋裡，壞豆進肚子裡。』但，究竟由誰來決定好與壞？」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>EZ Quality Sorter V2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>》是一台具工業風格的機器，能自動對豌豆種子進行品質分類與篩選。展覽現場邀請觀者透過光學裝置檢視單顆豌豆，並按壓綠色或紅色按鈕為其品質定調。觀者的這些決定將轉化為影像數據，成為機器隨後進行自動化分揀的依據。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本作品旨在探討人類的主觀判斷如何被制度化、並嵌入看似客觀且「智慧」的系統之中；同時也拋出反思：當複雜的現實經驗被精簡為非黑即白的二元分類時，我們將面臨什麼樣的景況？</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -14921,7 +14850,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -15004,7 +14933,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -15013,16 +14942,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -15080,7 +15009,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -15095,10 +15024,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -15158,7 +15087,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -15173,10 +15102,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -15186,7 +15115,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -15207,10 +15136,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -15231,7 +15160,7 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>70</v>
@@ -15249,10 +15178,10 @@
         <v>74</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>75</v>
@@ -15309,10 +15238,10 @@
         <v>87</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>88</v>
@@ -15321,16 +15250,16 @@
         <v>89</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>90</v>
@@ -15345,16 +15274,16 @@
         <v>93</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>94</v>
@@ -15362,11 +15291,11 @@
       <c r="V6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="W6" s="24" t="s">
-        <v>496</v>
+      <c r="W6" s="27" t="s">
+        <v>545</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>96</v>
+        <v>543</v>
       </c>
       <c r="Y6" s="13" t="s">
         <v>87</v>
@@ -15375,22 +15304,22 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -15399,140 +15328,140 @@
         <v>29</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="N7" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="O7" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="P7" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="P7" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="Q7" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R7" s="13"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="X7" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="W7" s="24" t="s">
-        <v>494</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>104</v>
-      </c>
       <c r="Y7" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z7" s="6"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="O8" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="P8" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="Q8" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="R8" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="Q8" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="R8" s="17" t="s">
+      <c r="S8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>117</v>
-      </c>
-      <c r="T8" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="X8" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="X8" s="16" t="s">
-        <v>120</v>
-      </c>
       <c r="Y8" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>123</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>28</v>
@@ -15541,109 +15470,109 @@
         <v>29</v>
       </c>
       <c r="I9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="O9" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="P9" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="Q9" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="R9" s="13">
         <v>2026</v>
       </c>
       <c r="S9" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="T9" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="U9" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="U9" s="16" t="s">
+      <c r="V9" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="W9" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="X9" s="16" t="s">
-        <v>138</v>
-      </c>
       <c r="Y9" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="K10" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>413</v>
-      </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="P10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="P10" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="Q10" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R10" s="13">
         <v>2026</v>
@@ -15655,19 +15584,19 @@
         <v>81</v>
       </c>
       <c r="U10" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="V10" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="V10" s="16" t="s">
+      <c r="W10" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="X10" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="X10" s="16" t="s">
-        <v>153</v>
-      </c>
       <c r="Y10" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
@@ -15676,19 +15605,19 @@
         <v>24</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="F11" s="13" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>28</v>
@@ -15697,53 +15626,53 @@
         <v>29</v>
       </c>
       <c r="I11" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>160</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="Q11" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>164</v>
       </c>
       <c r="R11" s="13">
         <v>2025</v>
       </c>
       <c r="S11" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="T11" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="U11" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="V11" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="W11" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="X11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="X11" s="16" t="s">
-        <v>170</v>
-      </c>
       <c r="Y11" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
@@ -15752,50 +15681,50 @@
         <v>40</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="J12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="K12" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="M12" s="15" t="s">
         <v>178</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>179</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="P12" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="R12" s="13">
         <v>2013</v>
@@ -15807,19 +15736,19 @@
         <v>51</v>
       </c>
       <c r="U12" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="V12" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="W12" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="X12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="X12" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="Y12" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
@@ -15828,19 +15757,19 @@
         <v>24</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>189</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>28</v>
@@ -15849,34 +15778,34 @@
         <v>29</v>
       </c>
       <c r="I13" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="K13" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="M13" s="15" t="s">
+      <c r="N13" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="O13" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="P13" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="Q13" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="17" t="s">
         <v>196</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>197</v>
       </c>
       <c r="S13" s="16" t="s">
         <v>34</v>
@@ -15885,19 +15814,19 @@
         <v>35</v>
       </c>
       <c r="U13" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="V13" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="W13" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="W13" s="16" t="s">
+      <c r="X13" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="X13" s="16" t="s">
-        <v>201</v>
-      </c>
       <c r="Y13" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
@@ -15906,19 +15835,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>203</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>28</v>
@@ -15927,55 +15856,55 @@
         <v>29</v>
       </c>
       <c r="I14" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="L14" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="M14" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="N14" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="O14" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="P14" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="Q14" s="13" t="s">
         <v>211</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>212</v>
       </c>
       <c r="R14" s="13">
         <v>2024</v>
       </c>
       <c r="S14" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="T14" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="T14" s="16" t="s">
+      <c r="U14" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="U14" s="16" t="s">
+      <c r="V14" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="V14" s="16" t="s">
+      <c r="W14" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="W14" s="16" t="s">
+      <c r="X14" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="X14" s="16" t="s">
-        <v>218</v>
-      </c>
       <c r="Y14" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
@@ -15984,50 +15913,50 @@
         <v>56</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="I15" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="J15" s="14" t="s">
-        <v>224</v>
-      </c>
       <c r="K15" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L15" s="14" t="s">
         <v>453</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>454</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="O15" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="Q15" s="13" t="s">
         <v>227</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>228</v>
       </c>
       <c r="R15" s="13">
         <v>2025</v>
@@ -16039,19 +15968,19 @@
         <v>35</v>
       </c>
       <c r="U15" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="V15" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="W15" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="W15" s="16" t="s">
+      <c r="X15" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="X15" s="16" t="s">
-        <v>232</v>
-      </c>
       <c r="Y15" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
@@ -16060,19 +15989,19 @@
         <v>68</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -16081,53 +16010,53 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="J16" s="14" t="s">
-        <v>235</v>
-      </c>
       <c r="K16" s="14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="O16" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="O16" s="13" t="s">
+      <c r="P16" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="Q16" s="13" t="s">
         <v>238</v>
-      </c>
-      <c r="Q16" s="13" t="s">
-        <v>239</v>
       </c>
       <c r="R16" s="13">
         <v>2026</v>
       </c>
       <c r="S16" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="U16" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="T16" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>457</v>
-      </c>
       <c r="V16" s="16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="W16" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="X16" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y16" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="Y16" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
@@ -16136,19 +16065,19 @@
         <v>68</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>243</v>
-      </c>
       <c r="F17" s="13" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -16157,55 +16086,55 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="K17" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="M17" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="K17" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="M17" s="15" t="s">
+      <c r="N17" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="N17" s="15" t="s">
+      <c r="O17" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="O17" s="13" t="s">
-        <v>248</v>
-      </c>
       <c r="P17" s="11" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="R17" s="13">
         <v>2025</v>
       </c>
       <c r="S17" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="T17" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="T17" s="16" t="s">
-        <v>214</v>
-      </c>
       <c r="U17" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="V17" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="V17" s="16" t="s">
+      <c r="W17" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="W17" s="16" t="s">
+      <c r="X17" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="X17" s="16" t="s">
+      <c r="Y17" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="Y17" s="13" t="s">
-        <v>253</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
@@ -16214,19 +16143,19 @@
         <v>68</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>255</v>
-      </c>
       <c r="F18" s="13" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -16235,29 +16164,29 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="K18" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="L18" s="14" t="s">
         <v>499</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>500</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>501</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="O18" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="P18" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="P18" s="13" t="s">
-        <v>258</v>
-      </c>
       <c r="Q18" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R18" s="13">
         <v>2026</v>
@@ -16266,22 +16195,22 @@
         <v>50</v>
       </c>
       <c r="T18" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="U18" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="U18" s="16" t="s">
+      <c r="V18" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="W18" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="X18" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="Y18" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="W18" s="25" t="s">
-        <v>502</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="Y18" s="13" t="s">
-        <v>262</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
@@ -16290,76 +16219,76 @@
         <v>68</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="F19" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="I19" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="J19" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="K19" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="L19" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="M19" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="M19" s="15" t="s">
+      <c r="N19" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="N19" s="15" t="s">
+      <c r="O19" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="P19" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="P19" s="13" t="s">
-        <v>274</v>
-      </c>
       <c r="Q19" s="13" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="R19" s="13">
         <v>2026</v>
       </c>
       <c r="S19" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="T19" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="T19" s="16" t="s">
+      <c r="U19" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="U19" s="16" t="s">
+      <c r="V19" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="V19" s="16" t="s">
+      <c r="W19" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="W19" s="19" t="s">
+      <c r="X19" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="X19" s="19" t="s">
+      <c r="Y19" s="13" t="s">
         <v>280</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>281</v>
       </c>
       <c r="Z19" s="7"/>
     </row>
@@ -16368,19 +16297,19 @@
         <v>68</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>283</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>88</v>
@@ -16389,55 +16318,55 @@
         <v>89</v>
       </c>
       <c r="I20" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="K20" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="M20" s="15" t="s">
+      <c r="N20" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="N20" s="15" t="s">
+      <c r="O20" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="P20" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="P20" s="13" t="s">
-        <v>289</v>
-      </c>
       <c r="Q20" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R20" s="13">
         <v>2025</v>
       </c>
       <c r="S20" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="T20" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="U20" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="V20" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="W20" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="W20" s="16" t="s">
+      <c r="X20" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="X20" s="16" t="s">
+      <c r="Y20" s="13" t="s">
         <v>295</v>
-      </c>
-      <c r="Y20" s="13" t="s">
-        <v>296</v>
       </c>
       <c r="Z20" s="6"/>
     </row>
@@ -16446,19 +16375,19 @@
         <v>86</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>298</v>
-      </c>
       <c r="F21" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>28</v>
@@ -16467,76 +16396,76 @@
         <v>29</v>
       </c>
       <c r="I21" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="J21" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="K21" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="L21" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="L21" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="M21" s="15" t="s">
+      <c r="N21" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="N21" s="15" t="s">
+      <c r="O21" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="P21" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="Q21" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>306</v>
       </c>
       <c r="R21" s="13">
         <v>2025</v>
       </c>
       <c r="S21" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="T21" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="T21" s="16" t="s">
+      <c r="U21" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="U21" s="16" t="s">
+      <c r="V21" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="W21" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="W21" s="16" t="s">
+      <c r="X21" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="X21" s="16" t="s">
-        <v>312</v>
-      </c>
       <c r="Y21" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z21" s="6"/>
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>314</v>
-      </c>
       <c r="F22" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -16545,72 +16474,72 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="K22" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="L22" s="14" t="s">
         <v>317</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>318</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="P22" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="Q22" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>321</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="T22" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="T22" s="16" t="s">
+      <c r="U22" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="W22" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="U22" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="V22" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="W22" s="16" t="s">
+      <c r="X22" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="X22" s="16" t="s">
-        <v>325</v>
-      </c>
       <c r="Y22" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>327</v>
-      </c>
       <c r="F23" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>28</v>
@@ -16619,29 +16548,29 @@
         <v>29</v>
       </c>
       <c r="I23" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>329</v>
-      </c>
       <c r="K23" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="O23" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="O23" s="13" t="s">
+      <c r="P23" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="Q23" s="13" t="s">
         <v>332</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>333</v>
       </c>
       <c r="R23" s="13">
         <v>2026</v>
@@ -16650,43 +16579,43 @@
         <v>50</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U23" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="V23" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="W23" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="W23" s="16" t="s">
+      <c r="X23" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="X23" s="16" t="s">
-        <v>337</v>
-      </c>
       <c r="Y23" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>339</v>
-      </c>
       <c r="F24" s="13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -16695,76 +16624,76 @@
         <v>29</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="M24" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="N24" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="N24" s="15" t="s">
+      <c r="O24" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="P24" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>343</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>344</v>
       </c>
       <c r="R24" s="13">
         <v>2026</v>
       </c>
       <c r="S24" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="T24" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="T24" s="16" t="s">
-        <v>346</v>
-      </c>
       <c r="U24" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="V24" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="V24" s="16" t="s">
-        <v>346</v>
-      </c>
       <c r="W24" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>348</v>
-      </c>
       <c r="F25" s="13" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -16773,76 +16702,76 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="K25" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="M25" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="K25" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="M25" s="15" t="s">
+      <c r="N25" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="N25" s="15" t="s">
+      <c r="O25" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="P25" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="P25" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>355</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="T25" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="U25" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="V25" s="16" t="s">
+      <c r="W25" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="W25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="X25" s="16" t="s">
-        <v>361</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>364</v>
-      </c>
       <c r="F26" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>28</v>
@@ -16851,31 +16780,31 @@
         <v>29</v>
       </c>
       <c r="I26" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="K26" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="M26" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="M26" s="15" t="s">
+      <c r="N26" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="N26" s="15" t="s">
+      <c r="O26" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="P26" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="Q26" s="13" t="s">
         <v>370</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>371</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -16887,19 +16816,19 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="V26" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="W26" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="W26" s="16" t="s">
+      <c r="X26" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="X26" s="16" t="s">
-        <v>375</v>
-      </c>
       <c r="Y26" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
@@ -16908,19 +16837,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="D27" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -16929,25 +16858,25 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="K27" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="L27" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>425</v>
-      </c>
       <c r="M27" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="N27" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="N27" s="15" t="s">
+      <c r="O27" s="13" t="s">
         <v>379</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>380</v>
       </c>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -16959,7 +16888,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
@@ -16968,19 +16897,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="D28" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -16989,55 +16918,55 @@
         <v>29</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K28" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L28" s="14" t="s">
         <v>465</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="M28" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="P28" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="M28" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="N28" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>467</v>
-      </c>
       <c r="Q28" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="R28" s="13">
         <v>2026</v>
       </c>
       <c r="S28" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="T28" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="T28" s="13" t="s">
-        <v>397</v>
-      </c>
       <c r="U28" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="V28" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="W28" s="28" t="s">
         <v>512</v>
       </c>
-      <c r="V28" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="W28" s="28" t="s">
-        <v>514</v>
-      </c>
       <c r="X28" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
@@ -17046,19 +16975,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="D29" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E29" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>382</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>383</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -17067,49 +16996,49 @@
         <v>29</v>
       </c>
       <c r="I29" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="K29" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="J29" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="K29" s="14" t="s">
+      <c r="L29" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="P29" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="O29" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>470</v>
-      </c>
       <c r="Q29" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="T29" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="T29" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13"/>
       <c r="W29" s="13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="X29" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
@@ -17118,19 +17047,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="D30" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E30" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>386</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>28</v>
@@ -17139,45 +17068,45 @@
         <v>29</v>
       </c>
       <c r="I30" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="K30" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="J30" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>473</v>
-      </c>
       <c r="L30" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="21" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="T30" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="T30" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="U30" s="13"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z30" s="6"/>
     </row>
@@ -17186,19 +17115,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="D31" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>28</v>
@@ -17207,49 +17136,49 @@
         <v>29</v>
       </c>
       <c r="I31" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="K31" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="L31" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="M31" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="P31" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="L31" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="N31" s="15" t="s">
+      <c r="Q31" s="13" t="s">
         <v>421</v>
-      </c>
-      <c r="O31" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q31" s="13" t="s">
-        <v>422</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="T31" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="T31" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
@@ -17258,44 +17187,44 @@
         <v>40</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C32" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="G32" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="H32" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="I32" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="J32" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="K32" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>394</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -17303,21 +17232,21 @@
         <v>2026</v>
       </c>
       <c r="S32" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="T32" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="T32" s="13" t="s">
-        <v>397</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="X32" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="X32" s="13" t="s">
-        <v>399</v>
-      </c>
       <c r="Y32" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Z32" s="6"/>
     </row>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72D64B3-2CC6-4743-BCAB-F661C8E2E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36FF8B1-78BF-4695-B49D-2DFEEDE56E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="633">
   <si>
     <t>地圖編號</t>
   </si>
@@ -325,22 +325,7 @@
     <t>main-06</t>
   </si>
   <si>
-    <t>https://clab.org.tw/unit/future-vision-lab/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/TCCLAB.ORG/?locale=zh_TW</t>
-  </si>
-  <si>
     <t>artist-06</t>
-  </si>
-  <si>
-    <t>GeodesicDome+3V+1a - Architectural Plans</t>
-  </si>
-  <si>
-    <t>Mixed media; dimensions and configuration variable depending on site</t>
-  </si>
-  <si>
-    <t>This small-scale DOME framework uses steel tubing as its structural support and is composed of seven different lengths of white powder-coated steel pipes. Each pipe is labeled with a letter for easy identification. The structure is assembled and secured with M10 hex-socket bolts, allowing the individual tubes to connect into a stable spherical framework.</t>
   </si>
   <si>
     <t>07</t>
@@ -407,28 +392,6 @@
   </si>
   <si>
     <t>Ho Hsin-Yuan works across new media, interactive installation, and interdisciplinary practice, examining how technological media reshape perception, bodily experience, and relationships with the surrounding environment. Beginning with everyday observations and personal sensations, she combines digital technologies, spatial installation, and participatory interaction to translate abstract perceptual states into forms that can be seen and experienced. Her projects and research have been presented through technology-art and interdisciplinary programmes, and her ongoing practice develops at the intersection of artistic experimentation and technical processes, with an emphasis on how audiences encounter and participate in mediated environments.</t>
-  </si>
-  <si>
-    <t>展演
-2026｜FUTURE VISION LAB 沉浸式影音工作坊, 臺灣當代文化實驗場, 臺北
-2025｜LAB X 藝術跨域實驗平台「2025 TSMC╳NTT+ 青年創作工作室」, 臺中國家歌劇院, 臺中
-2025｜關渡光藝術節《幻響》 , 科技藝術館, 臺北
-2025｜永晝海濱美術館雙年展《水啦》, 正濱漁港, 基隆
-2024｜Aavistus Festival 2024 - Off The Wall, 赫爾辛基, 芬蘭
-2023｜第十八屆臺北數位藝術節 :A-Real Engine《人造星系》, 國立臺灣科學教育館, 臺北
-2023｜聲響藝術節《人造星系》, 臺灣當代文化實驗場, 臺北
-2022｜關渡光藝術節《濟濟》, 關渡中港河碼頭, 臺北</t>
-  </si>
-  <si>
-    <t>GROUP EXHIBITIONS
-2026 | FUTURE VISION LAB－Immersive Audiovisual Workshop / Taiwan Contemporary Culture Lab, Taipei, Taiwan
-2025 | LAB X Arts Interdisciplinary Platform「2025 TSMC X NTT+ The Young Artists' Atelier」/ National Taichung Theater, Taichung ,Taiwan
-2025 | Kuan Du Light Art Festival“Illusonic” / Center for the Art &amp; Technology, Taipei, Taiwan
-2025 | Zhengbin Art Gallery Biennale“Water Lives Here”, Keelung, Taiwan
-2024 | Aavistus Festival 2024“Off The Wall”, Helsinki, Finland
-2023 | 18th Digital Art Festival Taipei: A-Real Engine“Artificial Galaxy”/ National Taiwan Science Education Center, Taipei, Taiwan
-2023 | C-LAB Sound Festival“Diversonics”-“Artificial Galaxy” / Taiwan Contemporary Culture Lab, Taipei, Taiwan
-2022 | Kuan Du Light Art Festival“Ji-Ji” / Kuan Du Zhong Gong River Wharf, Taipei, Taiwan</t>
   </si>
   <si>
     <t>https://hohsinyuan.notion.site/-profile</t>
@@ -914,9 +877,6 @@
     <t>Taiwan / France</t>
   </si>
   <si>
-    <t>藝術團體「超級浪」2022年成立於臺北萬華，成員以文化部2020年「MIT」計畫獲選藝術家為基礎，並陸續加入獨立藝術家與策展人。團名回應當代藝術的變異與不確定性，將藝術實踐帶入日常生活與現實環境。團隊透過展覽、駐村、研究、工作坊與公共活動，串聯不同文化背景的創作者，探索藝術、地方與社會的關係，計畫遍及臺灣、韓國、蒙古、泰國及歐洲等地。</t>
-  </si>
-  <si>
     <t>Hyper Wave is an art collective established in Taipei’s Wanhua District in 2022. Its founding members were artists selected for Taiwan’s Ministry of Culture 2020 MIT programme, with independent artists and curators joining over time. The collective’s name reflects the shifting and uncertain nature of contemporary art, and its practice brings artistic experimentation into everyday life and real-world contexts. Through exhibitions, residencies, research projects, workshops, and public programmes, Hyper Wave connects practitioners from different cultural backgrounds and explores relationships among art, place, and society. Its projects have taken place across Taiwan, South Korea, Mongolia, Thailand, and Europe.</t>
   </si>
   <si>
@@ -1332,9 +1292,6 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>Félix-Antoine Morin 是加拿大聲音與視覺藝術家，創作橫跨電聲音樂、錄像、圖像樂譜與沉浸式媒體，探討聲音、影像與感知如何將現實轉化為詩性的感官經驗。他從傳統與神聖音樂汲取靈感，以儀式的過程性邏輯發展持續變化的多感官作品，並關注心理聲學、尺度與量級，以及聲音與影像之間的主觀感知關係，在現實與抽象之間建構流動的感官空間。</t>
-  </si>
-  <si>
     <t>Félix-Antoine Morin is a Canadian sound and visual artist working across electroacoustic composition, video, graphic scores, and immersive media. His practice explores how sound, image, and perception can transform reality into poetic sensory experience. Drawing inspiration from traditional and sacred music, Morin approaches composition through the processual logic of ritual, creating multisensory works that remain in motion and transformation. His work also investigates psychoacoustics, relationships of scale and magnitude, and the subjective interactions that emerge between sound and image. Through these concerns, he constructs fluid perceptual spaces situated between concrete reality and abstraction.</t>
   </si>
   <si>
@@ -1348,9 +1305,6 @@
   </si>
   <si>
     <t>Audiovisual Performance</t>
-  </si>
-  <si>
-    <t>Félix-Antoine Morin（音樂）與 Alexandre Larose（影像）之視聽合作作品</t>
   </si>
   <si>
     <t>Audiovisual collaboration between Félix-Antoine Morin (music) and Alexandre Larose (video)</t>
@@ -12507,227 +12461,6 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>「未來視覺實驗室」在台灣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> context </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>下主要指由臺灣當代文化實驗場（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C-LAB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>）所推動的科技媒體實驗平台，特別是其專注於沉浸式影像的「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FUTURE VISION LAB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>」。該平台打造了穹頂劇場（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DOME</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>），利用球形投影技術探索未來視覺與科技藝術的極限，具備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>＆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>的能量，整合影像運算、拼接、軟硬體系統、環繞音場及建築結構設計等技術，除策劃展演及陪伴創作者以外，亦進行各項跨域實驗，持續開創未來視覺及創新科技的新視野。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>這個小型的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DOME</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>球形骨架設計上使用金屬鋼管作為支撐，一共有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>種不同長度的白色烤漆鋼管組成，每一隻白色鋼管上為了方便辨識，進行了字母的標籤記號，設計以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>內六角螺絲將每一支鋼管進行連接並固定，達到穩定的結構。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>複合媒材</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>FUTURE VISION LAB is a technology and media experimentation platform initiated by the Taiwan Contemporary Culture Lab (C-LAB), with a particular focus on immersive moving-image practices. At its core is DOME, a dome theater that uses spherical projection technology to explore new possibilities in future visual culture and technological art.
-With strong R&amp;D capabilities, the platform integrates technologies including image processing, projection stitching, hardware and software systems, surround sound, and architectural design. In addition to presenting exhibitions and performances and supporting creators in developing new works, FUTURE VISION LAB facilitates a wide range of interdisciplinary experiments, continually expanding new horizons for future visual practices and innovative technologies.</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
       <t>沈宇軒，</t>
     </r>
     <r>
@@ -14310,10 +14043,1317 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
       </rPr>
+      <t>未來視覺實驗室著重對未來視覺議題的探討與突破，自</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年起推出實驗展演計畫「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>FUTURE VISION LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」，以穹頂構築（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DOME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）概念打造超高解析沉浸式系統。實驗室更具備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>＆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>能量，整合影像運算、拼接、軟硬體系統、環繞音場及建築結構設計等技術，除策劃展演及陪伴創作者以外，亦進行各項跨域實驗，持續開創未來視覺及創新科技的新視野。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>C-LAB’s Future Vision Lab focuses on exploring the issue of the future vision. Since 2020, it has launched the experimental program FUTURE VISION LAB, which is an immersive dome theater exhibition and performance program, equipped with a high-resolution video and spatial sound environment. 
+The Lab also carries R&amp;D capacity, integration of image warping, edge blending, mapping, hardware-software system, spatial audio and architectural structure design. In addition to curating programs and working closely with creators, it also conducts cross-disciplinary experiments, continuously expanding the horizons in future vision practices and emerging technologies.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">展演
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FUTURE VISION LAB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>沉浸式影音工作坊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺灣當代文化實驗場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">臺北
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">LAB X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術跨域實驗平台「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025 TSMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>╳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NTT+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>青年創作工作室」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺中國家歌劇院</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">臺中
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜關渡光藝術節《幻響》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>科技藝術館</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">臺北
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜永晝海濱美術館雙年展《水啦》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>正濱漁港</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">基隆
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Aavistus Festival 2024 - Off The Wall, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>赫爾辛基</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">芬蘭
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜第十八屆臺北數位藝術節</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :A-Real Engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《人造星系》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>國立臺灣科學教育館</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">臺北
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜聲響藝術節《人造星系》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺灣當代文化實驗場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">臺北
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜關渡光藝術節《濟濟》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>關渡中港河碼頭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺北</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GROUP EXHIBITIONS
+2026 | FUTURE VISION LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immersive Audiovisual Workshop / Taiwan Contemporary Culture Lab, Taipei, Taiwan
+2025 | LAB X Arts Interdisciplinary Platform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025 TSMC X NTT+ The Young Artists' Atelier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ National Taichung Theater, Taichung ,Taiwan
+2025 | Kuan Du Light Art Festival“Illusonic” / Center for the Art &amp; Technology, Taipei, Taiwan
+2025 | Zhengbin Art Gallery Biennale“Water Lives Here”, Keelung, Taiwan
+2024 | Aavistus Festival 2024“Off The Wall”, Helsinki, Finland
+2023 | 18th Digital Art Festival Taipei: A-Real Engine“Artificial Galaxy”/ National Taiwan Science Education Center, Taipei, Taiwan
+2023 | C-LAB Sound Festival“Diversonics”-“Artificial Galaxy” / Taiwan Contemporary Culture Lab, Taipei, Taiwan
+2022 | Kuan Du Light Art Festival“Ji-Ji” / Kuan Du Zhong Gong River Wharf, Taipei, Taiwan</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>展演</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">FUTURE VISION LAB @ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>晴空季</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺灣當代文化實驗場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺北</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜「穹形語法」放映單元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, 2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>林茲電子藝術節</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2020 - 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FUTURE VISION LAB , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺灣當代文化實驗場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺北</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP EXHIBITIONS
+2026 | FUTURE VISION LAB @ Skyward / Taiwan Contemporary Culture Lab, Taipei, Taiwan
+2025 | Spherical Syntax, Ars Electronica 2025 / 2025 Ars Electronica , Austria
+2020 - 2026 | FUTURE VISION LAB / Taiwan Contemporary Culture Lab, Taipei, Taiwan</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fvl.clab.org.tw/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Facebook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.facebook.com/CLAB.FUTUREVISIONLAB 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instagram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.instagram.com/clab.futurevisionlab 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Threads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.threads.com/@clab.futurevisionlab?hl=zh-tw </t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_2</t>
+  </si>
+  <si>
+    <t>main-06_3</t>
+  </si>
+  <si>
+    <t>main-06_5</t>
+  </si>
+  <si>
+    <t>FUTURE VISION LAB Mini Dome</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉浸式影音體驗空間</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mixed media</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immersive Audio-Visual Experience Space</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Echoing the theme "Grey Automata" of the 2026 Taipei Digital Art Festival, C-LAB Future Vision Lab presents a curated selection of dome projection works created using AI and generative techniques, showcased inside the lab’s mini dome. Through this lightweight yet highly flexible immersive dome venue, diverse and compelling immersive creations by local and international artists are brought into the festival’s thematic framework. This initiative not only offers audiences an accessible entry point to experience immersive art for the first time, but also enables immersive imagery to be viewed, felt, and shared across various scales and contexts—further expanding the connection between digital art and the public.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>穹體</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Dome Entity</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>If architecture is frozen time, algorithms set structure back into motion. Utilizing the physical geometry of the FVL Dome as its generative foundation, The Dome Entity leverages real-time StreamDiffusion to unfold a linear imagination stretching from the past into the future.
+Through continuous diffusion, the once-stable dome perpetually grows, morphs, and reconfigures, compressing and unfolding vast temporal data to form a dynamic space between physical architecture and virtual imagination. Ceasing to be a mere projection screen, the dome evolves into a living organism bridging eras—inviting viewers inside a colossal vessel of consciousness that breathes, remembers, and dreams.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝爾蓋．普羅科菲耶夫</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sergey PROKOFYEV</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>謝爾蓋．普羅科菲耶夫是一位建築師與影像工作者，其作品以融合了建築概念與沉浸式的說故事方法聞名。從兩大領域的豐富經驗出發，普羅科菲耶夫擅長運用創新技術推移影像敘事與傳統溝通工具之間的分界，並融合多種影像手法，將虛構建物再現得栩栩如生，精巧地創造出挑戰感官、刺激觀者思考的沉浸式電影。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">透過與神經科學家之間的合作，普羅科菲耶夫專注於研究城市中人類感官與行為機制的運作過程。其沉浸式作品曾於各類國際影展中得到肯定並獲獎。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>影像：謝爾蓋．普羅科菲耶夫
+音樂：亞歷山大．穆爾</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Félix-Antoine Morin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是加拿大聲音與視覺藝術家，創作橫跨電聲音樂、錄像、圖像樂譜與沉浸式媒體，探討聲音、影像與感知如何將現實轉化為詩性的感官經驗。他從傳統與神聖音樂汲取靈感，以儀式的過程性邏輯發展持續變化的多感官作品，並關注心理聲學、尺度與量級，以及聲音與影像之間的主觀感知關係，在現實與抽象之間建構流動的感官空間。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Félix-Antoine Morin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（音樂）與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Alexandre Larose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（影像）之視聽合作作品</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sergey PROKOFYEV, architect and filmmaker, is renowned for his integration of architectural concepts with immersive storytelling. With extensive experience in both fields, Sergey specializes in using innovative techniques to push the boundaries of cinematic narrative and traditional communication tools. He incorporates a range of cinematic methods to bring architectural representations to life, crafting immersive movies that challenge perceptions and transport viewers to thought-provoking worlds.
+ Through collaboration with neuroscientists, he focused on studying the processes associated with the mechanisms of human perception and behavior in the city. His immersive projects have been recognized and awarded at various international film festivals.
+ Film by Sergey PROKOFYEV
+Music by Alexander MUELLl</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.prokofyevsergey.com/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.instagram.com/sergprokofyev/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>全球烏托邦中的在地反烏托邦</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Local Dystopias in the Global Utopia</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>在無止境延伸的沙漠中，獨特的觀影經驗透過DOME的多個銀幕展開，每一面銀幕都呈現了一個不同的建築故事。
+遊走於三個反烏托邦世界中，我們首先探索的是「摩天大樓狂熱」，這是一座廢棄的村莊，其中木造摩天大樓的複製品由氣球乘托而漂浮著，象徵了脆弱的希望。下一個世界「末日之城」將我們帶入無人之境，場景的塑造靈感來自畫家尼古拉斯．洛里奇（Nicholas Roerich）的作品。第三個建築故事的世界是「虛實間的靈薄獄」，這個令人困惑的數位環境持續地受到以人類情緒為基礎所打造的合成引擎（synthetic engines）刺激，身處其中便如同經歷著集體意識的夢境。
+這件沉浸式影像挑戰人們的感官，模糊了想像的建築與現實間的界線。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>In a sprawling desert, a unique cinematic experience unfolds through multiple dome screens, each depicting a distinct architectural tale.
+Journeying through three dystopian worlds, we first explore “High Rise Cult,” a forsaken village where wooden skyscraper replicas are buoyed by balloons, symbolizing fragile hopes. Next, “The Doomed City” draws us into a city birthed in no man’s land, influenced by a painting by Nicholas Roerich. The third architectural tale is “Phygital Limbo.”. A perplexing digital environment is continuously stimulated by synthetic engines based on human emotions. Being here is akin to experiencing a conscious collective dream.
+This immersive film challenges perceptions, blurring the boundaries of architectural imagination and reality.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳秉聖</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺灣藝術家、聲音藝術家、媒體藝術家，國立清華大學專任講師。創作橫跨聲音藝術、音像演出與媒體裝置。作品多次入選台北數位藝術節、國際媒體藝術節、及相關獎項；創作發表於台灣雙年展、台灣國際光影藝術節、台灣燈會、月津港燈節、台北白晝之夜、失聲祭等活動，作品及藝術駐村在亞洲、歐洲和北美地區的聯展和藝術節中展出。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pingshengwu.com/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.instagram.com/pingsheng_wu/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈魂的副翼：穹丘</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aileron of Soul: DOMOUND</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>《靈魂的副翼：穹丘》是對於人工智慧作為一種工具的假設提問出發，所延伸的視覺刺激與探索。它提供了一種非人類視覺的組構方式，如魔法般地將關鍵字嵌入影像與聲響中。作品試圖從建築學、地質學與天文學等圖像資料切入，從人工智慧所產出的視覺架構，探討AI視覺所描述的人類知識樣貌，並突顯非人類視覺認知的違和感。藉此提問人工智慧的影像產出，是引領人類靈魂突破現有認知引導的副翼，還是主導著一張張隱藏著等價交換的契約，而我們並不知道實際上背負的交換內容。作品以人類視聽感官為主題，從神話、宇宙探勘、科技、自然、AI等子題中，提煉出一種以聲音與影像為主體的敘事，藉由音像作品的特性，延展或凍結流轉的時間感，重新組織出一種視聽交融、精神穿越的感官體驗。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aileron of Soul: DOMOUND questions the assumption of AI as an instrument, and extends such questioning into visual stimulation and exploration. It offers a composition approach based on non-human vision, and magically embeds keywords into images and sounds. The work utilizes image data of architecture, geology, and astronomy as an entry point, and employs an AI-produced visual structure to investigate the contour of human knowledge perceived by AI vision, while highlighting an out-of-place feeling resulting from non-human visual cognition. Through this work, the artist questions about AI-produced imagery: is it an aileron that is able to guide the human soul and bring about cognitive breakthroughs? Or does it hide behind quid pro quo contracts without us knowing what these contracts stipulate? Themed on human senses of vision and hearing, this work weaves a narrative of sounds and images through the sub-themes of myth, cosmic prospecting, technology, nature, and AI, using the characteristics of audiovisual works to extend or freeze the flowing sense of time, while re-organizing a sensory experience of vision-hearing integration and spiritual transcendence.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>「灰姑娘的故事裡這麼說道：『好豆進鍋裡，壞豆進肚子裡。』但，究竟由誰來決定好與壞？」</t>
     </r>
     <r>
@@ -14322,6 +15362,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -14330,21 +15371,297 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>《</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EZ Quality Sorter V2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>》是一台具工業風格的機器，能自動對豌豆種子進行品質分類與篩選。展覽現場邀請觀者透過光學裝置檢視單顆豌豆，並按壓綠色或紅色按鈕為其品質定調。觀者的這些決定將轉化為影像數據，成為機器隨後進行自動化分揀的依據。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本作品旨在探討人類的主觀判斷如何被制度化、並嵌入看似客觀且「智慧」的系統之中；同時也拋出反思：當複雜的現實經驗被精簡為非黑即白的二元分類時，我們將面臨什麼樣的景況？</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未來視覺實驗室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穹頂實驗計劃</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>複合媒材</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C-LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未來視覺實驗室呼應「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>臺北數位藝術節」之主題「灰色自動體」，策劃邀請以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、生成式等創作手法之穹頂影像作品，使用實驗室之</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mini dome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>參與本次展呈。藉由輕量且具高度彈性的沉浸式穹頂場域，將國內外藝術家多元而精彩的沉浸式內容創作帶入藝術節主題脈絡，不僅提供觀眾親近並初次體驗沉浸式藝術的機會，也讓沉浸式影像得以在不同尺度與情境中被觀看、感知與交流，進一步拓展數位藝術與公眾之間的連結。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>如果建築是凝固的時間，演算法則讓結構重新流動。《穹體》以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FVL Dome </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的物理結構為基底，透過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> StreamDiffusion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>即時生成技術，在球幕上展開從「過去」邁向「未來」的線性想像。
+在連續擴散（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）過程中，原本穩定的穹頂於演算法中持續生長、變形與重構，將龐大的時間數據壓縮並即時展開，形成介於真實建築與虛擬想像間的動態空間。穹頂不再只是影像容器，而是連結不同時間想像的生命體；觀者仰望的不再只是銀幕，而是進入一個正在呼吸、記憶與做夢的巨大意識容器。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hello World x Dimension Plus x Hello Edo! x Kivi x Mr. Skin x LIM Giong</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>《</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>EZ Quality Sorter V2</t>
-    </r>
+      <t>台灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / 日本</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taiwan / Japan</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -14353,7 +15670,825 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>》是一台具工業風格的機器，能自動對豌豆種子進行品質分類與篩選。展覽現場邀請觀者透過光學裝置檢視單顆豌豆，並按壓綠色或紅色按鈕為其品質定調。觀者的這些決定將轉化為影像數據，成為機器隨後進行自動化分揀的依據。</t>
+      <t>初未來</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>超維度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>江戶未來世</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">x Kivi x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>賴皮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>林強</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_4/01.webp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_4/03.webp</t>
+  </si>
+  <si>
+    <t>main-06_4/04.webp</t>
+  </si>
+  <si>
+    <t>main-06_4/05.webp</t>
+  </si>
+  <si>
+    <t>新摩登時代</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEW MODERN TIMES</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>《新摩登時代》當臺灣文化意象撞擊 AI 世代的數位狂想！
+《新摩登時代》是一部以臺灣文化為核心的「奇想生成式沉浸影音作品」。它打破現實邊界，將自然環境、工業製造、廟會遶境、夜市印象，乃至於 AI 神話與未來太空，重新編織成一段幽默詼諧卻充滿啟發的視覺史詩。
+在巨大的穹形場域之下，你將感受 AI 影像生成的狂放力量，體驗集結「惡搞、創造、融合」於一身的文化衝擊。由初未來領銜製作，集結科技藝術代表超維度 與 AI 影像先鋒江戶未來世。音樂陣容更是夢幻：從排灣族天籟歌手 Kivi、潮流電音 DJ 賴皮，到傳奇音樂大師林強。頂尖藝術家跨界聯手，打造出這場橫跨部落與宇宙、傳統與未來的《新摩登時代》。
+本案獲文化內容策進院「2025年文化科技內容聯合徵件：穹頂投影展演計畫支持」。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEW MODERN TIMES: A Generative Audio-Visual Odyssey!
+When Taiwanese cultural heritage meets the digital frenzy of the AI generation, a sensory storm like no other is about to sweep through C-LAB! NEW MODERN TIMES is a generative immersive masterpiece centered on the soul of Taiwan. It shatters the boundaries of reality, weaving natural landscapes, industrial marvels, traditional temple processions, and neon-lit night markets with AI mythology and deep-space futures into a witty, thought-provoking visual epic.
+Under the massive immersive dome, you will witness the raw, untamed power of AI-generated visuals—a cultural collision of mischief, radical creativity, and artistic fusion. The visionaries behind the storm produced by Hello World, featuring the groundbreaking visual artistry of Dimension Plus and AI pioneers Hello Edo!. The soundtrack is a dream collaboration: from the celestial voice of Paiwan singer Kivi and the high-octane energy of  Mr. Skin, to the legendary soundscapes of electronic pioneer LIM Giong. Together, they bridge tribes and the cosmos, tradition and the future.
+This project is supported by TAICCA’s 2025 Innovative Co-Production Program: Dome Projection</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>初未來</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>超維度</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>江戶未來世</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kivi</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>賴皮</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>林強</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_4/06.webp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>策展人：蔡宏賢 
+影像創作：江戶未來世、超維度
+音樂：DJ賴皮、Kivi、林強
+編曲：劉詩偉
+製作團隊：初未來
+製作人：蔣孟涵、王思雅
+影像工程：李子臻、黃冠睿 
+發行單位：初未來 
+指導單位：文化部、文化內容策進院</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Curator: Escher TSAI
+Visual Artist: Hello Edo!, Dimension Plus
+Music Artist: Mr. Skin, Kivi, LIM Giong
+Arranger: LIU Shih-Wei 
+Production Team: Hello World
+Producer: Monique CHIANG, WANG Szu-Ya 
+Visual Enginner: LEE Tzu-Chen, HUANG K.Jui
+Presenter: Hello World
+Advisor: MOC, TAICCA</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Facebook:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> https://www.facebook.com/helloworldfuturearts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instagram:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> https://www.instagram.com/helloworld_futurearts/</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hello World</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hello Edo!</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dimension Plus</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mr. Skin</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Giong Lim</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ping-Sheng Wu</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ping-Sheng Wu is a Taiwanese artist working in sound and media, and a Lecturer at the Interdisciplinary Program of Technology and Art, National Tsing Hua University. His work spans sound art, audiovisual performance, and media installation. His works have been selected for the Taipei Digital Art Festival, international media art festivals, and related awards; presented at the Taiwan Biennial, Taiwan International Light Festival, Taiwan Lantern Festival, Yuejin Lantern Festival, Nuit Blanche Taipei, and Lacking Sound Festival, among others. His work and artist residencies have taken him to group exhibitions and art festivals across Asia, Europe, and North America.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>一個對於AI人工智能圖像生產技術深感興趣的創作團體，團員來自亞洲各地，熱衷於AI人工智能的影像創作，喜愛藝術、文化、機械、賽博格等未來想像的景致。 作品曾於2025 臺中國家歌劇院 Arts NOVA 「摩登時代」、「新世紀浮世繪」、2024「你好，人類」、台灣文化科技大會主題展「G.A.M.E.」、「文化燉」芬蘭站及香港站、2023「香港微波新媒體國際藝術節」展出。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>排灣族唱作人 kivi 來自屏東滿洲鄉八瑤部落，外型宛如 FKA Twigs 般時尚。初聽見她的聲音，也總讓人驚艷她瘦小身軀裡蘊含的巨大能量。kivi 輕柔婉轉的歌聲勾勒出不同世代原住民群體生活的記憶共感，像是老人家溫柔的叮嚀或祝福。這樣的特質讓她擁有眾多粉絲及數支 YouTube 破百萬點閱影片。2022年6月發行第一張族語創作專輯《 分水嶺 Padiyudr 》，入圍第 34 屆金曲獎 最佳原住民專輯、最佳原住民歌手、年度專輯等三大獎。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>賴皮 MR.SKIN不僅是各種音樂競賽的常勝軍，更是有「高雄最嗨夜店」之稱Cocco &amp; Co.的創辦人，以及知名夜店MUSE的音樂總監。閒不下來的賴皮平時除了創作和演出，更經常舉辦派對活動，在眾多五光十色的場域中擔任多重角色。賴皮為了抗爭夜店不能放中文歌曲這件事，於是創立了「國語作業簿」，「國語作業簿是想喚醒大家對於自己語言的認同。」。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>音樂工作者，主要製作電影和紀錄片配樂，也曾參與短片、廣告、舞蹈、燈光裝置藝術、VR等配樂，嘗試與各領域的藝術家交流合作，近期探索抽象電子聲響與實驗及環境音樂創作，虛實幻影，戲夢人生，應作如是觀。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>An Asia-based new media production company specializing in curating, producing, and promoting innovative works and artists with the goal of building an international platform for future art. Renowned for its expertise in international crossover collaborations, Hello World brings together leading Asian curators and producers in the field of technological art. In addition to representing artists, Hello World curates immersive exhibitions and fosters interdisciplinary collaborations at major international venues such as SXSW, MUTEK, MOCA Taipei, National Taichung Theater, National Taiwan Museum of Fine Arts, and West Kowloon Cultural District.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>A new media art collective based in Taiwan and Hong Kong, exploring the relationship between art and science through cross-disciplinary experiments. Their works mix old and new media to address social, cultural, and ethical issues. By combining traditional and contemporary mediums, they aim to reflect on the impact of technology while pushing creative boundaries. Notable awards include the Best Design of the Year of Taiwan Golden Pin Design Award, Tokyo TDC, Asia Digital Arts Awards Japan and Gold Award of Design for Asia Award Hong Kong, German Design Award 2018 etc.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>A creative collective deeply fascinated by AI-generated imagery. The members come from across Asia, passionate about using artificial intelligence for visual storytelling, drawing inspiration from art, culture, machinery, and futuristic visions of cyborg worlds. Their works have been featured in prominent exhibitions, including Modern Times and New Century Ukiyo-e at NTT Arts NOVA (National Taichung Theater, 2025), 2024 Hello, Human! exhibition, 2024 TTXC《G.A.M.E.》Culture Stew in Finland and Hong Kong, Microwave International New Media Arts Festival (Hong Kong, 2023)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paiwan singer-songwriter Kivi comes from Bayao Village in Manzhou Township, Pingtung, Taiwan. With a fashion-forward presence reminiscent of FKA twigs, she leaves a strong impression both visually and vocally. The first time you hear her sing, it is hard not to be struck by the powerful energy contained within her petite frame.
+Kivi’s soft and lyrical voice evokes shared memories and emotional resonance across generations of Indigenous communities—like a gentle reminder or blessing from an elder. This quality has earned her a devoted following, with several of her YouTube videos surpassing one million views.In June 2022, she released her debut Indigenous-language album Padiyudr, which was nominated for three major awards at the 34th Golden Melody Awards: Best Indigenous Language Album, Best Indigenous Language Singer, and Album of the Year.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mr. Skin is not only a champion in various music competitions but also the founder of the renowned nightclub Cocco &amp; Co. in Kaohsiung, often hailed as the city’s liveliest club. Additionally, he serves as the music director for the famous MUSE nightclub. Constantly creating, performing, and hosting parties, Mr. Skin plays multiple roles across vibrant venues. In response to nightclubs’ restrictions on Mandarin songs, he founded Mandarin Homework, a project aimed at rekindling pride and identity of the mother tongue.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Musicworker. Mainly produces music scores of fiction films and documentaries and has also worked on scores of shorts, commercials, dance performances, light installations and VR; and has tried to collaborate and exchange ideas with artists from various fields. He is exploring abstract electronic tones and experimental and ambient music creation – sailing through reality and imagination, existence and dreams, the way it is to view our life.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉澈</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Che Yeh</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年正式成軍的「初未來」，集結亞洲優秀科技藝術策展人及製作人，以未來藝術生產與科技藝術展覽之專業視野，協助新銳獨立藝術家推展國際跨域整合製作。製作經驗包括：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺中國家歌劇院</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Arts NOVA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「摩登時代」、「新世紀浮世繪」、「靈魂」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SXSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>台灣館「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VS AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>街頭對戰」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VS AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>街頭對戰」世界大賽及國際展出、「你好，人類」、台灣文化科技大會主題「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G.A.M.E.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GIGABYTE AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新紀元，人類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>科技特展」等。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺港新媒體藝術創作團隊，專注藝術創作與科技媒體，擅長應用新媒體結合空間與跨領域的創作。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>澳門設計雙年展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>全場金獎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Macau Design Biennial - Gold Award - "Straw in the wind"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>亞洲具影響力設計獎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>金獎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hong Kong DFA Design for Asia Award - Gold Award </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>台灣金點設計獎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年度最佳設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Taiwan Golden Pin Design Award - 2018 Best Design</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>德國設計獎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> German design award </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>金獎。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taiwan / Hongkong</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>台灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / 香港</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Japan</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>影像藝術家，創作領域包括電影、錄像、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">、劇場、攝影、音像表演。多從影像的產製方式著手，以不同的媒材本質，尋找個人情感或者人類共同經驗，創作出企及集體意識的作品。目前專注於使用影像進入空間敘事的不同可能。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【製作團隊】</t>
     </r>
     <r>
       <rPr>
@@ -14369,11 +16504,439 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>導演：葉澈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>演出：吳靜依</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+3D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>美術：韓希妶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術家：吳冠誼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聲音：劉文奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>造型：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Jonny Lin, Aura Wang @</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>髦髦時髦工作室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攝影助理：王俊為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>歌曲：〈神神〉—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>吳靜依</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A Taiwanese artist who uses video as his creative medium.
+Che has a wide range of works that include video art, films, music videos and theatre.His works draw inspiration from personal experiences and emotion which are all based on production point of view of images. Che uses different types of media to create his works. In doing so, he seeks to express the collective consciousness of human beings through art.
+【Production Team】
+Director: YEH Che
+Talent: Jing WU
+3D Artist: HAN Shi-Shiuan
+AI Artist: Kiki WU
+Sound Supervisor: LIU Wen-Chi
+Stylist: Jonny LIN, Aura WANG @MEOW WARDROBE
+Camera Assistant: WANG Chun-Wei </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yehche.com/ </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Facebook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.facebook.com/scott.yeh.7/ 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instagram:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> https://www.instagram.com/yehche.7/ </t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻幕</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>What a Screen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>本作品旨在探討人類的主觀判斷如何被制度化、並嵌入看似客觀且「智慧」的系統之中；同時也拋出反思：當複雜的現實經驗被精簡為非黑即白的二元分類時，我們將面臨什麼樣的景況？</t>
+      <t>自影像出現以來，我們不斷經歷著觀看裝置的轉化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>電影院、電視機、手機、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>牆、光雕投影……。隨著裝置的更迭，影像也持續變異著自身的比例與身體，同時框架出人類的觀看方式，形塑著我們對世界的想像。
+《幻幕》從影像的「比例」出發，回望影像史中不同畫幅與技術框架所帶來的感知經驗，帶領觀眾在穹頂空間中穿梭於不同時期的影像身體。然而，當我們再次回望這片被光與聲包覆的世界，才發現自己依然被框架其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>在另一種影像的尺幅裡，被觀看、被包圍。
+如同作品中使用的歌曲〈神神〉所唱：「攏咧騙囡仔疕，等嘛等無你」（中譯：都是騙小孩的話，怎麼等都等不到你。），我們始終被影像欺騙與隔絕。螢幕允諾我們進入它的美好世界，卻始終讓我們停留在門外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>在幻幕之中，也在幻幕之外。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Since the birth of the moving image, we have continuously experienced transformations in the devices through which we watch the world — the cinema, the television, the smartphone, the LED wall, and architectural projection. As these technologies evolve, images also mutate: they reshape their own aspect ratios and bodies, while framing how humans see, and how we imagine reality itself.
+What a Screen! begins with the notion of the ratio. It revisits the sensory experiences shaped by different aspect ratios and technical frameworks throughout the history of images, guiding the audience through a dome where various temporal bodies of the image coexist. Yet, when we look back at this luminous, resonant space, we realize that we remain enclosed within another frame — being watched, contained, and defined by the very image we enter.
+As the song Await in the work sings: “You’re only fooling kids, but I wait — waiting for your never-coming.” We are forever deceived and distanced by images.The screen promises us entry into its beautiful world, yet we are always left outside —watching the screen, and never within it.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>藝術團體「超級浪」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年成立於臺北萬華，成員以文化部</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」計畫獲選藝術家為基礎，並陸續加入獨立藝術家與策展人。團名回應當代藝術的變異與不確定性，將藝術實踐帶入日常生活與現實環境。團隊透過展覽、駐村、研究、工作坊與公共活動，串聯不同文化背景的創作者，探索藝術、地方與社會的關係，計畫遍及臺灣、韓國、蒙古、泰國及歐洲等地。</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -14382,7 +16945,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14507,6 +17070,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -14530,7 +17111,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -14605,6 +17186,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -14821,7 +17415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
@@ -14850,7 +17444,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -14933,7 +17527,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -14942,16 +17536,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -15009,7 +17603,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -15024,10 +17618,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -15087,7 +17681,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -15102,10 +17696,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -15115,7 +17709,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -15136,10 +17730,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -15160,7 +17754,7 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>70</v>
@@ -15178,10 +17772,10 @@
         <v>74</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>75</v>
@@ -15238,10 +17832,10 @@
         <v>87</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>88</v>
@@ -15250,16 +17844,16 @@
         <v>89</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>90</v>
@@ -15274,16 +17868,16 @@
         <v>93</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>94</v>
@@ -15291,11 +17885,11 @@
       <c r="V6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="W6" s="27" t="s">
-        <v>545</v>
+      <c r="W6" s="16" t="s">
+        <v>571</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="Y6" s="13" t="s">
         <v>87</v>
@@ -15316,10 +17910,10 @@
         <v>97</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -15327,43 +17921,53 @@
       <c r="H7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>492</v>
+      <c r="I7" s="29" t="s">
+        <v>531</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="O7" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="P7" s="13" t="s">
-        <v>101</v>
+        <v>572</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="R7" s="13"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="25" t="s">
-        <v>494</v>
+        <v>543</v>
+      </c>
+      <c r="R7" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="T7" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>573</v>
       </c>
       <c r="V7" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="W7" s="24" t="s">
-        <v>493</v>
+        <v>545</v>
+      </c>
+      <c r="W7" s="16" t="s">
+        <v>574</v>
       </c>
       <c r="X7" s="16" t="s">
-        <v>103</v>
+        <v>547</v>
       </c>
       <c r="Y7" s="13" t="s">
         <v>97</v>
@@ -15372,636 +17976,596 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="12" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>486</v>
+        <v>481</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>472</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>106</v>
+        <v>505</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>109</v>
+        <v>29</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>531</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>111</v>
+        <v>532</v>
+      </c>
+      <c r="K8" s="23"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="31" t="s">
+        <v>537</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>112</v>
+        <v>538</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>113</v>
+        <v>481</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>114</v>
+        <v>548</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>115</v>
+        <v>549</v>
+      </c>
+      <c r="R8" s="13">
+        <v>2026</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="X8" s="16" t="s">
-        <v>119</v>
+        <v>206</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="X8" s="13" t="s">
+        <v>550</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>105</v>
+        <v>539</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>121</v>
+        <v>481</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>122</v>
+        <v>551</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>123</v>
+        <v>89</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>553</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>126</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
       <c r="M9" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>128</v>
+        <v>557</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>558</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>129</v>
+        <v>481</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>130</v>
+        <v>559</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>131</v>
+        <v>560</v>
       </c>
       <c r="R9" s="13">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="U9" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="V9" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="W9" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>137</v>
+        <v>206</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="X9" s="13" t="s">
+        <v>562</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>121</v>
+        <v>540</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>485</v>
+        <v>481</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>563</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>140</v>
+        <v>603</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>143</v>
+        <v>564</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>146</v>
+        <v>604</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>566</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>147</v>
+        <v>481</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>148</v>
+        <v>567</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>148</v>
+        <v>568</v>
       </c>
       <c r="R10" s="13">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="U10" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="V10" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="W10" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="X10" s="16" t="s">
-        <v>152</v>
+        <v>206</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="X10" s="13" t="s">
+        <v>570</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>139</v>
+        <v>541</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="12" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>155</v>
+        <v>481</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>579</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>28</v>
+        <v>576</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>577</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>29</v>
+        <v>578</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>156</v>
+        <v>595</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="15" t="s">
-        <v>160</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
       <c r="O11" s="13" t="s">
-        <v>161</v>
+        <v>481</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>162</v>
+        <v>584</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>163</v>
+        <v>585</v>
       </c>
       <c r="R11" s="13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="V11" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="X11" s="16" t="s">
-        <v>169</v>
+        <v>206</v>
+      </c>
+      <c r="U11" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V11" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W11" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="X11" s="13" t="s">
+        <v>587</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>154</v>
+        <v>623</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="12" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>588</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>171</v>
+        <v>598</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>174</v>
+        <v>617</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="N12" s="13"/>
+        <v>609</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15" t="s">
+        <v>597</v>
+      </c>
       <c r="O12" s="13" t="s">
-        <v>179</v>
+        <v>481</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>180</v>
+        <v>481</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="R12" s="13">
-        <v>2013</v>
-      </c>
-      <c r="S12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="T12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="U12" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="V12" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="W12" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="X12" s="16" t="s">
-        <v>185</v>
+        <v>481</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X12" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="12" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>187</v>
+        <v>481</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>188</v>
+        <v>589</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>28</v>
+        <v>600</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>620</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>189</v>
+        <v>619</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>618</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>413</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>192</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
       <c r="O13" s="13" t="s">
-        <v>193</v>
+        <v>481</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>194</v>
+        <v>481</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="S13" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="T13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U13" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="V13" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="W13" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="X13" s="16" t="s">
-        <v>200</v>
+        <v>481</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W13" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X13" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>187</v>
+        <v>481</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="12" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>201</v>
+        <v>481</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>202</v>
+        <v>590</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>28</v>
+        <v>599</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>621</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>29</v>
+        <v>622</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>203</v>
+        <v>605</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>208</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
       <c r="O14" s="13" t="s">
-        <v>209</v>
+        <v>481</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>210</v>
+        <v>481</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="R14" s="13">
-        <v>2024</v>
-      </c>
-      <c r="S14" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="T14" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="U14" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="V14" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="W14" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="X14" s="16" t="s">
-        <v>217</v>
+        <v>481</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X14" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>201</v>
+        <v>581</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="12" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>218</v>
+        <v>97</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>219</v>
+        <v>591</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>528</v>
+        <v>591</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>221</v>
+        <v>29</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>222</v>
+        <v>606</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="15" t="s">
-        <v>224</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
       <c r="O15" s="13" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>226</v>
+        <v>481</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="R15" s="13">
-        <v>2025</v>
-      </c>
-      <c r="S15" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U15" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="V15" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="W15" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="X15" s="16" t="s">
-        <v>231</v>
+        <v>481</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W15" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X15" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y15" s="13" t="s">
-        <v>218</v>
+        <v>582</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="12" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>489</v>
+        <v>97</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>232</v>
+        <v>592</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>533</v>
+        <v>601</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -16010,74 +18574,68 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>233</v>
+        <v>607</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13" t="s">
-        <v>235</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
       <c r="O16" s="13" t="s">
-        <v>236</v>
+        <v>481</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>237</v>
+        <v>481</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="R16" s="13">
-        <v>2026</v>
-      </c>
-      <c r="S16" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="T16" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="V16" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="W16" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>415</v>
+        <v>481</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X16" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y16" s="13" t="s">
-        <v>240</v>
+        <v>583</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="12" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>241</v>
+        <v>97</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>242</v>
+        <v>481</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>593</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>523</v>
+        <v>602</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -16086,76 +18644,68 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>243</v>
+        <v>608</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>246</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
       <c r="O17" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="P17" s="11" t="s">
-        <v>539</v>
+        <v>481</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="R17" s="13">
-        <v>2025</v>
-      </c>
-      <c r="S17" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="T17" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="U17" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="V17" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="W17" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="X17" s="16" t="s">
-        <v>251</v>
+        <v>481</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W17" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X17" s="13" t="s">
+        <v>481</v>
       </c>
       <c r="Y17" s="13" t="s">
-        <v>252</v>
+        <v>594</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="12" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>253</v>
+        <v>97</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>253</v>
+        <v>481</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>254</v>
+        <v>615</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>520</v>
+        <v>616</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -16164,308 +18714,302 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>496</v>
+        <v>624</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>498</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="M18" s="13"/>
+        <v>625</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="15" t="s">
+        <v>626</v>
+      </c>
       <c r="N18" s="15" t="s">
-        <v>255</v>
+        <v>627</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>256</v>
+        <v>481</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>257</v>
+        <v>628</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>257</v>
+        <v>629</v>
       </c>
       <c r="R18" s="13">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="U18" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="V18" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="W18" s="25" t="s">
-        <v>500</v>
+        <v>206</v>
+      </c>
+      <c r="U18" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V18" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W18" s="24" t="s">
+        <v>630</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>501</v>
+        <v>631</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>261</v>
+        <v>542</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
-    <row r="19" spans="1:26" s="5" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="1:26">
       <c r="A19" s="12" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>262</v>
+        <v>100</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>263</v>
+        <v>100</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>476</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>532</v>
+        <v>101</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>269</v>
+        <v>103</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>439</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>270</v>
+        <v>106</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>272</v>
+        <v>108</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>273</v>
+        <v>109</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="R19" s="13">
-        <v>2026</v>
+        <v>109</v>
+      </c>
+      <c r="R19" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="S19" s="16" t="s">
-        <v>274</v>
+        <v>111</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="U19" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="V19" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="W19" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="X19" s="19" t="s">
-        <v>279</v>
+        <v>112</v>
+      </c>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="X19" s="16" t="s">
+        <v>114</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="Z19" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Z19" s="6"/>
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="12" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>538</v>
+        <v>117</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>282</v>
+        <v>517</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>283</v>
+        <v>118</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>458</v>
+        <v>119</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>533</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>285</v>
+        <v>120</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>286</v>
+        <v>121</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>288</v>
+        <v>123</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>288</v>
+        <v>124</v>
       </c>
       <c r="R20" s="13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="S20" s="16" t="s">
-        <v>289</v>
+        <v>125</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>291</v>
+        <v>127</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="W20" s="16" t="s">
-        <v>293</v>
+        <v>129</v>
       </c>
       <c r="X20" s="16" t="s">
-        <v>294</v>
+        <v>130</v>
       </c>
       <c r="Y20" s="13" t="s">
-        <v>295</v>
+        <v>116</v>
       </c>
       <c r="Z20" s="6"/>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="12" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>296</v>
+        <v>132</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>297</v>
+        <v>132</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>475</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>521</v>
+        <v>133</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>298</v>
+        <v>136</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>301</v>
+        <v>138</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>302</v>
+        <v>139</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>304</v>
+        <v>141</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>305</v>
+        <v>141</v>
       </c>
       <c r="R21" s="13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="S21" s="16" t="s">
-        <v>306</v>
+        <v>50</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>308</v>
+        <v>142</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>309</v>
+        <v>143</v>
       </c>
       <c r="W21" s="16" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="X21" s="16" t="s">
-        <v>311</v>
+        <v>145</v>
       </c>
       <c r="Y21" s="13" t="s">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="Z21" s="6"/>
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="12" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>312</v>
+        <v>147</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>312</v>
+        <v>147</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>313</v>
+        <v>148</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -16474,148 +19018,150 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>314</v>
+        <v>149</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>316</v>
+        <v>151</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>317</v>
+        <v>152</v>
       </c>
       <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
+      <c r="N22" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="O22" s="13" t="s">
-        <v>318</v>
+        <v>154</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>319</v>
+        <v>155</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>320</v>
+        <v>156</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
-        <v>321</v>
+        <v>157</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>322</v>
+        <v>158</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>322</v>
+        <v>160</v>
       </c>
       <c r="W22" s="16" t="s">
-        <v>323</v>
+        <v>161</v>
       </c>
       <c r="X22" s="16" t="s">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>253</v>
+        <v>147</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="12" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>326</v>
+        <v>163</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>473</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>525</v>
+        <v>164</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>327</v>
+        <v>167</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>328</v>
+        <v>168</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>459</v>
+        <v>169</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="15" t="s">
-        <v>329</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="N23" s="13"/>
       <c r="O23" s="13" t="s">
-        <v>330</v>
+        <v>172</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>331</v>
+        <v>173</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>332</v>
+        <v>174</v>
       </c>
       <c r="R23" s="13">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="S23" s="16" t="s">
         <v>50</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>258</v>
+        <v>51</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>333</v>
+        <v>175</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>334</v>
+        <v>176</v>
       </c>
       <c r="W23" s="16" t="s">
-        <v>335</v>
+        <v>177</v>
       </c>
       <c r="X23" s="16" t="s">
-        <v>336</v>
+        <v>178</v>
       </c>
       <c r="Y23" s="13" t="s">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="12" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>338</v>
+        <v>181</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -16623,77 +19169,77 @@
       <c r="H24" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="26" t="s">
-        <v>506</v>
+      <c r="I24" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="K24" s="23" t="s">
-        <v>504</v>
+        <v>183</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>441</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>505</v>
+        <v>403</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>339</v>
+        <v>184</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>340</v>
+        <v>185</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>341</v>
+        <v>186</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>342</v>
+        <v>187</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="R24" s="13">
-        <v>2026</v>
+        <v>188</v>
+      </c>
+      <c r="R24" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="S24" s="16" t="s">
-        <v>344</v>
+        <v>34</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>345</v>
+        <v>35</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>344</v>
+        <v>190</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="W24" s="27" t="s">
-        <v>503</v>
+        <v>191</v>
+      </c>
+      <c r="W24" s="16" t="s">
+        <v>192</v>
       </c>
       <c r="X24" s="16" t="s">
-        <v>502</v>
+        <v>193</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>281</v>
+        <v>180</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="12" t="s">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>346</v>
+        <v>194</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>346</v>
+        <v>194</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>347</v>
+        <v>195</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -16702,109 +19248,107 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>349</v>
+        <v>197</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>460</v>
+        <v>198</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>403</v>
+        <v>199</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>351</v>
+        <v>201</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>352</v>
+        <v>202</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>353</v>
+        <v>203</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>354</v>
+        <v>204</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>356</v>
+        <v>206</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>357</v>
+        <v>207</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>358</v>
+        <v>208</v>
       </c>
       <c r="W25" s="16" t="s">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="X25" s="16" t="s">
-        <v>360</v>
+        <v>210</v>
       </c>
       <c r="Y25" s="13" t="s">
-        <v>296</v>
+        <v>194</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="12" t="s">
-        <v>361</v>
+        <v>56</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>362</v>
+        <v>211</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>362</v>
+        <v>211</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>363</v>
+        <v>212</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>364</v>
+        <v>215</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>365</v>
+        <v>216</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="M26" s="15" t="s">
-        <v>366</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="M26" s="13"/>
       <c r="N26" s="15" t="s">
-        <v>367</v>
+        <v>217</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>369</v>
+        <v>219</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>370</v>
+        <v>220</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -16816,40 +19360,40 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>371</v>
+        <v>221</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>372</v>
+        <v>222</v>
       </c>
       <c r="W26" s="16" t="s">
-        <v>373</v>
+        <v>223</v>
       </c>
       <c r="X26" s="16" t="s">
-        <v>374</v>
+        <v>224</v>
       </c>
       <c r="Y26" s="13" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="12" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>376</v>
+        <v>479</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>225</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -16858,58 +19402,74 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>462</v>
+        <v>226</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>423</v>
+        <v>227</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="N27" s="15" t="s">
-        <v>378</v>
+        <v>404</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="s">
+        <v>228</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
+        <v>229</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="R27" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S27" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="T27" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="U27" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="V27" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="W27" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="X27" s="16" t="s">
+        <v>405</v>
+      </c>
       <c r="Y27" s="13" t="s">
-        <v>376</v>
+        <v>233</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="12" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>376</v>
+        <v>234</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>508</v>
+        <v>234</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>235</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -16917,77 +19477,77 @@
       <c r="H28" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="29" t="s">
-        <v>509</v>
+      <c r="I28" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>431</v>
+        <v>237</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>465</v>
+        <v>392</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>437</v>
+        <v>238</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>438</v>
+        <v>239</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>466</v>
+        <v>240</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>525</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>426</v>
+        <v>526</v>
       </c>
       <c r="R28" s="13">
-        <v>2026</v>
-      </c>
-      <c r="S28" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="T28" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U28" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="V28" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="W28" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="X28" s="13" t="s">
-        <v>429</v>
+        <v>2025</v>
+      </c>
+      <c r="S28" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="T28" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="U28" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="V28" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="W28" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="X28" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>380</v>
+        <v>245</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="12" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>376</v>
+        <v>246</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>491</v>
+        <v>246</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>381</v>
+        <v>247</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>382</v>
+        <v>506</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -16995,309 +19555,1175 @@
       <c r="H29" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>467</v>
+      <c r="I29" s="23" t="s">
+        <v>482</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>468</v>
+        <v>483</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>484</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>435</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="M29" s="13"/>
       <c r="N29" s="15" t="s">
-        <v>436</v>
+        <v>248</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>491</v>
+        <v>249</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>469</v>
+        <v>250</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="T29" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="X29" s="13" t="s">
-        <v>428</v>
+        <v>250</v>
+      </c>
+      <c r="R29" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T29" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="V29" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="W29" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="X29" s="16" t="s">
+        <v>487</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>481</v>
+        <v>254</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" s="5" customFormat="1" ht="16.5" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>376</v>
+        <v>255</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>491</v>
+        <v>255</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>385</v>
+        <v>518</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="M30" s="20"/>
-      <c r="N30" s="21" t="s">
-        <v>439</v>
+        <v>258</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>632</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="N30" s="15" t="s">
+        <v>263</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>491</v>
+        <v>264</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>473</v>
+        <v>265</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>427</v>
+        <v>527</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
-      <c r="S30" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="T30" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
+      <c r="S30" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="T30" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="U30" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="V30" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="W30" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="X30" s="19" t="s">
+        <v>271</v>
+      </c>
       <c r="Y30" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="Z30" s="6"/>
+        <v>272</v>
+      </c>
+      <c r="Z30" s="7"/>
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="12" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>376</v>
+        <v>273</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>491</v>
+        <v>273</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>474</v>
+        <v>524</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>517</v>
+        <v>274</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>475</v>
+        <v>275</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>417</v>
+        <v>276</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>419</v>
+        <v>277</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>420</v>
+        <v>278</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>491</v>
+        <v>279</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>477</v>
+        <v>280</v>
       </c>
       <c r="Q31" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="T31" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="X31" s="13" t="s">
-        <v>422</v>
+        <v>280</v>
+      </c>
+      <c r="R31" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S31" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="U31" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="V31" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="W31" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="X31" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>386</v>
+        <v>287</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="12" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>387</v>
+        <v>288</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>491</v>
+        <v>288</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>488</v>
+        <v>289</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>388</v>
+        <v>507</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>389</v>
+        <v>28</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>390</v>
+        <v>29</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>479</v>
+        <v>292</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="N32" s="13"/>
+        <v>293</v>
+      </c>
+      <c r="N32" s="15" t="s">
+        <v>294</v>
+      </c>
       <c r="O32" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
+        <v>295</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q32" s="13" t="s">
+        <v>297</v>
+      </c>
       <c r="R32" s="13">
-        <v>2026</v>
-      </c>
-      <c r="S32" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="T32" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="X32" s="13" t="s">
-        <v>398</v>
+        <v>2025</v>
+      </c>
+      <c r="S32" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="T32" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="V32" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="W32" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="X32" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="Y32" s="13" t="s">
-        <v>387</v>
+        <v>234</v>
       </c>
       <c r="Z32" s="6"/>
     </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="Y33" s="4"/>
+    <row r="33" spans="1:26">
+      <c r="A33" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q33" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="R33" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S33" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="T33" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="V33" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="W33" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="X33" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y33" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z33" s="6"/>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="Y34" s="4"/>
+    <row r="34" spans="1:26">
+      <c r="A34" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q34" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="R34" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T34" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="U34" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="V34" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="W34" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="X34" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y34" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z34" s="6"/>
     </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="H35" s="4"/>
+    <row r="35" spans="1:26">
+      <c r="A35" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="K35" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q35" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="R35" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S35" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="T35" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="U35" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="V35" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="W35" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="X35" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y35" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z35" s="6"/>
     </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="H36" s="4"/>
+    <row r="36" spans="1:26">
+      <c r="A36" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="N36" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q36" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="R36" s="13">
+        <v>2024</v>
+      </c>
+      <c r="S36" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="T36" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="U36" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="V36" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="W36" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="X36" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y36" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="Z36" s="6"/>
     </row>
-    <row r="37" spans="1:25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="H37" s="4"/>
+    <row r="37" spans="1:26">
+      <c r="A37" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="N37" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="P37" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="R37" s="13">
+        <v>2025</v>
+      </c>
+      <c r="S37" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T37" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="U37" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="V37" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="W37" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="X37" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y37" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z37" s="6"/>
+    </row>
+    <row r="38" spans="1:26">
+      <c r="A38" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="N38" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="S38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="U38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="X38" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y38" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z38" s="6"/>
+    </row>
+    <row r="39" spans="1:26">
+      <c r="A39" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>495</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="N39" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="P39" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="R39" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S39" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T39" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="V39" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="W39" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="X39" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y39" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z39" s="6"/>
+    </row>
+    <row r="40" spans="1:26">
+      <c r="A40" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="N40" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="P40" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T40" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U40" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V40" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W40" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="X40" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="Y40" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z40" s="6"/>
+    </row>
+    <row r="41" spans="1:26">
+      <c r="A41" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="M41" s="20"/>
+      <c r="N41" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="R41" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S41" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T41" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U41" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V41" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z41" s="6"/>
+    </row>
+    <row r="42" spans="1:26">
+      <c r="A42" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="P42" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="R42" s="13"/>
+      <c r="S42" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T42" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U42" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V42" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W42" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="X42" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y42" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z42" s="6"/>
+    </row>
+    <row r="43" spans="1:26">
+      <c r="A43" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13">
+        <v>2026</v>
+      </c>
+      <c r="S43" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T43" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U43" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="V43" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="W43" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="X43" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="Y43" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="Z43" s="6"/>
+    </row>
+    <row r="44" spans="1:26">
+      <c r="A44" s="3"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="Y44" s="4"/>
+    </row>
+    <row r="45" spans="1:26">
+      <c r="A45" s="3"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="Y45" s="4"/>
+    </row>
+    <row r="46" spans="1:26">
+      <c r="A46" s="3"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:26">
+      <c r="A47" s="3"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:26">
+      <c r="A48" s="3"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="H48" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -17310,48 +20736,52 @@
     <hyperlink ref="N5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="M6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="N6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M7" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="M8" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="M10" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N10" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N11" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="M12" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="M13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N13" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="M14" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N14" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N15" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="M17" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N17" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N18" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="M19" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N19" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="M20" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N20" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="M21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="N23" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="M24" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N24" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="M25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="N25" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="M26" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="N26" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="M27" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N27" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="M32" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="M31" r:id="rId43" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
-    <hyperlink ref="N31" r:id="rId44" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
-    <hyperlink ref="N29" r:id="rId45" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
-    <hyperlink ref="M28" r:id="rId46" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
-    <hyperlink ref="N28" r:id="rId47" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
-    <hyperlink ref="N30" r:id="rId48" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
+    <hyperlink ref="M19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N20" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M21" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N25" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N28" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N29" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M32" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N34" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M35" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N37" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M38" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M43" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M42" r:id="rId41" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
+    <hyperlink ref="N42" r:id="rId42" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
+    <hyperlink ref="N40" r:id="rId43" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
+    <hyperlink ref="M39" r:id="rId44" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
+    <hyperlink ref="N39" r:id="rId45" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
+    <hyperlink ref="N41" r:id="rId46" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
+    <hyperlink ref="M8" r:id="rId47" xr:uid="{F2227BB7-C7C6-4A63-BC21-25041D725FC4}"/>
+    <hyperlink ref="M7" r:id="rId48" xr:uid="{686DFB38-CC34-422E-8DC4-D365B8CE1AAC}"/>
+    <hyperlink ref="N9" r:id="rId49" xr:uid="{3A63468A-580F-4DFB-BFAD-AA4C4030E02E}"/>
+    <hyperlink ref="M10" r:id="rId50" xr:uid="{CA79AC72-99CB-4630-9E20-9ACFB12FD7B6}"/>
+    <hyperlink ref="N10" r:id="rId51" xr:uid="{3770183D-4122-4C79-A40D-23E074FDF2C8}"/>
+    <hyperlink ref="M18" r:id="rId52" xr:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36FF8B1-78BF-4695-B49D-2DFEEDE56E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C821070-1CE2-4380-A30E-518AA2A72941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10590" yWindow="8055" windowWidth="28740" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="633">
   <si>
     <t>地圖編號</t>
   </si>
@@ -18823,8 +18823,12 @@
       <c r="T19" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
+      <c r="U19" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>481</v>
+      </c>
       <c r="W19" s="16" t="s">
         <v>113</v>
       </c>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C821070-1CE2-4380-A30E-518AA2A72941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61C0511-4EA3-4EA9-917E-56D099AE46C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10590" yWindow="8055" windowWidth="28740" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="634">
   <si>
     <t>地圖編號</t>
   </si>
@@ -16939,6 +16939,9 @@
       <t>」計畫獲選藝術家為基礎，並陸續加入獨立藝術家與策展人。團名回應當代藝術的變異與不確定性，將藝術實踐帶入日常生活與現實環境。團隊透過展覽、駐村、研究、工作坊與公共活動，串聯不同文化背景的創作者，探索藝術、地方與社會的關係，計畫遍及臺灣、韓國、蒙古、泰國及歐洲等地。</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>main-06_4/02.webp</t>
   </si>
 </sst>
 </file>
@@ -18404,7 +18407,7 @@
         <v>481</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>481</v>
+        <v>633</v>
       </c>
       <c r="Z13" s="6"/>
     </row>

--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61C0511-4EA3-4EA9-917E-56D099AE46C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DD1A4B-360B-4994-A067-570FEE6AB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="635">
   <si>
     <t>地圖編號</t>
   </si>
@@ -458,12 +458,6 @@
   </si>
   <si>
     <t>Belugas’ Sphere</t>
-  </si>
-  <si>
-    <t>充氦 Mylar 鋁膜氣球、光線感測器、馬達、壓電式喇叭、電子元件、控制系統與燈光。最終的作品組件與設備規格，將依展覽場地條件與主辦單位協調後確認。</t>
-  </si>
-  <si>
-    <t>helium-filled Mylar inflatables, light sensors, motors, piezo speakers, electronics, control systems, and light. Final component specifications will be confirmed in coordination with the organizer.</t>
   </si>
   <si>
     <t>《Belugas’ Sphere》重新回望 2008 年作品《Beluga Pod》，將其發展為一個由自主機器實體構成的新型生態系。每一隻白鯨皆以光線為感知與行動的依據，追尋光源，並隨著周遭環境的變化而移動。當光線強度發生改變，牠們的活動與群體行為也隨之演變，逐漸形成流動的隊形、群聚與歌唱，而非依循預先設定的固定編舞。
@@ -16942,6 +16936,46 @@
   </si>
   <si>
     <t>main-06_4/02.webp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>充氦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mylar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>鋁膜氣球、光線感測器、馬達、壓電式喇叭、電子元件、控制系統與燈光。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>helium-filled Mylar inflatables, light sensors, motors, piezo speakers, electronics, control systems, and light.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dries Depoorter</t>
   </si>
 </sst>
 </file>
@@ -17417,7 +17451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17447,7 +17481,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -17530,7 +17564,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -17539,16 +17573,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -17606,7 +17640,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -17621,10 +17655,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -17684,7 +17718,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -17699,10 +17733,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -17712,7 +17746,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -17733,10 +17767,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -17757,10 +17791,10 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>70</v>
+        <v>634</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>71</v>
@@ -17775,10 +17809,10 @@
         <v>74</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>75</v>
@@ -17835,10 +17869,10 @@
         <v>87</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>88</v>
@@ -17847,16 +17881,16 @@
         <v>89</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>90</v>
@@ -17871,16 +17905,16 @@
         <v>93</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>94</v>
@@ -17889,10 +17923,10 @@
         <v>95</v>
       </c>
       <c r="W6" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Y6" s="13" t="s">
         <v>87</v>
@@ -17913,10 +17947,10 @@
         <v>97</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -17925,52 +17959,52 @@
         <v>29</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K7" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="M7" s="31" t="s">
         <v>535</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="N7" s="15" t="s">
         <v>536</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>538</v>
       </c>
       <c r="O7" s="13" t="s">
         <v>98</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="R7" s="13">
         <v>2026</v>
       </c>
       <c r="S7" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="T7" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="T7" s="16" t="s">
-        <v>546</v>
-      </c>
       <c r="U7" s="16" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="W7" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="X7" s="16" t="s">
         <v>545</v>
-      </c>
-      <c r="W7" s="16" t="s">
-        <v>574</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>547</v>
       </c>
       <c r="Y7" s="13" t="s">
         <v>97</v>
@@ -17988,13 +18022,13 @@
         <v>97</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>28</v>
@@ -18003,51 +18037,51 @@
         <v>29</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="14"/>
       <c r="M8" s="31" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="R8" s="13">
         <v>2026</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U8" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="X8" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
@@ -18062,13 +18096,13 @@
         <v>97</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>88</v>
@@ -18077,51 +18111,51 @@
         <v>89</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P9" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="Q9" s="13" t="s">
         <v>558</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>560</v>
       </c>
       <c r="R9" s="13">
         <v>2024</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U9" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V9" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="X9" s="13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
@@ -18136,13 +18170,13 @@
         <v>97</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>28</v>
@@ -18151,51 +18185,51 @@
         <v>29</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="32" t="s">
+        <v>563</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P10" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="N10" s="33" t="s">
+      <c r="Q10" s="13" t="s">
         <v>566</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>568</v>
       </c>
       <c r="R10" s="13">
         <v>2023</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U10" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W10" s="13" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="X10" s="13" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
@@ -18210,62 +18244,62 @@
         <v>97</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F11" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>575</v>
+      </c>
+      <c r="H11" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="G11" s="28" t="s">
-        <v>577</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>578</v>
-      </c>
       <c r="I11" s="14" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="R11" s="13">
         <v>2026</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U11" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V11" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="X11" s="13" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
@@ -18280,13 +18314,13 @@
         <v>97</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>28</v>
@@ -18295,49 +18329,49 @@
         <v>29</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
@@ -18352,62 +18386,62 @@
         <v>97</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X13" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
@@ -18422,62 +18456,62 @@
         <v>97</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
@@ -18492,13 +18526,13 @@
         <v>97</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>28</v>
@@ -18507,47 +18541,47 @@
         <v>29</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X15" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y15" s="13" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
@@ -18562,13 +18596,13 @@
         <v>97</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -18577,47 +18611,47 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X16" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y16" s="13" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
@@ -18632,13 +18666,13 @@
         <v>97</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -18647,47 +18681,47 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X17" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y17" s="13" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
@@ -18702,13 +18736,13 @@
         <v>97</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -18717,51 +18751,51 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P18" s="13" t="s">
         <v>626</v>
       </c>
-      <c r="N18" s="15" t="s">
+      <c r="Q18" s="13" t="s">
         <v>627</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P18" s="13" t="s">
-        <v>628</v>
-      </c>
-      <c r="Q18" s="13" t="s">
-        <v>629</v>
       </c>
       <c r="R18" s="13">
         <v>2025</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V18" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W18" s="24" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
@@ -18779,7 +18813,7 @@
         <v>100</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>101</v>
@@ -18797,10 +18831,10 @@
         <v>105</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>106</v>
@@ -18827,10 +18861,10 @@
         <v>112</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W19" s="16" t="s">
         <v>113</v>
@@ -18860,7 +18894,7 @@
         <v>117</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>28</v>
@@ -18875,10 +18909,10 @@
         <v>119</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M20" s="15" t="s">
         <v>120</v>
@@ -18935,7 +18969,7 @@
         <v>132</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>133</v>
@@ -18953,10 +18987,10 @@
         <v>137</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>138</v>
@@ -18982,17 +19016,17 @@
       <c r="T21" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="U21" s="16" t="s">
+      <c r="U21" s="24" t="s">
+        <v>632</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>633</v>
+      </c>
+      <c r="W21" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="X21" s="16" t="s">
         <v>143</v>
-      </c>
-      <c r="W21" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>145</v>
       </c>
       <c r="Y21" s="13" t="s">
         <v>132</v>
@@ -19004,19 +19038,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>148</v>
-      </c>
       <c r="F22" s="13" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -19025,53 +19059,53 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="L22" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="P22" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="O22" s="13" t="s">
+      <c r="Q22" s="13" t="s">
         <v>154</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="T22" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="U22" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="T22" s="16" t="s">
+      <c r="V22" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="U22" s="16" t="s">
+      <c r="W22" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="X22" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="W22" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="X22" s="16" t="s">
-        <v>162</v>
-      </c>
       <c r="Y22" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
@@ -19080,50 +19114,50 @@
         <v>40</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="F23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="I23" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="J23" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="K23" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="L23" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="M23" s="15" t="s">
         <v>169</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>171</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q23" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="R23" s="13">
         <v>2013</v>
@@ -19135,19 +19169,19 @@
         <v>51</v>
       </c>
       <c r="U23" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="V23" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="W23" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="X23" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="W23" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="X23" s="16" t="s">
-        <v>178</v>
-      </c>
       <c r="Y23" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
@@ -19156,19 +19190,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>181</v>
-      </c>
       <c r="F24" s="13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -19177,34 +19211,34 @@
         <v>29</v>
       </c>
       <c r="I24" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="M24" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="N24" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="K24" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="M24" s="15" t="s">
+      <c r="O24" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="N24" s="15" t="s">
+      <c r="P24" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="R24" s="17" t="s">
         <v>187</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="R24" s="17" t="s">
-        <v>189</v>
       </c>
       <c r="S24" s="16" t="s">
         <v>34</v>
@@ -19213,19 +19247,19 @@
         <v>35</v>
       </c>
       <c r="U24" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="W24" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="V24" s="16" t="s">
+      <c r="X24" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="W24" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="X24" s="16" t="s">
-        <v>193</v>
-      </c>
       <c r="Y24" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
@@ -19234,19 +19268,19 @@
         <v>40</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -19255,55 +19289,55 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="K25" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="L25" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="M25" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="N25" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="O25" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="N25" s="15" t="s">
+      <c r="P25" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="U25" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="V25" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="W25" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="V25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="W25" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="X25" s="16" t="s">
-        <v>210</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
@@ -19312,50 +19346,50 @@
         <v>56</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="I26" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="J26" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="I26" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>216</v>
-      </c>
       <c r="K26" s="14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="P26" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="Q26" s="13" t="s">
         <v>218</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -19367,19 +19401,19 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="V26" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="W26" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="X26" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="W26" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="X26" s="16" t="s">
-        <v>224</v>
-      </c>
       <c r="Y26" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
@@ -19388,19 +19422,19 @@
         <v>68</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -19409,53 +19443,53 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="P27" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="O27" s="13" t="s">
+      <c r="Q27" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="R27" s="13">
         <v>2026</v>
       </c>
       <c r="S27" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U27" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="W27" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="X27" s="16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Y27" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
@@ -19464,19 +19498,19 @@
         <v>68</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -19485,55 +19519,55 @@
         <v>29</v>
       </c>
       <c r="I28" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="M28" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="J28" s="14" t="s">
+      <c r="N28" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="M28" s="15" t="s">
+      <c r="O28" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="N28" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>240</v>
-      </c>
       <c r="P28" s="11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R28" s="13">
         <v>2025</v>
       </c>
       <c r="S28" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T28" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U28" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="V28" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="W28" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="V28" s="16" t="s">
+      <c r="X28" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="W28" s="16" t="s">
+      <c r="Y28" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="X28" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="Y28" s="13" t="s">
-        <v>245</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
@@ -19542,19 +19576,19 @@
         <v>68</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -19563,29 +19597,29 @@
         <v>29</v>
       </c>
       <c r="I29" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="K29" s="23" t="s">
         <v>482</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="L29" s="14" t="s">
         <v>483</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>484</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>485</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="P29" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="O29" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>250</v>
-      </c>
       <c r="Q29" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R29" s="13">
         <v>2026</v>
@@ -19594,22 +19628,22 @@
         <v>50</v>
       </c>
       <c r="T29" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="V29" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="W29" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="X29" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y29" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="V29" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="W29" s="25" t="s">
-        <v>486</v>
-      </c>
-      <c r="X29" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="Y29" s="13" t="s">
-        <v>254</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
@@ -19618,76 +19652,76 @@
         <v>68</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C30" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="E30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="I30" s="30" t="s">
+        <v>630</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="K30" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="I30" s="30" t="s">
-        <v>632</v>
-      </c>
-      <c r="J30" s="18" t="s">
+      <c r="L30" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="K30" s="18" t="s">
+      <c r="M30" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="L30" s="18" t="s">
+      <c r="N30" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="M30" s="15" t="s">
+      <c r="O30" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="N30" s="15" t="s">
+      <c r="P30" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="O30" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="P30" s="13" t="s">
-        <v>265</v>
-      </c>
       <c r="Q30" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="T30" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="T30" s="16" t="s">
+      <c r="V30" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="U30" s="16" t="s">
+      <c r="W30" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="V30" s="16" t="s">
+      <c r="X30" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="W30" s="19" t="s">
+      <c r="Y30" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="X30" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y30" s="13" t="s">
-        <v>272</v>
       </c>
       <c r="Z30" s="7"/>
     </row>
@@ -19696,19 +19730,19 @@
         <v>68</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>88</v>
@@ -19717,55 +19751,55 @@
         <v>89</v>
       </c>
       <c r="I31" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="M31" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="N31" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="M31" s="15" t="s">
+      <c r="O31" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="N31" s="15" t="s">
+      <c r="P31" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="O31" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>280</v>
-      </c>
       <c r="Q31" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R31" s="13">
         <v>2025</v>
       </c>
       <c r="S31" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="U31" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="T31" s="16" t="s">
+      <c r="V31" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="W31" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="V31" s="16" t="s">
+      <c r="X31" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="W31" s="16" t="s">
+      <c r="Y31" s="13" t="s">
         <v>285</v>
-      </c>
-      <c r="X31" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="Y31" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
@@ -19774,19 +19808,19 @@
         <v>86</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>28</v>
@@ -19795,55 +19829,55 @@
         <v>29</v>
       </c>
       <c r="I32" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="K32" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="L32" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="N32" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="L32" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="M32" s="15" t="s">
+      <c r="O32" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="N32" s="15" t="s">
+      <c r="P32" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="O32" s="13" t="s">
+      <c r="Q32" s="13" t="s">
         <v>295</v>
-      </c>
-      <c r="P32" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q32" s="13" t="s">
-        <v>297</v>
       </c>
       <c r="R32" s="13">
         <v>2025</v>
       </c>
       <c r="S32" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="T32" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="T32" s="16" t="s">
+      <c r="V32" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="U32" s="16" t="s">
+      <c r="W32" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="V32" s="16" t="s">
+      <c r="X32" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="W32" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="X32" s="16" t="s">
-        <v>303</v>
-      </c>
       <c r="Y32" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Z32" s="6"/>
     </row>
@@ -19852,19 +19886,19 @@
         <v>96</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>28</v>
@@ -19873,51 +19907,51 @@
         <v>29</v>
       </c>
       <c r="I33" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="K33" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="L33" s="14" t="s">
         <v>307</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>309</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q33" s="13" t="s">
         <v>310</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q33" s="13" t="s">
-        <v>312</v>
       </c>
       <c r="R33" s="13">
         <v>2025</v>
       </c>
       <c r="S33" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="T33" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="V33" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="W33" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="T33" s="16" t="s">
+      <c r="X33" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="U33" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="V33" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="W33" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="X33" s="16" t="s">
-        <v>316</v>
-      </c>
       <c r="Y33" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z33" s="6"/>
     </row>
@@ -19926,19 +19960,19 @@
         <v>99</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>28</v>
@@ -19947,29 +19981,29 @@
         <v>29</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="P34" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="O34" s="13" t="s">
+      <c r="Q34" s="13" t="s">
         <v>322</v>
-      </c>
-      <c r="P34" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q34" s="13" t="s">
-        <v>324</v>
       </c>
       <c r="R34" s="13">
         <v>2026</v>
@@ -19978,22 +20012,22 @@
         <v>50</v>
       </c>
       <c r="T34" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U34" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="V34" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="W34" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="V34" s="16" t="s">
+      <c r="X34" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="W34" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="X34" s="16" t="s">
-        <v>328</v>
-      </c>
       <c r="Y34" s="13" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z34" s="6"/>
     </row>
@@ -20002,19 +20036,19 @@
         <v>115</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>28</v>
@@ -20023,55 +20057,55 @@
         <v>29</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="M35" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="O35" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="N35" s="15" t="s">
+      <c r="P35" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="O35" s="13" t="s">
+      <c r="Q35" s="13" t="s">
         <v>333</v>
-      </c>
-      <c r="P35" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q35" s="13" t="s">
-        <v>335</v>
       </c>
       <c r="R35" s="13">
         <v>2026</v>
       </c>
       <c r="S35" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="T35" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="U35" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="V35" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="W35" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="X35" s="16" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="Y35" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Z35" s="6"/>
     </row>
@@ -20080,19 +20114,19 @@
         <v>131</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>28</v>
@@ -20101,76 +20135,76 @@
         <v>29</v>
       </c>
       <c r="I36" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="M36" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="J36" s="14" t="s">
+      <c r="N36" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="K36" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>393</v>
-      </c>
-      <c r="M36" s="15" t="s">
+      <c r="O36" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="N36" s="15" t="s">
+      <c r="P36" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="O36" s="13" t="s">
+      <c r="Q36" s="13" t="s">
         <v>344</v>
-      </c>
-      <c r="P36" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q36" s="13" t="s">
-        <v>346</v>
       </c>
       <c r="R36" s="13">
         <v>2024</v>
       </c>
       <c r="S36" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="T36" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="U36" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="T36" s="16" t="s">
+      <c r="V36" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="W36" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="V36" s="16" t="s">
+      <c r="X36" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="W36" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="X36" s="16" t="s">
-        <v>352</v>
-      </c>
       <c r="Y36" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Z36" s="6"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>355</v>
-      </c>
       <c r="F37" s="13" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>28</v>
@@ -20179,31 +20213,31 @@
         <v>29</v>
       </c>
       <c r="I37" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="M37" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="J37" s="14" t="s">
+      <c r="N37" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="K37" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="M37" s="15" t="s">
+      <c r="O37" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="N37" s="15" t="s">
+      <c r="P37" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="O37" s="13" t="s">
+      <c r="Q37" s="13" t="s">
         <v>360</v>
-      </c>
-      <c r="P37" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q37" s="13" t="s">
-        <v>362</v>
       </c>
       <c r="R37" s="13">
         <v>2025</v>
@@ -20215,19 +20249,19 @@
         <v>35</v>
       </c>
       <c r="U37" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="V37" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="W37" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="V37" s="16" t="s">
+      <c r="X37" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="W37" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="X37" s="16" t="s">
-        <v>366</v>
-      </c>
       <c r="Y37" s="13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Z37" s="6"/>
     </row>
@@ -20236,19 +20270,19 @@
         <v>24</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>28</v>
@@ -20257,55 +20291,55 @@
         <v>29</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M38" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="N38" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="O38" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="N38" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="O38" s="13" t="s">
-        <v>371</v>
-      </c>
       <c r="P38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="U38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="X38" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Y38" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Z38" s="6"/>
     </row>
@@ -20314,19 +20348,19 @@
         <v>24</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>28</v>
@@ -20335,55 +20369,55 @@
         <v>29</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K39" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="N39" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P39" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="L39" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="M39" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="N39" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="O39" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P39" s="13" t="s">
-        <v>456</v>
-      </c>
       <c r="Q39" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R39" s="13">
         <v>2026</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T39" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U39" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="V39" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="W39" s="28" t="s">
         <v>496</v>
       </c>
-      <c r="V39" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="W39" s="28" t="s">
-        <v>498</v>
-      </c>
       <c r="X39" s="13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y39" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="Z39" s="6"/>
     </row>
@@ -20392,19 +20426,19 @@
         <v>24</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>28</v>
@@ -20413,53 +20447,53 @@
         <v>29</v>
       </c>
       <c r="I40" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="N40" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P40" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="J40" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="M40" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="N40" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="O40" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P40" s="13" t="s">
-        <v>459</v>
-      </c>
       <c r="Q40" s="13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="R40" s="13"/>
       <c r="S40" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T40" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U40" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V40" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W40" s="13" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="X40" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="Y40" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Z40" s="6"/>
     </row>
@@ -20468,19 +20502,19 @@
         <v>24</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>28</v>
@@ -20489,49 +20523,49 @@
         <v>29</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J41" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="L41" s="14" t="s">
         <v>422</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>424</v>
       </c>
       <c r="M41" s="20"/>
       <c r="N41" s="21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="O41" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q41" s="13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="R41" s="13">
         <v>2026</v>
       </c>
       <c r="S41" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T41" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U41" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V41" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
       <c r="Y41" s="13" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Z41" s="6"/>
     </row>
@@ -20540,19 +20574,19 @@
         <v>24</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>28</v>
@@ -20561,53 +20595,53 @@
         <v>29</v>
       </c>
       <c r="I42" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="N42" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="P42" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="J42" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>466</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="M42" s="15" t="s">
+      <c r="Q42" s="13" t="s">
         <v>409</v>
-      </c>
-      <c r="N42" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="O42" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="P42" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q42" s="13" t="s">
-        <v>411</v>
       </c>
       <c r="R42" s="13"/>
       <c r="S42" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T42" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U42" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="V42" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W42" s="13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="X42" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Y42" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Z42" s="6"/>
     </row>
@@ -20616,44 +20650,44 @@
         <v>40</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="F43" s="13" t="s">
+      <c r="H43" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="I43" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="J43" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="K43" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="M43" s="15" t="s">
         <v>382</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="L43" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>384</v>
       </c>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
@@ -20661,25 +20695,25 @@
         <v>2026</v>
       </c>
       <c r="S43" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="T43" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="U43" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="V43" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="W43" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="X43" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="T43" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="U43" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="V43" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="W43" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="X43" s="13" t="s">
-        <v>388</v>
-      </c>
       <c r="Y43" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Z43" s="6"/>
     </row>
@@ -20735,60 +20769,60 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="M6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N20" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="M21" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="M23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="M24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="M25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N25" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="M28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N28" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N29" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="M30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="M31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="M32" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="N34" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="M35" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="M36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="M37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="N37" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="M38" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="M43" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="M42" r:id="rId41" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
-    <hyperlink ref="N42" r:id="rId42" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
-    <hyperlink ref="N40" r:id="rId43" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
-    <hyperlink ref="M39" r:id="rId44" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
-    <hyperlink ref="N39" r:id="rId45" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
-    <hyperlink ref="N41" r:id="rId46" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
-    <hyperlink ref="M8" r:id="rId47" xr:uid="{F2227BB7-C7C6-4A63-BC21-25041D725FC4}"/>
-    <hyperlink ref="M7" r:id="rId48" xr:uid="{686DFB38-CC34-422E-8DC4-D365B8CE1AAC}"/>
-    <hyperlink ref="N9" r:id="rId49" xr:uid="{3A63468A-580F-4DFB-BFAD-AA4C4030E02E}"/>
-    <hyperlink ref="M10" r:id="rId50" xr:uid="{CA79AC72-99CB-4630-9E20-9ACFB12FD7B6}"/>
-    <hyperlink ref="N10" r:id="rId51" xr:uid="{3770183D-4122-4C79-A40D-23E074FDF2C8}"/>
-    <hyperlink ref="M18" r:id="rId52" xr:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
+    <hyperlink ref="M2" ns3:id="rId1" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" ns3:id="rId2" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N3" ns3:id="rId3" ns2:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M4" ns3:id="rId4" ns2:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M5" ns3:id="rId5" ns2:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N5" ns3:id="rId6" ns2:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M6" ns3:id="rId7" ns2:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N6" ns3:id="rId8" ns2:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M19" ns3:id="rId9" ns2:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N19" ns3:id="rId10" ns2:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M20" ns3:id="rId11" ns2:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N20" ns3:id="rId12" ns2:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M21" ns3:id="rId13" ns2:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N21" ns3:id="rId14" ns2:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N22" ns3:id="rId15" ns2:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M23" ns3:id="rId16" ns2:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" ns3:id="rId17" ns2:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N24" ns3:id="rId18" ns2:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M25" ns3:id="rId19" ns2:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N25" ns3:id="rId20" ns2:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N26" ns3:id="rId21" ns2:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M28" ns3:id="rId22" ns2:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N28" ns3:id="rId23" ns2:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N29" ns3:id="rId24" ns2:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M30" ns3:id="rId25" ns2:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N30" ns3:id="rId26" ns2:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M31" ns3:id="rId27" ns2:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N31" ns3:id="rId28" ns2:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M32" ns3:id="rId29" ns2:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N32" ns3:id="rId30" ns2:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N34" ns3:id="rId31" ns2:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M35" ns3:id="rId32" ns2:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N35" ns3:id="rId33" ns2:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M36" ns3:id="rId34" ns2:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N36" ns3:id="rId35" ns2:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M37" ns3:id="rId36" ns2:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N37" ns3:id="rId37" ns2:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M38" ns3:id="rId38" ns2:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N38" ns3:id="rId39" ns2:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M43" ns3:id="rId40" ns2:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M42" ns3:id="rId41" ns2:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
+    <hyperlink ref="N42" ns3:id="rId42" ns2:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
+    <hyperlink ref="N40" ns3:id="rId43" ns2:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
+    <hyperlink ref="M39" ns3:id="rId44" ns2:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
+    <hyperlink ref="N39" ns3:id="rId45" ns2:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
+    <hyperlink ref="N41" ns3:id="rId46" ns2:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
+    <hyperlink ref="M8" ns3:id="rId47" ns2:uid="{F2227BB7-C7C6-4A63-BC21-25041D725FC4}"/>
+    <hyperlink ref="M7" ns3:id="rId48" ns2:uid="{686DFB38-CC34-422E-8DC4-D365B8CE1AAC}"/>
+    <hyperlink ref="N9" ns3:id="rId49" ns2:uid="{3A63468A-580F-4DFB-BFAD-AA4C4030E02E}"/>
+    <hyperlink ref="M10" ns3:id="rId50" ns2:uid="{CA79AC72-99CB-4630-9E20-9ACFB12FD7B6}"/>
+    <hyperlink ref="N10" ns3:id="rId51" ns2:uid="{3770183D-4122-4C79-A40D-23E074FDF2C8}"/>
+    <hyperlink ref="M18" ns3:id="rId52" ns2:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" ns3:id="rId53"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DD1A4B-360B-4994-A067-570FEE6AB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E0764E66-48CB-490D-95B4-5C7216FDD819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="635">
   <si>
     <t>地圖編號</t>
   </si>
@@ -237,9 +238,6 @@
   </si>
   <si>
     <t>main-04</t>
-  </si>
-  <si>
-    <t>Dries Depooter</t>
   </si>
   <si>
     <t>比利時</t>
@@ -949,9 +947,6 @@
     <t>Bety Krňanská</t>
   </si>
   <si>
-    <t>Bety Krňanská 是1992年生的捷克藝術家，現居希臘雅典。創作介於繪畫、紡織工藝與科技之間，關注女性形象、身體自主權，以及慾望與數位文化的關係。她將拼布、鉤針、蠟染與繪畫等傳統技法結合 AI 生成影像，探討誘惑與自動化、手工與合成之間的張力。畢業於布拉格藝術、建築與設計學院繪畫藝術碩士，作品曾於雅典、布拉格及國際展覽展出。</t>
-  </si>
-  <si>
     <t>Bety Krňanská, born in 1992, is a Czech artist based in Athens. Working at the intersection of painting, textile craft, and technology, she explores female representation, bodily autonomy, and changing relationships between desire and digital culture. Her practice combines traditional techniques such as patchwork, crochet, batik, and painting with AI-generated imagery, examining tensions between seduction and automation, and between handmade and synthetic production. Krňanská holds an MFA in Painting from the Academy of Arts, Architecture and Design in Prague. Her work has been shown internationally in Athens, Prague, and other European contexts through solo and group exhibitions.</t>
   </si>
   <si>
@@ -1241,42 +1236,24 @@
     <t>開幕表演</t>
   </si>
   <si>
-    <t>performance-01</t>
-  </si>
-  <si>
     <t>https://fluidnoise.com/about/</t>
   </si>
   <si>
     <t>https://www.facebook.com/fluidnoise/?locale=zh_TW</t>
   </si>
   <si>
-    <t>artist-26</t>
-  </si>
-  <si>
-    <t>performance-01_1</t>
-  </si>
-  <si>
     <t>張哲瑜</t>
   </si>
   <si>
     <t>Che-Yu Chang</t>
   </si>
   <si>
-    <t>performance-01_3</t>
-  </si>
-  <si>
     <t>陳亮</t>
   </si>
   <si>
     <t>Liang Chen</t>
   </si>
   <si>
-    <t>performance-01_4</t>
-  </si>
-  <si>
-    <t>performance-02</t>
-  </si>
-  <si>
     <t>Félix-Antoine Morin</t>
   </si>
   <si>
@@ -1290,9 +1267,6 @@
   </si>
   <si>
     <t>https://felixantoinemorin.com/</t>
-  </si>
-  <si>
-    <t>artist-27</t>
   </si>
   <si>
     <t>音像表演</t>
@@ -1583,10 +1557,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Field Notes 2026</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>A scene, a frame.
 Some are landscapes seen before waking, while others are scenes from films I love. The ones left uncategorized may be fragments of memory. Places I may have once been, or places I may never be able to reach.
 The work is presented through a series of “places,” with an avatar placed within each one, creating a sense of being there, and not being there at the same time.</t>
@@ -11124,30 +11094,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>田調隨筆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - 2026</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -12390,9 +12336,6 @@
   <si>
     <t>噪流</t>
     <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>performance-01_2</t>
   </si>
   <si>
     <r>
@@ -16938,6 +16881,16 @@
     <t>main-06_4/02.webp</t>
   </si>
   <si>
+    <t>Field Notes – morning Taipei</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dries Depoorter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bety Krňanská </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -16946,6 +16899,59 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1992</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年生的捷克藝術家，現居希臘雅典。創作介於繪畫、紡織工藝與科技之間，關注女性形象、身體自主權，以及慾望與數位文化的關係。她將拼布、鉤針、蠟染與繪畫等傳統技法結合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>生成影像，探討誘惑與自動化、手工與合成之間的張力。畢業於布拉格藝術、建築與設計學院繪畫藝術碩士，作品曾於雅典、布拉格及國際展覽展出。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
       <t>充氦</t>
     </r>
     <r>
@@ -16975,7 +16981,41 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Dries Depoorter</t>
+    <t>artist-27</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>artist-26</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>performance-01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>performance-02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>performance-02_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>performance-02_2</t>
+  </si>
+  <si>
+    <t>performance-02_3</t>
+  </si>
+  <si>
+    <t>performance-02_4</t>
+  </si>
+  <si>
+    <t>札記 - 早安台北</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17451,7 +17491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17481,7 +17521,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -17564,7 +17604,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -17573,16 +17613,16 @@
         <v>29</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>31</v>
@@ -17640,7 +17680,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>28</v>
@@ -17655,10 +17695,10 @@
         <v>44</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -17718,7 +17758,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>28</v>
@@ -17733,10 +17773,10 @@
         <v>60</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>61</v>
@@ -17746,7 +17786,7 @@
         <v>62</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="Q4" s="13" t="s">
         <v>63</v>
@@ -17767,10 +17807,10 @@
         <v>67</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>57</v>
@@ -17791,64 +17831,64 @@
         <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="M5" s="15" t="s">
+      <c r="N5" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="O5" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="P5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="Q5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="R5" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>80</v>
       </c>
       <c r="S5" s="16" t="s">
         <v>50</v>
       </c>
       <c r="T5" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="U5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="U5" s="16" t="s">
+      <c r="V5" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="W5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="W5" s="16" t="s">
+      <c r="X5" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="X5" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="Y5" s="13" t="s">
         <v>69</v>
@@ -17857,100 +17897,100 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="M6" s="15" t="s">
+      <c r="N6" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="O6" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="P6" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="Q6" s="13" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="R6" s="13">
         <v>2023</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="U6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="V6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="16" t="s">
-        <v>95</v>
-      </c>
       <c r="W6" s="16" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="Y6" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z6" s="6"/>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>28</v>
@@ -17959,76 +17999,76 @@
         <v>29</v>
       </c>
       <c r="I7" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q7" s="13" t="s">
         <v>529</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>533</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>541</v>
       </c>
       <c r="R7" s="13">
         <v>2026</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="V7" s="16" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="W7" s="16" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="X7" s="16" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="Y7" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Z7" s="6"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>28</v>
@@ -18037,146 +18077,146 @@
         <v>29</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="14"/>
       <c r="M8" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q8" s="13" t="s">
         <v>535</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>547</v>
       </c>
       <c r="R8" s="13">
         <v>2026</v>
       </c>
       <c r="S8" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T8" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T8" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U8" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="X8" s="13" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="G9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="I9" s="23" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="15" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="R9" s="13">
         <v>2024</v>
       </c>
       <c r="S9" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T9" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T9" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U9" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V9" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="X9" s="13" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="Z9" s="6"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>28</v>
@@ -18185,142 +18225,142 @@
         <v>29</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="32" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="R10" s="13">
         <v>2023</v>
       </c>
       <c r="S10" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T10" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T10" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U10" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W10" s="13" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="X10" s="13" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="Z10" s="6"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="R11" s="13">
         <v>2026</v>
       </c>
       <c r="S11" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T11" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T11" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U11" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V11" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="X11" s="13" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>28</v>
@@ -18329,210 +18369,210 @@
         <v>29</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="Z12" s="6"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X13" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="Z13" s="6"/>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="F14" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>597</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>620</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>603</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>609</v>
       </c>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="Z14" s="6"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>28</v>
@@ -18541,68 +18581,68 @@
         <v>29</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X15" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y15" s="13" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>28</v>
@@ -18611,68 +18651,68 @@
         <v>29</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X16" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y16" s="13" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>28</v>
@@ -18681,68 +18721,68 @@
         <v>29</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="U17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X17" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="Y17" s="13" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="Z17" s="6"/>
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>28</v>
@@ -18751,150 +18791,150 @@
         <v>29</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="15" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="R18" s="13">
         <v>2025</v>
       </c>
       <c r="S18" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T18" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T18" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U18" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V18" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W18" s="24" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="Z18" s="6"/>
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="G19" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="I19" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="J19" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="K19" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="M19" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="M19" s="15" t="s">
+      <c r="N19" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="N19" s="15" t="s">
+      <c r="O19" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="P19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="Q19" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="Q19" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="R19" s="17" t="s">
+      <c r="S19" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S19" s="16" t="s">
+      <c r="T19" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="T19" s="16" t="s">
+      <c r="U19" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="W19" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="V19" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="W19" s="16" t="s">
+      <c r="X19" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="X19" s="16" t="s">
-        <v>114</v>
-      </c>
       <c r="Y19" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z19" s="6"/>
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>117</v>
-      </c>
       <c r="F20" s="13" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>28</v>
@@ -18903,109 +18943,109 @@
         <v>29</v>
       </c>
       <c r="I20" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="K20" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="K20" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="M20" s="15" t="s">
+      <c r="N20" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="15" t="s">
+      <c r="O20" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="P20" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="P20" s="13" t="s">
+      <c r="Q20" s="13" t="s">
         <v>123</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>124</v>
       </c>
       <c r="R20" s="13">
         <v>2026</v>
       </c>
       <c r="S20" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="T20" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="U20" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="U20" s="16" t="s">
+      <c r="V20" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="W20" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="W20" s="16" t="s">
+      <c r="X20" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="X20" s="16" t="s">
-        <v>130</v>
-      </c>
       <c r="Y20" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z20" s="6"/>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="G21" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="H21" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="I21" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="J21" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="K21" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="K21" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="M21" s="15" t="s">
+      <c r="N21" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="N21" s="15" t="s">
+      <c r="O21" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="P21" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="P21" s="13" t="s">
-        <v>141</v>
-      </c>
       <c r="Q21" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R21" s="13">
         <v>2026</v>
@@ -19014,22 +19054,22 @@
         <v>50</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U21" s="24" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="W21" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="X21" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="X21" s="16" t="s">
-        <v>143</v>
-      </c>
       <c r="Y21" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z21" s="6"/>
     </row>
@@ -19038,19 +19078,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>146</v>
-      </c>
       <c r="F22" s="13" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>28</v>
@@ -19059,53 +19099,53 @@
         <v>29</v>
       </c>
       <c r="I22" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="K22" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="L22" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="O22" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="O22" s="13" t="s">
+      <c r="P22" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="Q22" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>154</v>
       </c>
       <c r="R22" s="13">
         <v>2025</v>
       </c>
       <c r="S22" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="T22" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="T22" s="16" t="s">
+      <c r="U22" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="U22" s="16" t="s">
+      <c r="V22" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="V22" s="16" t="s">
+      <c r="W22" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="W22" s="16" t="s">
+      <c r="X22" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="X22" s="16" t="s">
-        <v>160</v>
-      </c>
       <c r="Y22" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z22" s="6"/>
     </row>
@@ -19114,50 +19154,50 @@
         <v>40</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="F23" s="13" t="s">
+      <c r="G23" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="I23" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="J23" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="K23" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="L23" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="M23" s="15" t="s">
         <v>168</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>169</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="P23" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="Q23" s="13" t="s">
         <v>171</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>172</v>
       </c>
       <c r="R23" s="13">
         <v>2013</v>
@@ -19169,19 +19209,19 @@
         <v>51</v>
       </c>
       <c r="U23" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="V23" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="V23" s="16" t="s">
+      <c r="W23" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="W23" s="16" t="s">
+      <c r="X23" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="X23" s="16" t="s">
-        <v>176</v>
-      </c>
       <c r="Y23" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Z23" s="6"/>
     </row>
@@ -19190,19 +19230,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>179</v>
-      </c>
       <c r="F24" s="13" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>28</v>
@@ -19211,34 +19251,34 @@
         <v>29</v>
       </c>
       <c r="I24" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="K24" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="M24" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="K24" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="M24" s="15" t="s">
+      <c r="N24" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="N24" s="15" t="s">
+      <c r="O24" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="P24" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="Q24" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="Q24" s="13" t="s">
+      <c r="R24" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="R24" s="17" t="s">
-        <v>187</v>
       </c>
       <c r="S24" s="16" t="s">
         <v>34</v>
@@ -19247,19 +19287,19 @@
         <v>35</v>
       </c>
       <c r="U24" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="V24" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="V24" s="16" t="s">
+      <c r="W24" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="W24" s="16" t="s">
+      <c r="X24" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="X24" s="16" t="s">
-        <v>191</v>
-      </c>
       <c r="Y24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z24" s="6"/>
     </row>
@@ -19268,19 +19308,19 @@
         <v>40</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>193</v>
-      </c>
       <c r="F25" s="13" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>28</v>
@@ -19289,55 +19329,55 @@
         <v>29</v>
       </c>
       <c r="I25" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="K25" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="L25" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="M25" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="N25" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="N25" s="15" t="s">
+      <c r="O25" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="O25" s="13" t="s">
+      <c r="P25" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="P25" s="13" t="s">
+      <c r="Q25" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>202</v>
       </c>
       <c r="R25" s="13">
         <v>2024</v>
       </c>
       <c r="S25" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T25" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T25" s="16" t="s">
+      <c r="U25" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="U25" s="16" t="s">
+      <c r="V25" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="V25" s="16" t="s">
+      <c r="W25" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="W25" s="16" t="s">
+      <c r="X25" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="X25" s="16" t="s">
-        <v>208</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z25" s="6"/>
     </row>
@@ -19346,50 +19386,50 @@
         <v>56</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="F26" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="I26" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="J26" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="J26" s="14" t="s">
-        <v>214</v>
-      </c>
       <c r="K26" s="14" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="O26" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="P26" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="Q26" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="R26" s="13">
         <v>2025</v>
@@ -19401,19 +19441,19 @@
         <v>35</v>
       </c>
       <c r="U26" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="V26" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="W26" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="W26" s="16" t="s">
+      <c r="X26" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="X26" s="16" t="s">
-        <v>222</v>
-      </c>
       <c r="Y26" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z26" s="6"/>
     </row>
@@ -19422,19 +19462,19 @@
         <v>68</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>28</v>
@@ -19443,53 +19483,53 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="J27" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J27" s="14" t="s">
-        <v>225</v>
-      </c>
       <c r="K27" s="14" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="O27" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="O27" s="13" t="s">
+      <c r="P27" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="P27" s="13" t="s">
+      <c r="Q27" s="13" t="s">
         <v>228</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>229</v>
       </c>
       <c r="R27" s="13">
         <v>2026</v>
       </c>
       <c r="S27" s="16" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U27" s="16" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="W27" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="X27" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y27" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="X27" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="Y27" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="Z27" s="6"/>
     </row>
@@ -19498,19 +19538,19 @@
         <v>68</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>233</v>
-      </c>
       <c r="F28" s="13" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>28</v>
@@ -19519,55 +19559,55 @@
         <v>29</v>
       </c>
       <c r="I28" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="J28" s="14" t="s">
+      <c r="K28" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="M28" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="M28" s="15" t="s">
+      <c r="N28" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="N28" s="15" t="s">
+      <c r="O28" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="O28" s="13" t="s">
-        <v>238</v>
-      </c>
       <c r="P28" s="11" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="R28" s="13">
         <v>2025</v>
       </c>
       <c r="S28" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T28" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="T28" s="16" t="s">
-        <v>204</v>
-      </c>
       <c r="U28" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="V28" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="V28" s="16" t="s">
+      <c r="W28" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="W28" s="16" t="s">
+      <c r="X28" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="X28" s="16" t="s">
+      <c r="Y28" s="13" t="s">
         <v>242</v>
-      </c>
-      <c r="Y28" s="13" t="s">
-        <v>243</v>
       </c>
       <c r="Z28" s="6"/>
     </row>
@@ -19576,19 +19616,19 @@
         <v>68</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>245</v>
-      </c>
       <c r="F29" s="13" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>28</v>
@@ -19597,29 +19637,29 @@
         <v>29</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="O29" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="O29" s="13" t="s">
+      <c r="P29" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="P29" s="13" t="s">
-        <v>248</v>
-      </c>
       <c r="Q29" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R29" s="13">
         <v>2026</v>
@@ -19628,22 +19668,22 @@
         <v>50</v>
       </c>
       <c r="T29" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="U29" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V29" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="V29" s="16" t="s">
+      <c r="W29" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="X29" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y29" s="13" t="s">
         <v>251</v>
-      </c>
-      <c r="W29" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="X29" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="Y29" s="13" t="s">
-        <v>252</v>
       </c>
       <c r="Z29" s="6"/>
     </row>
@@ -19652,76 +19692,76 @@
         <v>68</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C30" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="13" t="s">
+      <c r="F30" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="I30" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="I30" s="30" t="s">
-        <v>630</v>
-      </c>
-      <c r="J30" s="18" t="s">
+      <c r="K30" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="K30" s="18" t="s">
+      <c r="L30" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="L30" s="18" t="s">
+      <c r="M30" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="M30" s="15" t="s">
+      <c r="N30" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="N30" s="15" t="s">
+      <c r="O30" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="O30" s="13" t="s">
+      <c r="P30" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="P30" s="13" t="s">
-        <v>263</v>
-      </c>
       <c r="Q30" s="13" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="R30" s="13">
         <v>2026</v>
       </c>
       <c r="S30" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="T30" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="T30" s="16" t="s">
+      <c r="U30" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="U30" s="16" t="s">
+      <c r="V30" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="V30" s="16" t="s">
+      <c r="W30" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="W30" s="19" t="s">
+      <c r="X30" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="X30" s="19" t="s">
+      <c r="Y30" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="Y30" s="13" t="s">
-        <v>270</v>
       </c>
       <c r="Z30" s="7"/>
     </row>
@@ -19730,97 +19770,97 @@
         <v>68</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C31" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="F31" s="13" t="s">
+      <c r="G31" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="J31" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="14" t="s">
+      <c r="K31" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="M31" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="N31" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>393</v>
-      </c>
-      <c r="M31" s="15" t="s">
+      <c r="O31" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="N31" s="15" t="s">
+      <c r="P31" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="O31" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>278</v>
-      </c>
       <c r="Q31" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R31" s="13">
         <v>2025</v>
       </c>
       <c r="S31" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="U31" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="T31" s="16" t="s">
+      <c r="V31" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="U31" s="16" t="s">
+      <c r="W31" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="V31" s="16" t="s">
+      <c r="X31" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="W31" s="16" t="s">
+      <c r="Y31" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="X31" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="Y31" s="13" t="s">
-        <v>285</v>
       </c>
       <c r="Z31" s="6"/>
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>28</v>
@@ -19829,76 +19869,76 @@
         <v>29</v>
       </c>
       <c r="I32" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="K32" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="L32" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="M32" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="N32" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="L32" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="M32" s="15" t="s">
+      <c r="O32" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="N32" s="15" t="s">
+      <c r="P32" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="O32" s="13" t="s">
+      <c r="Q32" s="13" t="s">
         <v>293</v>
-      </c>
-      <c r="P32" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q32" s="13" t="s">
-        <v>295</v>
       </c>
       <c r="R32" s="13">
         <v>2025</v>
       </c>
       <c r="S32" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="T32" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="U32" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="T32" s="16" t="s">
+      <c r="V32" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="U32" s="16" t="s">
+      <c r="W32" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="V32" s="16" t="s">
+      <c r="X32" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="W32" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="X32" s="16" t="s">
-        <v>301</v>
-      </c>
       <c r="Y32" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z32" s="6"/>
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>28</v>
@@ -19907,72 +19947,72 @@
         <v>29</v>
       </c>
       <c r="I33" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="K33" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="L33" s="14" t="s">
         <v>305</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>307</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q33" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q33" s="13" t="s">
-        <v>310</v>
       </c>
       <c r="R33" s="13">
         <v>2025</v>
       </c>
       <c r="S33" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="T33" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="V33" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="W33" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="T33" s="16" t="s">
+      <c r="X33" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="U33" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="V33" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="W33" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="X33" s="16" t="s">
-        <v>314</v>
-      </c>
       <c r="Y33" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Z33" s="6"/>
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>28</v>
@@ -19981,29 +20021,29 @@
         <v>29</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="P34" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="O34" s="13" t="s">
+      <c r="Q34" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="P34" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q34" s="13" t="s">
-        <v>322</v>
       </c>
       <c r="R34" s="13">
         <v>2026</v>
@@ -20012,43 +20052,43 @@
         <v>50</v>
       </c>
       <c r="T34" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U34" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="V34" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="W34" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="V34" s="16" t="s">
+      <c r="X34" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="W34" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="X34" s="16" t="s">
-        <v>326</v>
-      </c>
       <c r="Y34" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z34" s="6"/>
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>28</v>
@@ -20057,76 +20097,76 @@
         <v>29</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="M35" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="O35" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="N35" s="15" t="s">
+      <c r="P35" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="O35" s="13" t="s">
+      <c r="Q35" s="13" t="s">
         <v>331</v>
-      </c>
-      <c r="P35" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q35" s="13" t="s">
-        <v>333</v>
       </c>
       <c r="R35" s="13">
         <v>2026</v>
       </c>
       <c r="S35" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T35" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="U35" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V35" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="W35" s="27" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="X35" s="16" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="Y35" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z35" s="6"/>
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>28</v>
@@ -20135,76 +20175,76 @@
         <v>29</v>
       </c>
       <c r="I36" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="M36" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="J36" s="14" t="s">
+      <c r="N36" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="K36" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="M36" s="15" t="s">
+      <c r="O36" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="N36" s="15" t="s">
+      <c r="P36" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="O36" s="13" t="s">
+      <c r="Q36" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="P36" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q36" s="13" t="s">
-        <v>344</v>
       </c>
       <c r="R36" s="13">
         <v>2024</v>
       </c>
       <c r="S36" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="T36" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="U36" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="T36" s="16" t="s">
+      <c r="V36" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="U36" s="16" t="s">
+      <c r="W36" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="V36" s="16" t="s">
+      <c r="X36" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="W36" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="X36" s="16" t="s">
-        <v>350</v>
-      </c>
       <c r="Y36" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Z36" s="6"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>353</v>
-      </c>
       <c r="F37" s="13" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>28</v>
@@ -20213,31 +20253,31 @@
         <v>29</v>
       </c>
       <c r="I37" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="M37" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="J37" s="14" t="s">
+      <c r="N37" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="K37" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="M37" s="15" t="s">
+      <c r="O37" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="N37" s="15" t="s">
+      <c r="P37" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="O37" s="13" t="s">
+      <c r="Q37" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="P37" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q37" s="13" t="s">
-        <v>360</v>
       </c>
       <c r="R37" s="13">
         <v>2025</v>
@@ -20249,118 +20289,112 @@
         <v>35</v>
       </c>
       <c r="U37" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="V37" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="W37" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="V37" s="16" t="s">
+      <c r="X37" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="W37" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="X37" s="16" t="s">
-        <v>364</v>
-      </c>
       <c r="Y37" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Z37" s="6"/>
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="12" t="s">
-        <v>24</v>
+        <v>629</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>464</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>499</v>
+        <v>370</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>28</v>
+        <v>371</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>29</v>
+        <v>372</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="M38" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="N38" s="15" t="s">
-        <v>368</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N38" s="13"/>
       <c r="O38" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="P38" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="Q38" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="R38" s="13" t="s">
-        <v>479</v>
+        <v>626</v>
+      </c>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13">
+        <v>2026</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>479</v>
+        <v>375</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>479</v>
+        <v>376</v>
       </c>
       <c r="U38" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V38" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W38" s="13" t="s">
-        <v>479</v>
+        <v>541</v>
       </c>
       <c r="X38" s="13" t="s">
-        <v>479</v>
+        <v>377</v>
       </c>
       <c r="Y38" s="13" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>366</v>
+        <v>628</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>492</v>
+        <v>467</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>457</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>28</v>
@@ -20368,77 +20402,77 @@
       <c r="H39" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I39" s="29" t="s">
-        <v>493</v>
+      <c r="I39" s="14" t="s">
+        <v>440</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>453</v>
+        <v>403</v>
       </c>
       <c r="M39" s="15" t="s">
-        <v>425</v>
+        <v>364</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="O39" s="13" t="s">
-        <v>479</v>
+        <v>625</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="R39" s="13">
-        <v>2026</v>
+        <v>467</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>467</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>384</v>
+        <v>467</v>
       </c>
       <c r="T39" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>494</v>
+        <v>467</v>
+      </c>
+      <c r="U39" s="13" t="s">
+        <v>467</v>
       </c>
       <c r="V39" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="W39" s="28" t="s">
-        <v>496</v>
+        <v>467</v>
+      </c>
+      <c r="W39" s="13" t="s">
+        <v>467</v>
       </c>
       <c r="X39" s="13" t="s">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="Y39" s="13" t="s">
-        <v>370</v>
+        <v>628</v>
       </c>
       <c r="Z39" s="6"/>
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>366</v>
+        <v>628</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>28</v>
@@ -20447,74 +20481,70 @@
         <v>29</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="M40" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="N40" s="15" t="s">
-        <v>424</v>
+        <v>412</v>
+      </c>
+      <c r="M40" s="20"/>
+      <c r="N40" s="21" t="s">
+        <v>417</v>
       </c>
       <c r="O40" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="P40" s="13" t="s">
-        <v>457</v>
+        <v>467</v>
+      </c>
+      <c r="P40" s="11" t="s">
+        <v>634</v>
       </c>
       <c r="Q40" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="R40" s="13"/>
+        <v>620</v>
+      </c>
+      <c r="R40" s="13">
+        <v>2026</v>
+      </c>
       <c r="S40" s="13" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="T40" s="13" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="U40" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V40" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="W40" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="X40" s="13" t="s">
-        <v>416</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
       <c r="Y40" s="13" t="s">
-        <v>469</v>
+        <v>630</v>
       </c>
       <c r="Z40" s="6"/>
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>366</v>
+        <v>628</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>374</v>
+        <v>451</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>375</v>
+        <v>489</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>28</v>
@@ -20523,70 +20553,74 @@
         <v>29</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="L41" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="M41" s="20"/>
-      <c r="N41" s="21" t="s">
-        <v>427</v>
+        <v>397</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="N41" s="15" t="s">
+        <v>399</v>
       </c>
       <c r="O41" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="Q41" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="R41" s="13">
-        <v>2026</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="R41" s="13"/>
       <c r="S41" s="13" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="T41" s="13" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="U41" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V41" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
+        <v>467</v>
+      </c>
+      <c r="W41" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="X41" s="13" t="s">
+        <v>401</v>
+      </c>
       <c r="Y41" s="13" t="s">
-        <v>373</v>
+        <v>631</v>
       </c>
       <c r="Z41" s="6"/>
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C42" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>462</v>
-      </c>
       <c r="F42" s="13" t="s">
-        <v>501</v>
+        <v>367</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>28</v>
@@ -20595,53 +20629,53 @@
         <v>29</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="L42" s="14" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M42" s="15" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="O42" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="P42" s="13" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="Q42" s="13" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="R42" s="13"/>
       <c r="S42" s="13" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="T42" s="13" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="U42" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="V42" s="13" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="W42" s="13" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="X42" s="13" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="Y42" s="13" t="s">
-        <v>376</v>
+        <v>632</v>
       </c>
       <c r="Z42" s="6"/>
     </row>
@@ -20650,70 +20684,76 @@
         <v>40</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>377</v>
+        <v>628</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>476</v>
+        <v>467</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>480</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>378</v>
+        <v>488</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>379</v>
+        <v>28</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>552</v>
+        <v>29</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>481</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="K43" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="N43" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="O43" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="L43" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="P43" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q43" s="13" t="s">
+        <v>405</v>
+      </c>
       <c r="R43" s="13">
         <v>2026</v>
       </c>
       <c r="S43" s="13" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="T43" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="U43" s="13" t="s">
-        <v>479</v>
+        <v>376</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>482</v>
       </c>
       <c r="V43" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="W43" s="13" t="s">
-        <v>553</v>
+        <v>483</v>
+      </c>
+      <c r="W43" s="28" t="s">
+        <v>484</v>
       </c>
       <c r="X43" s="13" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="Y43" s="13" t="s">
-        <v>377</v>
+        <v>633</v>
       </c>
       <c r="Z43" s="6"/>
     </row>
@@ -20769,60 +20809,60 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M2" ns3:id="rId1" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M3" ns3:id="rId2" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N3" ns3:id="rId3" ns2:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M4" ns3:id="rId4" ns2:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M5" ns3:id="rId5" ns2:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N5" ns3:id="rId6" ns2:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="M6" ns3:id="rId7" ns2:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N6" ns3:id="rId8" ns2:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M19" ns3:id="rId9" ns2:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N19" ns3:id="rId10" ns2:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M20" ns3:id="rId11" ns2:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N20" ns3:id="rId12" ns2:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="M21" ns3:id="rId13" ns2:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N21" ns3:id="rId14" ns2:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N22" ns3:id="rId15" ns2:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="M23" ns3:id="rId16" ns2:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="M24" ns3:id="rId17" ns2:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N24" ns3:id="rId18" ns2:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="M25" ns3:id="rId19" ns2:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N25" ns3:id="rId20" ns2:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N26" ns3:id="rId21" ns2:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="M28" ns3:id="rId22" ns2:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N28" ns3:id="rId23" ns2:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N29" ns3:id="rId24" ns2:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="M30" ns3:id="rId25" ns2:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N30" ns3:id="rId26" ns2:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="M31" ns3:id="rId27" ns2:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N31" ns3:id="rId28" ns2:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="M32" ns3:id="rId29" ns2:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N32" ns3:id="rId30" ns2:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="N34" ns3:id="rId31" ns2:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="M35" ns3:id="rId32" ns2:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N35" ns3:id="rId33" ns2:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="M36" ns3:id="rId34" ns2:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="N36" ns3:id="rId35" ns2:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="M37" ns3:id="rId36" ns2:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="N37" ns3:id="rId37" ns2:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="M38" ns3:id="rId38" ns2:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N38" ns3:id="rId39" ns2:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="M43" ns3:id="rId40" ns2:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="M42" ns3:id="rId41" ns2:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
-    <hyperlink ref="N42" ns3:id="rId42" ns2:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
-    <hyperlink ref="N40" ns3:id="rId43" ns2:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
-    <hyperlink ref="M39" ns3:id="rId44" ns2:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
-    <hyperlink ref="N39" ns3:id="rId45" ns2:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
-    <hyperlink ref="N41" ns3:id="rId46" ns2:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
-    <hyperlink ref="M8" ns3:id="rId47" ns2:uid="{F2227BB7-C7C6-4A63-BC21-25041D725FC4}"/>
-    <hyperlink ref="M7" ns3:id="rId48" ns2:uid="{686DFB38-CC34-422E-8DC4-D365B8CE1AAC}"/>
-    <hyperlink ref="N9" ns3:id="rId49" ns2:uid="{3A63468A-580F-4DFB-BFAD-AA4C4030E02E}"/>
-    <hyperlink ref="M10" ns3:id="rId50" ns2:uid="{CA79AC72-99CB-4630-9E20-9ACFB12FD7B6}"/>
-    <hyperlink ref="N10" ns3:id="rId51" ns2:uid="{3770183D-4122-4C79-A40D-23E074FDF2C8}"/>
-    <hyperlink ref="M18" ns3:id="rId52" ns2:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N19" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N20" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M21" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N25" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N28" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N29" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M30" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M32" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N34" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M35" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N37" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N39" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M41" r:id="rId41" xr:uid="{BB1CE165-A387-4418-8295-83320A6E1C6D}"/>
+    <hyperlink ref="N41" r:id="rId42" xr:uid="{1FCC1871-0234-468A-B0DD-4ADC6A22392C}"/>
+    <hyperlink ref="N42" r:id="rId43" xr:uid="{4E4A19F5-A88D-4C37-BA17-3BBEAFC105ED}"/>
+    <hyperlink ref="N40" r:id="rId44" xr:uid="{E30D8491-B1C1-42D5-9BD9-C45AA2592264}"/>
+    <hyperlink ref="M8" r:id="rId45" xr:uid="{F2227BB7-C7C6-4A63-BC21-25041D725FC4}"/>
+    <hyperlink ref="M7" r:id="rId46" xr:uid="{686DFB38-CC34-422E-8DC4-D365B8CE1AAC}"/>
+    <hyperlink ref="N9" r:id="rId47" xr:uid="{3A63468A-580F-4DFB-BFAD-AA4C4030E02E}"/>
+    <hyperlink ref="M10" r:id="rId48" xr:uid="{CA79AC72-99CB-4630-9E20-9ACFB12FD7B6}"/>
+    <hyperlink ref="N10" r:id="rId49" xr:uid="{3770183D-4122-4C79-A40D-23E074FDF2C8}"/>
+    <hyperlink ref="M18" r:id="rId50" xr:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
+    <hyperlink ref="N43" r:id="rId51" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
+    <hyperlink ref="M43" r:id="rId52" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" ns3:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_作品&藝術家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E0764E66-48CB-490D-95B4-5C7216FDD819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4076703A-0812-4C09-9466-41ADB27C711D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="作品&amp;藝術家" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="650">
   <si>
     <t>地圖編號</t>
   </si>
@@ -17017,12 +17016,73 @@
     <t>札記 - 早安台北</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>影片連結</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XTPzJ-lzobo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19ydHg35yHbzjiYRbXFdiCg8YsLtRCEIM/view?usp=drive_link
+https://drive.google.com/file/d/118It20SgZ5u1doug79jlyLPdWwQnHtBe/view?usp=drive_link</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/ygRaaQP0NXk?si=10N-19-A1487ZL7d</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/OvTRXUJFpq0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/ECsMa6HxrOY</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-LQRlGfzne0_J4nhxIvUTFjCue4MyWAs/view?usp=sharing</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/xUBnyI_IK8M</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/150U2efvgK8mYunYcL4LKPXYRh2HY7Y4d/view?u%20sp=sharing</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sqmmYXyaynXnnQO-ncI7cicJtZHI21bf/view?usp=sharing</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/nRK3TdYaKGM</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Dhok3VN7KAiCEjjIdWa8hEC6QE7sIfd3/view?usp=sharing</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/JM4bneQTeUM</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LFIEck_1-%20tSaa36swMT62zVr4apO8PCo/view?usp=sharing</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n8bIwTVwjCnG63VbpJw7fkNXDTuxtC6/view?usp=%20drive_link</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -17165,6 +17225,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -17188,7 +17256,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -17277,6 +17345,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -17492,25 +17563,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="4" width="15.42578125" customWidth="1"/>
     <col min="5" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" customWidth="1"/>
     <col min="9" max="14" width="21.28515625" customWidth="1"/>
     <col min="15" max="15" width="9.140625" customWidth="1"/>
     <col min="16" max="16" width="26.85546875" customWidth="1"/>
     <col min="17" max="17" width="16.42578125" customWidth="1"/>
-    <col min="18" max="22" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" customWidth="1"/>
+    <col min="19" max="22" width="11.5703125" customWidth="1"/>
     <col min="23" max="24" width="16.140625" customWidth="1"/>
-    <col min="25" max="25" width="18.85546875" customWidth="1"/>
+    <col min="25" max="26" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="25.5">
+    <row r="1" spans="1:27" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -17586,8 +17658,11 @@
       <c r="Y1" s="9" t="s">
         <v>23</v>
       </c>
+      <c r="Z1" s="35" t="s">
+        <v>635</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="12" t="s">
         <v>24</v>
       </c>
@@ -17661,9 +17736,10 @@
       <c r="Y2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="6"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3" s="12" t="s">
         <v>40</v>
       </c>
@@ -17739,9 +17815,10 @@
       <c r="Y3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Z3" s="6"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="6"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4" s="12" t="s">
         <v>56</v>
       </c>
@@ -17815,9 +17892,10 @@
       <c r="Y4" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="6"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="6"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5" s="12" t="s">
         <v>68</v>
       </c>
@@ -17893,9 +17971,10 @@
       <c r="Y5" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="Z5" s="6"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="6"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6" s="12" t="s">
         <v>85</v>
       </c>
@@ -17971,9 +18050,10 @@
       <c r="Y6" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="Z6" s="6"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="6"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7" s="12" t="s">
         <v>95</v>
       </c>
@@ -18049,9 +18129,10 @@
       <c r="Y7" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="Z7" s="6"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="6"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8" s="12" t="s">
         <v>95</v>
       </c>
@@ -18123,9 +18204,10 @@
       <c r="Y8" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="Z8" s="6"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="6"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9" s="12" t="s">
         <v>95</v>
       </c>
@@ -18197,9 +18279,10 @@
       <c r="Y9" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="Z9" s="6"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="6"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10" s="12" t="s">
         <v>95</v>
       </c>
@@ -18271,9 +18354,10 @@
       <c r="Y10" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="Z10" s="6"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="6"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11" s="12" t="s">
         <v>95</v>
       </c>
@@ -18341,9 +18425,10 @@
       <c r="Y11" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="Z11" s="6"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="6"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12" s="12" t="s">
         <v>95</v>
       </c>
@@ -18413,9 +18498,10 @@
       <c r="Y12" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="6"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13" s="12" t="s">
         <v>95</v>
       </c>
@@ -18483,9 +18569,10 @@
       <c r="Y13" s="13" t="s">
         <v>619</v>
       </c>
-      <c r="Z13" s="6"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="6"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14" s="12" t="s">
         <v>95</v>
       </c>
@@ -18553,9 +18640,10 @@
       <c r="Y14" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="Z14" s="6"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="6"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15" s="12" t="s">
         <v>95</v>
       </c>
@@ -18623,9 +18711,10 @@
       <c r="Y15" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="Z15" s="6"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="6"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16" s="12" t="s">
         <v>95</v>
       </c>
@@ -18693,9 +18782,10 @@
       <c r="Y16" s="13" t="s">
         <v>569</v>
       </c>
-      <c r="Z16" s="6"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="6"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:27">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -18763,9 +18853,10 @@
       <c r="Y17" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="Z17" s="6"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="6"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:27">
       <c r="A18" s="12" t="s">
         <v>95</v>
       </c>
@@ -18837,9 +18928,10 @@
       <c r="Y18" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="Z18" s="6"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="6"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:27">
       <c r="A19" s="12" t="s">
         <v>98</v>
       </c>
@@ -18915,9 +19007,10 @@
       <c r="Y19" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="Z19" s="6"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="6"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:27">
       <c r="A20" s="12" t="s">
         <v>114</v>
       </c>
@@ -18993,9 +19086,12 @@
       <c r="Y20" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="Z20" s="6"/>
+      <c r="Z20" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="AA20" s="6"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:27">
       <c r="A21" s="12" t="s">
         <v>130</v>
       </c>
@@ -19071,9 +19167,12 @@
       <c r="Y21" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="AA21" s="6"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:27">
       <c r="A22" s="12" t="s">
         <v>24</v>
       </c>
@@ -19147,9 +19246,12 @@
       <c r="Y22" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="Z22" s="6"/>
+      <c r="Z22" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="AA22" s="6"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:27">
       <c r="A23" s="12" t="s">
         <v>40</v>
       </c>
@@ -19223,9 +19325,10 @@
       <c r="Y23" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="Z23" s="6"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="6"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:27">
       <c r="A24" s="12" t="s">
         <v>24</v>
       </c>
@@ -19301,9 +19404,12 @@
       <c r="Y24" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="Z24" s="6"/>
+      <c r="Z24" s="31" t="s">
+        <v>639</v>
+      </c>
+      <c r="AA24" s="6"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:27">
       <c r="A25" s="12" t="s">
         <v>40</v>
       </c>
@@ -19379,9 +19485,12 @@
       <c r="Y25" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="Z25" s="6"/>
+      <c r="Z25" s="31" t="s">
+        <v>646</v>
+      </c>
+      <c r="AA25" s="6"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:27">
       <c r="A26" s="12" t="s">
         <v>56</v>
       </c>
@@ -19455,9 +19564,12 @@
       <c r="Y26" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="Z26" s="6"/>
+      <c r="Z26" s="31" t="s">
+        <v>641</v>
+      </c>
+      <c r="AA26" s="6"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:27">
       <c r="A27" s="12" t="s">
         <v>68</v>
       </c>
@@ -19531,9 +19643,12 @@
       <c r="Y27" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="Z27" s="6"/>
+      <c r="Z27" s="31" t="s">
+        <v>644</v>
+      </c>
+      <c r="AA27" s="6"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:27">
       <c r="A28" s="12" t="s">
         <v>68</v>
       </c>
@@ -19609,9 +19724,12 @@
       <c r="Y28" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="Z28" s="6"/>
+      <c r="Z28" s="31" t="s">
+        <v>647</v>
+      </c>
+      <c r="AA28" s="6"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:27">
       <c r="A29" s="12" t="s">
         <v>68</v>
       </c>
@@ -19685,9 +19803,12 @@
       <c r="Y29" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="Z29" s="6"/>
+      <c r="Z29" s="31" t="s">
+        <v>648</v>
+      </c>
+      <c r="AA29" s="6"/>
     </row>
-    <row r="30" spans="1:26" s="5" customFormat="1" ht="16.5" customHeight="1">
+    <row r="30" spans="1:27" s="5" customFormat="1" ht="16.5" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>68</v>
       </c>
@@ -19763,9 +19884,10 @@
       <c r="Y30" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="Z30" s="7"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="7"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:27">
       <c r="A31" s="12" t="s">
         <v>68</v>
       </c>
@@ -19841,9 +19963,10 @@
       <c r="Y31" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="Z31" s="6"/>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="6"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:27">
       <c r="A32" s="12" t="s">
         <v>85</v>
       </c>
@@ -19919,9 +20042,12 @@
       <c r="Y32" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="Z32" s="6"/>
+      <c r="Z32" s="31" t="s">
+        <v>645</v>
+      </c>
+      <c r="AA32" s="6"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:27">
       <c r="A33" s="12" t="s">
         <v>95</v>
       </c>
@@ -19993,9 +20119,10 @@
       <c r="Y33" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="Z33" s="6"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="6"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:27">
       <c r="A34" s="12" t="s">
         <v>98</v>
       </c>
@@ -20069,9 +20196,12 @@
       <c r="Y34" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="Z34" s="6"/>
+      <c r="Z34" s="31" t="s">
+        <v>642</v>
+      </c>
+      <c r="AA34" s="6"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:27">
       <c r="A35" s="12" t="s">
         <v>114</v>
       </c>
@@ -20147,9 +20277,12 @@
       <c r="Y35" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="Z35" s="6"/>
+      <c r="Z35" s="31" t="s">
+        <v>640</v>
+      </c>
+      <c r="AA35" s="6"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:27">
       <c r="A36" s="12" t="s">
         <v>130</v>
       </c>
@@ -20225,9 +20358,12 @@
       <c r="Y36" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="Z36" s="6"/>
+      <c r="Z36" s="31" t="s">
+        <v>643</v>
+      </c>
+      <c r="AA36" s="6"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:27">
       <c r="A37" s="12" t="s">
         <v>349</v>
       </c>
@@ -20303,9 +20439,12 @@
       <c r="Y37" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="Z37" s="6"/>
+      <c r="Z37" s="31" t="s">
+        <v>649</v>
+      </c>
+      <c r="AA37" s="6"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:27">
       <c r="A38" s="12" t="s">
         <v>629</v>
       </c>
@@ -20375,9 +20514,10 @@
       <c r="Y38" s="13" t="s">
         <v>627</v>
       </c>
-      <c r="Z38" s="6"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="6"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:27">
       <c r="A39" s="12" t="s">
         <v>40</v>
       </c>
@@ -20453,9 +20593,10 @@
       <c r="Y39" s="13" t="s">
         <v>628</v>
       </c>
-      <c r="Z39" s="6"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="6"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:27">
       <c r="A40" s="12" t="s">
         <v>40</v>
       </c>
@@ -20525,9 +20666,10 @@
       <c r="Y40" s="13" t="s">
         <v>630</v>
       </c>
-      <c r="Z40" s="6"/>
+      <c r="Z40" s="13"/>
+      <c r="AA40" s="6"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:27">
       <c r="A41" s="12" t="s">
         <v>40</v>
       </c>
@@ -20601,9 +20743,10 @@
       <c r="Y41" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="Z41" s="6"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="6"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:27">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -20677,9 +20820,10 @@
       <c r="Y42" s="13" t="s">
         <v>632</v>
       </c>
-      <c r="Z42" s="6"/>
+      <c r="Z42" s="13"/>
+      <c r="AA42" s="6"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:27">
       <c r="A43" s="12" t="s">
         <v>40</v>
       </c>
@@ -20755,9 +20899,10 @@
       <c r="Y43" s="13" t="s">
         <v>633</v>
       </c>
-      <c r="Z43" s="6"/>
+      <c r="Z43" s="13"/>
+      <c r="AA43" s="6"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:27">
       <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="4"/>
@@ -20767,8 +20912,9 @@
       <c r="H44" s="4"/>
       <c r="O44" s="4"/>
       <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:27">
       <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="4"/>
@@ -20778,8 +20924,9 @@
       <c r="H45" s="4"/>
       <c r="O45" s="4"/>
       <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:27">
       <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="4"/>
@@ -20788,7 +20935,7 @@
       <c r="F46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:27">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
@@ -20797,7 +20944,7 @@
       <c r="F47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:27">
       <c r="A48" s="3"/>
       <c r="B48" s="1"/>
       <c r="C48" s="4"/>
@@ -20861,8 +21008,21 @@
     <hyperlink ref="M18" r:id="rId50" xr:uid="{7A71FE85-C7EC-4CCA-9CCB-02082C8E4C9E}"/>
     <hyperlink ref="N43" r:id="rId51" xr:uid="{EB135855-3B70-4A36-8227-E106B34FE89E}"/>
     <hyperlink ref="M43" r:id="rId52" xr:uid="{D338CF17-C509-4BDA-9E73-79BE90E8A529}"/>
+    <hyperlink ref="Z21" r:id="rId53" xr:uid="{A3129422-BC3C-4D18-BDFC-D71F8D595BC3}"/>
+    <hyperlink ref="Z22" r:id="rId54" xr:uid="{338EED50-B017-4550-AC7C-4910B30E1304}"/>
+    <hyperlink ref="Z24" r:id="rId55" xr:uid="{D045CA3E-EA74-4BA7-BF7E-A8E7EC534AD6}"/>
+    <hyperlink ref="Z35" r:id="rId56" xr:uid="{3DD6AE91-B84B-4425-81A6-06DEB82D1C1E}"/>
+    <hyperlink ref="Z26" r:id="rId57" xr:uid="{A99CB6DB-D04B-4E57-B1F1-5FE0FAF4588A}"/>
+    <hyperlink ref="Z34" r:id="rId58" xr:uid="{20FFB708-728B-4B7E-9C91-95DD0C7300FC}"/>
+    <hyperlink ref="Z36" r:id="rId59" xr:uid="{D0295532-E317-4D3E-83AE-7328283EE68C}"/>
+    <hyperlink ref="Z27" r:id="rId60" xr:uid="{3CA96AD6-C024-4B5F-AB8D-CAB096395384}"/>
+    <hyperlink ref="Z32" r:id="rId61" xr:uid="{5573748C-D0BF-403C-B4DC-99A87ABD2729}"/>
+    <hyperlink ref="Z25" r:id="rId62" xr:uid="{51E646D5-A822-4080-A7E7-B1FC19F60498}"/>
+    <hyperlink ref="Z28" r:id="rId63" xr:uid="{64FCC849-A670-422A-8840-CEA61B187B1A}"/>
+    <hyperlink ref="Z29" r:id="rId64" xr:uid="{B0FB2A24-EDC3-434E-8C6C-4CD4D297C04B}"/>
+    <hyperlink ref="Z37" r:id="rId65" xr:uid="{D71E78C4-449A-491D-B499-A6361613AD39}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
 </worksheet>
 </file>